--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY194"/>
+  <dimension ref="A1:AY195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129287650</v>
+        <v>129294077</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523970</v>
+        <v>523957</v>
       </c>
       <c r="R2" t="n">
-        <v>7044272</v>
+        <v>7044053</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +776,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,48 +817,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129303162</v>
+        <v>129293037</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>98577</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>219795</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524071</v>
+        <v>524020</v>
       </c>
       <c r="R3" t="n">
-        <v>7044020</v>
+        <v>7044025</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,11 +899,21 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -863,26 +922,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129303134</v>
+        <v>129303207</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +954,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523912</v>
+        <v>523916</v>
       </c>
       <c r="R4" t="n">
-        <v>7044281</v>
+        <v>7044193</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,11 +1014,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129303106</v>
+        <v>129303197</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +1051,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524060</v>
+        <v>524192</v>
       </c>
       <c r="R5" t="n">
-        <v>7043917</v>
+        <v>7043748</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,11 +1111,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129294077</v>
+        <v>129303201</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,42 +1148,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523957</v>
+        <v>524232</v>
       </c>
       <c r="R6" t="n">
-        <v>7044053</v>
+        <v>7043959</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,26 +1205,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1184,103 +1218,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129293037</v>
+        <v>129287650</v>
       </c>
       <c r="B7" t="n">
-        <v>98577</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219795</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524020</v>
+        <v>523970</v>
       </c>
       <c r="R7" t="n">
-        <v>7044025</v>
+        <v>7044272</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,11 +1325,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1351,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129303207</v>
+        <v>129303162</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,21 +1352,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1386,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523916</v>
+        <v>524071</v>
       </c>
       <c r="R8" t="n">
-        <v>7044193</v>
+        <v>7044020</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129303197</v>
+        <v>129303134</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524192</v>
+        <v>523912</v>
       </c>
       <c r="R9" t="n">
-        <v>7043748</v>
+        <v>7044281</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,6 +1509,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129303201</v>
+        <v>129303106</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,21 +1551,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524232</v>
+        <v>524060</v>
       </c>
       <c r="R10" t="n">
-        <v>7043959</v>
+        <v>7043917</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,6 +1611,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2340,48 +2340,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129294284</v>
+        <v>129303149</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>92480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524055</v>
+        <v>523933</v>
       </c>
       <c r="R17" t="n">
-        <v>7043952</v>
+        <v>7044287</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2408,21 +2408,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2431,28 +2421,23 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129292345</v>
+        <v>129303199</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2483,14 +2468,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524220</v>
+        <v>524280</v>
       </c>
       <c r="R18" t="n">
-        <v>7043956</v>
+        <v>7043899</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,26 +2505,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2548,48 +2518,23 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129289415</v>
+        <v>129303198</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2620,17 +2565,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524038</v>
+        <v>524207</v>
       </c>
       <c r="R19" t="n">
-        <v>7044201</v>
+        <v>7043773</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2657,19 +2602,9 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,22 +2619,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129286516</v>
+        <v>129303164</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>80146</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,53 +2642,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523928</v>
+        <v>523921</v>
       </c>
       <c r="R20" t="n">
-        <v>7044231</v>
+        <v>7044287</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2783,26 +2699,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst 2 livliga talltitor i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2811,74 +2712,80 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129294979</v>
+        <v>129303183</v>
       </c>
       <c r="B21" t="n">
-        <v>98595</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524252</v>
+        <v>524194</v>
       </c>
       <c r="R21" t="n">
-        <v>7043871</v>
+        <v>7043977</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2905,19 +2812,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:53</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,71 +2828,72 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129303099</v>
+        <v>129294979</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>98595</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524298</v>
+        <v>524252</v>
       </c>
       <c r="R22" t="n">
-        <v>7043861</v>
+        <v>7043871</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3017,14 +2920,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,48 +2943,53 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129303149</v>
+        <v>129303099</v>
       </c>
       <c r="B23" t="n">
-        <v>92480</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3086,10 +2999,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523933</v>
+        <v>524298</v>
       </c>
       <c r="R23" t="n">
-        <v>7044287</v>
+        <v>7043861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,6 +3035,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,10 +3066,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129303199</v>
+        <v>129286516</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,34 +3077,53 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524280</v>
+        <v>523928</v>
       </c>
       <c r="R24" t="n">
-        <v>7043899</v>
+        <v>7044231</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3216,11 +3153,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minst 2 livliga talltitor i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3229,23 +3181,28 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129303198</v>
+        <v>129294284</v>
       </c>
       <c r="B25" t="n">
         <v>79041</v>
@@ -3276,17 +3233,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524207</v>
+        <v>524055</v>
       </c>
       <c r="R25" t="n">
-        <v>7043773</v>
+        <v>7043952</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3313,11 +3270,21 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3326,26 +3293,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129303164</v>
+        <v>129292345</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,34 +3325,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523921</v>
+        <v>524220</v>
       </c>
       <c r="R26" t="n">
-        <v>7044287</v>
+        <v>7043956</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3410,11 +3382,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3423,80 +3410,89 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129303183</v>
+        <v>129289415</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524194</v>
+        <v>524038</v>
       </c>
       <c r="R27" t="n">
-        <v>7043977</v>
+        <v>7044201</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3523,14 +3519,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3539,19 +3540,18 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4720,50 +4720,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129286799</v>
+        <v>129303132</v>
       </c>
       <c r="B38" t="n">
-        <v>92480</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523936</v>
+        <v>523958</v>
       </c>
       <c r="R38" t="n">
-        <v>7044149</v>
+        <v>7044246</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4793,19 +4788,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:57</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2 Bohål ca 3 respektive 3,5 m upp i död gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4816,74 +4806,64 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129287712</v>
+        <v>129303120</v>
       </c>
       <c r="B39" t="n">
-        <v>92480</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523996</v>
+        <v>523983</v>
       </c>
       <c r="R39" t="n">
-        <v>7044263</v>
+        <v>7044011</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4910,24 +4890,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>I ett fuktstråk.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4938,31 +4908,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129303167</v>
+        <v>129303118</v>
       </c>
       <c r="B40" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4970,21 +4935,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4994,10 +4959,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523877</v>
+        <v>524000</v>
       </c>
       <c r="R40" t="n">
-        <v>7044241</v>
+        <v>7043995</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5030,6 +4995,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5056,45 +5026,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129303182</v>
+        <v>129286799</v>
       </c>
       <c r="B41" t="n">
-        <v>98678</v>
+        <v>92480</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524243</v>
+        <v>523936</v>
       </c>
       <c r="R41" t="n">
-        <v>7043957</v>
+        <v>7044149</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5124,11 +5099,21 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5137,64 +5122,74 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129303132</v>
+        <v>129287712</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>92480</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523958</v>
+        <v>523996</v>
       </c>
       <c r="R42" t="n">
-        <v>7044246</v>
+        <v>7044263</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5221,14 +5216,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>2 Bohål ca 3 respektive 3,5 m upp i död gran</t>
+          <t>I ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5239,26 +5244,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129303120</v>
+        <v>129303167</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5266,21 +5276,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5290,10 +5300,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523983</v>
+        <v>523877</v>
       </c>
       <c r="R43" t="n">
-        <v>7044011</v>
+        <v>7044241</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5326,11 +5336,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5357,32 +5362,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129303118</v>
+        <v>129303182</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5392,10 +5397,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524000</v>
+        <v>524243</v>
       </c>
       <c r="R44" t="n">
-        <v>7043995</v>
+        <v>7043957</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5428,11 +5433,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5459,38 +5459,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129292836</v>
+        <v>129290450</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>92480</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5499,13 +5499,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524162</v>
+        <v>524148</v>
       </c>
       <c r="R45" t="n">
-        <v>7043929</v>
+        <v>7044081</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5544,12 +5544,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5560,31 +5555,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5601,10 +5571,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129303206</v>
+        <v>129286184</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5612,37 +5582,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523867</v>
+        <v>523842</v>
       </c>
       <c r="R46" t="n">
-        <v>7044254</v>
+        <v>7044233</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5669,14 +5644,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5687,64 +5672,103 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129303177</v>
+        <v>129294365</v>
       </c>
       <c r="B47" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523950</v>
+        <v>524086</v>
       </c>
       <c r="R47" t="n">
-        <v>7044075</v>
+        <v>7043927</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5771,11 +5795,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 55 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5784,26 +5823,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129303155</v>
+        <v>129303124</v>
       </c>
       <c r="B48" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5811,21 +5855,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5835,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524032</v>
+        <v>523976</v>
       </c>
       <c r="R48" t="n">
-        <v>7044022</v>
+        <v>7044029</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5871,6 +5915,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5897,53 +5946,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129290450</v>
+        <v>129303129</v>
       </c>
       <c r="B49" t="n">
-        <v>92480</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524148</v>
+        <v>524088</v>
       </c>
       <c r="R49" t="n">
-        <v>7044081</v>
+        <v>7044015</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5970,19 +6014,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:51</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5997,19 +6036,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129286184</v>
+        <v>129292836</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -6049,13 +6088,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523842</v>
+        <v>524162</v>
       </c>
       <c r="R50" t="n">
-        <v>7044233</v>
+        <v>7043929</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6084,7 +6123,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6094,12 +6133,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6113,7 +6152,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6151,62 +6190,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129294365</v>
+        <v>129303206</v>
       </c>
       <c r="B51" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524086</v>
+        <v>523867</v>
       </c>
       <c r="R51" t="n">
-        <v>7043927</v>
+        <v>7044254</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6233,24 +6258,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 55 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6261,31 +6276,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129303124</v>
+        <v>129303177</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6293,21 +6303,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6317,10 +6327,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523976</v>
+        <v>523950</v>
       </c>
       <c r="R52" t="n">
-        <v>7044029</v>
+        <v>7044075</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6353,11 +6363,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6384,10 +6389,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129303129</v>
+        <v>129303155</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6395,21 +6400,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6419,10 +6424,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524088</v>
+        <v>524032</v>
       </c>
       <c r="R53" t="n">
-        <v>7044015</v>
+        <v>7044022</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6455,11 +6460,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6486,10 +6486,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129286739</v>
+        <v>129290167</v>
       </c>
       <c r="B54" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6497,27 +6497,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6526,13 +6526,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523903</v>
+        <v>524109</v>
       </c>
       <c r="R54" t="n">
-        <v>7044152</v>
+        <v>7044093</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6571,7 +6571,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6590,22 +6595,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6623,10 +6628,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129303136</v>
+        <v>129303080</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6634,21 +6639,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6658,10 +6663,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523897</v>
+        <v>523920</v>
       </c>
       <c r="R55" t="n">
-        <v>7044281</v>
+        <v>7044284</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6694,11 +6699,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6725,10 +6725,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129303135</v>
+        <v>129303159</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523902</v>
+        <v>524095</v>
       </c>
       <c r="R56" t="n">
-        <v>7044288</v>
+        <v>7044035</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6796,11 +6796,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6827,7 +6822,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129303111</v>
+        <v>129303136</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -6862,10 +6857,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524047</v>
+        <v>523897</v>
       </c>
       <c r="R57" t="n">
-        <v>7043931</v>
+        <v>7044281</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6929,10 +6924,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129303080</v>
+        <v>129303135</v>
       </c>
       <c r="B58" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6940,21 +6935,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6964,10 +6959,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523920</v>
+        <v>523902</v>
       </c>
       <c r="R58" t="n">
-        <v>7044284</v>
+        <v>7044288</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7000,6 +6995,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7026,7 +7026,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129290167</v>
+        <v>129303111</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -7055,21 +7055,16 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524109</v>
+        <v>524047</v>
       </c>
       <c r="R59" t="n">
-        <v>7044093</v>
+        <v>7043931</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7099,24 +7094,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7127,86 +7112,77 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129303159</v>
+        <v>129303187</v>
       </c>
       <c r="B60" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524095</v>
+        <v>524099</v>
       </c>
       <c r="R60" t="n">
-        <v>7044035</v>
+        <v>7044032</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7241,12 +7217,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7265,64 +7247,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129303187</v>
+        <v>129286739</v>
       </c>
       <c r="B61" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524099</v>
+        <v>523903</v>
       </c>
       <c r="R61" t="n">
-        <v>7044032</v>
+        <v>7044152</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7349,14 +7320,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7365,19 +7341,43 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -9498,10 +9498,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129295640</v>
+        <v>129295984</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9509,37 +9509,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524194</v>
+        <v>524244</v>
       </c>
       <c r="R80" t="n">
-        <v>7043776</v>
+        <v>7043732</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9568,7 +9573,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9578,7 +9583,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gränsen till färska.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9607,12 +9617,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9630,10 +9640,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129295781</v>
+        <v>129294143</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9641,42 +9651,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524196</v>
+        <v>523985</v>
       </c>
       <c r="R81" t="n">
-        <v>7043740</v>
+        <v>7044028</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9705,7 +9715,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9715,12 +9725,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar. Med fertila.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9749,12 +9759,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9772,64 +9782,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129291435</v>
+        <v>129303195</v>
       </c>
       <c r="B82" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524168</v>
+        <v>524202</v>
       </c>
       <c r="R82" t="n">
-        <v>7044018</v>
+        <v>7043730</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9859,24 +9850,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Minst 70 plantor inom ca 3 m2 yta.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9887,66 +9868,77 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129303092</v>
+        <v>129303186</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524227</v>
+        <v>524137</v>
       </c>
       <c r="R83" t="n">
-        <v>7043799</v>
+        <v>7043990</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9983,7 +9975,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9992,6 +9984,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10010,10 +10003,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129303148</v>
+        <v>129295640</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10021,37 +10014,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523952</v>
+        <v>524194</v>
       </c>
       <c r="R84" t="n">
-        <v>7044072</v>
+        <v>7043776</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10078,14 +10071,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10096,26 +10094,51 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129303098</v>
+        <v>129295781</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10123,34 +10146,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524297</v>
+        <v>524196</v>
       </c>
       <c r="R85" t="n">
-        <v>7043866</v>
+        <v>7043740</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10180,14 +10208,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på flera granar. Med fertila.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10198,61 +10236,105 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129303093</v>
+        <v>129291435</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524246</v>
+        <v>524168</v>
       </c>
       <c r="R86" t="n">
-        <v>7043787</v>
+        <v>7044018</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10282,14 +10364,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Minst 70 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10300,26 +10392,31 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129303195</v>
+        <v>129303092</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10327,21 +10424,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10351,10 +10448,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524202</v>
+        <v>524227</v>
       </c>
       <c r="R87" t="n">
-        <v>7043730</v>
+        <v>7043799</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10391,7 +10488,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10418,61 +10515,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129303186</v>
+        <v>129303148</v>
       </c>
       <c r="B88" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524137</v>
+        <v>523952</v>
       </c>
       <c r="R88" t="n">
-        <v>7043990</v>
+        <v>7044072</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10509,7 +10590,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10518,7 +10599,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10537,7 +10617,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129295984</v>
+        <v>129303098</v>
       </c>
       <c r="B89" t="n">
         <v>57727</v>
@@ -10566,21 +10646,16 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524244</v>
+        <v>524297</v>
       </c>
       <c r="R89" t="n">
-        <v>7043732</v>
+        <v>7043866</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10610,24 +10685,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10638,48 +10703,23 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129294143</v>
+        <v>129303093</v>
       </c>
       <c r="B90" t="n">
         <v>57727</v>
@@ -10708,24 +10748,19 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523985</v>
+        <v>524246</v>
       </c>
       <c r="R90" t="n">
-        <v>7044028</v>
+        <v>7043787</v>
       </c>
       <c r="S90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10752,24 +10787,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10780,41 +10805,16 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -14899,53 +14899,48 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129290529</v>
+        <v>129303210</v>
       </c>
       <c r="B127" t="n">
-        <v>80146</v>
+        <v>100866</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>524152</v>
+        <v>523999</v>
       </c>
       <c r="R127" t="n">
-        <v>7044077</v>
+        <v>7043998</v>
       </c>
       <c r="S127" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14972,26 +14967,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Fertil lunglav.</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -15000,51 +14980,26 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129303094</v>
+        <v>129290529</v>
       </c>
       <c r="B128" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15052,37 +15007,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>524244</v>
+        <v>524152</v>
       </c>
       <c r="R128" t="n">
-        <v>7043795</v>
+        <v>7044077</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15109,14 +15069,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Fertil lunglav.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15127,23 +15097,48 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129303117</v>
+        <v>129303094</v>
       </c>
       <c r="B129" t="n">
         <v>57727</v>
@@ -15178,10 +15173,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524002</v>
+        <v>524244</v>
       </c>
       <c r="R129" t="n">
-        <v>7043990</v>
+        <v>7043795</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15218,7 +15213,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15245,7 +15240,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129303101</v>
+        <v>129303117</v>
       </c>
       <c r="B130" t="n">
         <v>57727</v>
@@ -15280,10 +15275,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524169</v>
+        <v>524002</v>
       </c>
       <c r="R130" t="n">
-        <v>7043927</v>
+        <v>7043990</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15320,7 +15315,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15347,7 +15342,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129303125</v>
+        <v>129303101</v>
       </c>
       <c r="B131" t="n">
         <v>57727</v>
@@ -15382,10 +15377,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>523973</v>
+        <v>524169</v>
       </c>
       <c r="R131" t="n">
-        <v>7044031</v>
+        <v>7043927</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15449,10 +15444,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129303157</v>
+        <v>129303125</v>
       </c>
       <c r="B132" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15460,21 +15455,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15484,10 +15479,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524023</v>
+        <v>523973</v>
       </c>
       <c r="R132" t="n">
-        <v>7044002</v>
+        <v>7044031</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15520,6 +15515,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15546,7 +15546,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129303176</v>
+        <v>129303157</v>
       </c>
       <c r="B133" t="n">
         <v>80146</v>
@@ -15581,10 +15581,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>523949</v>
+        <v>524023</v>
       </c>
       <c r="R133" t="n">
-        <v>7044082</v>
+        <v>7044002</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15643,61 +15643,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129303194</v>
+        <v>129303176</v>
       </c>
       <c r="B134" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524066</v>
+        <v>523949</v>
       </c>
       <c r="R134" t="n">
-        <v>7044087</v>
+        <v>7044082</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15732,18 +15716,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
-        </is>
-      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -15762,7 +15740,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129303189</v>
+        <v>129303194</v>
       </c>
       <c r="B135" t="n">
         <v>98678</v>
@@ -15790,17 +15768,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524054</v>
+        <v>524066</v>
       </c>
       <c r="R135" t="n">
-        <v>7044027</v>
+        <v>7044087</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15835,12 +15829,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -15859,32 +15859,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129303210</v>
+        <v>129303189</v>
       </c>
       <c r="B136" t="n">
-        <v>100866</v>
+        <v>98678</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15894,10 +15894,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>523999</v>
+        <v>524054</v>
       </c>
       <c r="R136" t="n">
-        <v>7043998</v>
+        <v>7044027</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16063,67 +16063,53 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129296451</v>
+        <v>129292744</v>
       </c>
       <c r="B138" t="n">
-        <v>98678</v>
+        <v>92480</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>524225</v>
+        <v>524257</v>
       </c>
       <c r="R138" t="n">
-        <v>7043763</v>
+        <v>7043942</v>
       </c>
       <c r="S138" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16152,7 +16138,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16162,12 +16148,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor och 2 fröställningar inom ca 0,5 m2 yta i gammal granskog.</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16178,11 +16159,6 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
@@ -16199,7 +16175,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129294820</v>
+        <v>129303191</v>
       </c>
       <c r="B139" t="n">
         <v>98678</v>
@@ -16229,7 +16205,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -16237,21 +16213,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>524171</v>
+        <v>524076</v>
       </c>
       <c r="R139" t="n">
-        <v>7043952</v>
+        <v>7044084</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16281,24 +16259,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Minst 25 plantor och 5 fröställningar inom ca 1 m2 yta.</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16307,30 +16275,26 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129290074</v>
+        <v>129296451</v>
       </c>
       <c r="B140" t="n">
         <v>98678</v>
@@ -16360,7 +16324,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -16370,22 +16334,27 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>524078</v>
+        <v>524225</v>
       </c>
       <c r="R140" t="n">
-        <v>7044092</v>
+        <v>7043763</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16414,7 +16383,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16424,12 +16393,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 1 m2 yta</t>
+          <t>Minst 40 plantor och 2 fröställningar inom ca 0,5 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16443,7 +16412,7 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16461,45 +16430,59 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129303130</v>
+        <v>129294820</v>
       </c>
       <c r="B141" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>524087</v>
+        <v>524171</v>
       </c>
       <c r="R141" t="n">
-        <v>7044036</v>
+        <v>7043952</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16529,14 +16512,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 25 plantor och 5 fröställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16547,61 +16540,80 @@
       </c>
       <c r="AG141" t="b">
         <v>0</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129303104</v>
+        <v>129290074</v>
       </c>
       <c r="B142" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>524081</v>
+        <v>524078</v>
       </c>
       <c r="R142" t="n">
-        <v>7043892</v>
+        <v>7044092</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16631,14 +16643,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 20 plantor inom ca 1 m2 yta</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16649,26 +16671,31 @@
       </c>
       <c r="AG142" t="b">
         <v>0</v>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129303113</v>
+        <v>129303204</v>
       </c>
       <c r="B143" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16676,21 +16703,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16700,10 +16727,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>524042</v>
+        <v>524128</v>
       </c>
       <c r="R143" t="n">
-        <v>7043944</v>
+        <v>7044050</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16740,7 +16767,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16767,10 +16794,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129303109</v>
+        <v>129303174</v>
       </c>
       <c r="B144" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16778,21 +16805,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16802,10 +16829,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>524053</v>
+        <v>523897</v>
       </c>
       <c r="R144" t="n">
-        <v>7043923</v>
+        <v>7044154</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16838,11 +16865,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16869,7 +16891,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129303105</v>
+        <v>129303130</v>
       </c>
       <c r="B145" t="n">
         <v>57727</v>
@@ -16904,10 +16926,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>524079</v>
+        <v>524087</v>
       </c>
       <c r="R145" t="n">
-        <v>7043891</v>
+        <v>7044036</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16944,7 +16966,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16971,61 +16993,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129303191</v>
+        <v>129303104</v>
       </c>
       <c r="B146" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>524076</v>
+        <v>524081</v>
       </c>
       <c r="R146" t="n">
-        <v>7044084</v>
+        <v>7043892</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17062,7 +17068,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17071,7 +17077,6 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -17090,10 +17095,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129303204</v>
+        <v>129303113</v>
       </c>
       <c r="B147" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17101,21 +17106,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17125,10 +17130,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>524128</v>
+        <v>524042</v>
       </c>
       <c r="R147" t="n">
-        <v>7044050</v>
+        <v>7043944</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17165,7 +17170,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17192,10 +17197,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129303174</v>
+        <v>129303142</v>
       </c>
       <c r="B148" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17203,21 +17208,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17227,10 +17232,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>523897</v>
+        <v>523900</v>
       </c>
       <c r="R148" t="n">
-        <v>7044154</v>
+        <v>7044204</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17263,6 +17268,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17289,7 +17299,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129303142</v>
+        <v>129303109</v>
       </c>
       <c r="B149" t="n">
         <v>57727</v>
@@ -17324,10 +17334,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>523900</v>
+        <v>524053</v>
       </c>
       <c r="R149" t="n">
-        <v>7044204</v>
+        <v>7043923</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17391,50 +17401,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129292744</v>
+        <v>129303105</v>
       </c>
       <c r="B150" t="n">
-        <v>92480</v>
+        <v>57727</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>524257</v>
+        <v>524079</v>
       </c>
       <c r="R150" t="n">
-        <v>7043942</v>
+        <v>7043891</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17464,19 +17469,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>12:41</t>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17491,74 +17491,65 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129295438</v>
+        <v>129287611</v>
       </c>
       <c r="B151" t="n">
-        <v>98678</v>
+        <v>92480</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>524215</v>
+        <v>523944</v>
       </c>
       <c r="R151" t="n">
-        <v>7043793</v>
+        <v>7044196</v>
       </c>
       <c r="S151" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17587,7 +17578,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17597,12 +17588,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 3 m2 yta intill en ringhackad gran.</t>
+          <t>Vid ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17634,52 +17625,38 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129294021</v>
+        <v>129294247</v>
       </c>
       <c r="B152" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -17688,13 +17665,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>523995</v>
+        <v>524031</v>
       </c>
       <c r="R152" t="n">
-        <v>7044066</v>
+        <v>7043970</v>
       </c>
       <c r="S152" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17723,7 +17700,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17733,12 +17710,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Minst 50 plantor inom ca 8 m2 yta.</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17752,7 +17724,27 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -17770,10 +17762,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129303100</v>
+        <v>129295347</v>
       </c>
       <c r="B153" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17781,37 +17773,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>524235</v>
+        <v>524217</v>
       </c>
       <c r="R153" t="n">
-        <v>7043960</v>
+        <v>7043807</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17838,14 +17830,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17860,22 +17857,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129303143</v>
+        <v>129294611</v>
       </c>
       <c r="B154" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17883,37 +17880,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>523911</v>
+        <v>524157</v>
       </c>
       <c r="R154" t="n">
-        <v>7044178</v>
+        <v>7043937</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17940,14 +17937,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17958,26 +17960,51 @@
       </c>
       <c r="AG154" t="b">
         <v>0</v>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129303112</v>
+        <v>129303154</v>
       </c>
       <c r="B155" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17985,21 +18012,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18009,10 +18036,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>524044</v>
+        <v>523989</v>
       </c>
       <c r="R155" t="n">
-        <v>7043935</v>
+        <v>7044014</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18045,11 +18072,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18076,10 +18098,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129303116</v>
+        <v>129303173</v>
       </c>
       <c r="B156" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18087,21 +18109,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -18111,10 +18133,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>524033</v>
+        <v>523917</v>
       </c>
       <c r="R156" t="n">
-        <v>7043952</v>
+        <v>7044208</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18147,11 +18169,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18178,10 +18195,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129303138</v>
+        <v>129303171</v>
       </c>
       <c r="B157" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18189,21 +18206,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18213,10 +18230,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>523879</v>
+        <v>523890</v>
       </c>
       <c r="R157" t="n">
-        <v>7044256</v>
+        <v>7044215</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18249,11 +18266,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18280,10 +18292,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129303131</v>
+        <v>129303205</v>
       </c>
       <c r="B158" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18291,21 +18303,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18315,10 +18327,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>524059</v>
+        <v>523935</v>
       </c>
       <c r="R158" t="n">
-        <v>7044016</v>
+        <v>7044292</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18355,7 +18367,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18382,7 +18394,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129303128</v>
+        <v>129294096</v>
       </c>
       <c r="B159" t="n">
         <v>57727</v>
@@ -18411,19 +18423,24 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>524186</v>
+        <v>523971</v>
       </c>
       <c r="R159" t="n">
-        <v>7043943</v>
+        <v>7044037</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18450,14 +18467,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18468,69 +18495,103 @@
       </c>
       <c r="AG159" t="b">
         <v>0</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129287611</v>
+        <v>129295438</v>
       </c>
       <c r="B160" t="n">
-        <v>92480</v>
+        <v>98678</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>523944</v>
+        <v>524215</v>
       </c>
       <c r="R160" t="n">
-        <v>7044196</v>
+        <v>7043793</v>
       </c>
       <c r="S160" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18559,7 +18620,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18569,12 +18630,12 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Vid ett fuktstråk.</t>
+          <t>Minst 40 plantor inom ca 3 m2 yta intill en ringhackad gran.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18606,38 +18667,52 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129294247</v>
+        <v>129294021</v>
       </c>
       <c r="B161" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18646,13 +18721,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>524031</v>
+        <v>523995</v>
       </c>
       <c r="R161" t="n">
-        <v>7043970</v>
+        <v>7044066</v>
       </c>
       <c r="S161" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18681,7 +18756,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18691,7 +18766,12 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Minst 50 plantor inom ca 8 m2 yta.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18705,27 +18785,7 @@
       </c>
       <c r="AH161" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
@@ -18743,10 +18803,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129295347</v>
+        <v>129303100</v>
       </c>
       <c r="B162" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18754,37 +18814,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>524217</v>
+        <v>524235</v>
       </c>
       <c r="R162" t="n">
-        <v>7043807</v>
+        <v>7043960</v>
       </c>
       <c r="S162" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18811,19 +18871,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>15:15</t>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18838,22 +18893,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129294611</v>
+        <v>129303143</v>
       </c>
       <c r="B163" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18861,37 +18916,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>524157</v>
+        <v>523911</v>
       </c>
       <c r="R163" t="n">
-        <v>7043937</v>
+        <v>7044178</v>
       </c>
       <c r="S163" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18918,19 +18973,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>14:38</t>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18941,48 +18991,23 @@
       </c>
       <c r="AG163" t="b">
         <v>0</v>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM163" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129294096</v>
+        <v>129303138</v>
       </c>
       <c r="B164" t="n">
         <v>57727</v>
@@ -19011,24 +19036,19 @@
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>523971</v>
+        <v>523879</v>
       </c>
       <c r="R164" t="n">
-        <v>7044037</v>
+        <v>7044256</v>
       </c>
       <c r="S164" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -19055,24 +19075,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19083,51 +19093,26 @@
       </c>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129303154</v>
+        <v>129303112</v>
       </c>
       <c r="B165" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19135,21 +19120,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -19159,10 +19144,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>523989</v>
+        <v>524044</v>
       </c>
       <c r="R165" t="n">
-        <v>7044014</v>
+        <v>7043935</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19195,6 +19180,11 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19221,10 +19211,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129303173</v>
+        <v>129303116</v>
       </c>
       <c r="B166" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19232,21 +19222,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19256,10 +19246,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>523917</v>
+        <v>524033</v>
       </c>
       <c r="R166" t="n">
-        <v>7044208</v>
+        <v>7043952</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19292,6 +19282,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19318,10 +19313,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303171</v>
+        <v>129303131</v>
       </c>
       <c r="B167" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19329,21 +19324,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -19353,10 +19348,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>523890</v>
+        <v>524059</v>
       </c>
       <c r="R167" t="n">
-        <v>7044215</v>
+        <v>7044016</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19389,6 +19384,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19415,10 +19415,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129303205</v>
+        <v>129303128</v>
       </c>
       <c r="B168" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19426,21 +19426,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>523935</v>
+        <v>524186</v>
       </c>
       <c r="R168" t="n">
-        <v>7044292</v>
+        <v>7043943</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19490,7 +19490,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -22564,6 +22564,107 @@
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>129376007</v>
+      </c>
+      <c r="B195" t="n">
+        <v>91902</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>sögsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>524025</v>
+      </c>
+      <c r="R195" t="n">
+        <v>7044176</v>
+      </c>
+      <c r="S195" t="n">
+        <v>10</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -1642,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129295161</v>
+        <v>129289927</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>80148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,37 +1653,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524240</v>
+        <v>524085</v>
       </c>
       <c r="R11" t="n">
-        <v>7043842</v>
+        <v>7044128</v>
       </c>
       <c r="S11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1712,7 +1717,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1722,7 +1727,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,6 +1743,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1749,38 +1784,52 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129289927</v>
+        <v>129291542</v>
       </c>
       <c r="B12" t="n">
-        <v>80148</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1789,13 +1838,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524085</v>
+        <v>524169</v>
       </c>
       <c r="R12" t="n">
-        <v>7044128</v>
+        <v>7044012</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1834,12 +1883,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en grov sälglåga.</t>
+          <t>Minst 130 plantor i grupper inom ca 8 m2 yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1853,27 +1902,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1891,67 +1920,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129291542</v>
+        <v>129303165</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>80148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524169</v>
+        <v>523906</v>
       </c>
       <c r="R13" t="n">
-        <v>7044012</v>
+        <v>7044257</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1978,26 +1988,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 130 plantor i grupper inom ca 8 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2006,28 +2001,23 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129303165</v>
+        <v>129303169</v>
       </c>
       <c r="B14" t="n">
         <v>80148</v>
@@ -2062,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523906</v>
+        <v>523880</v>
       </c>
       <c r="R14" t="n">
-        <v>7044257</v>
+        <v>7044224</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,45 +2114,61 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129303169</v>
+        <v>129303181</v>
       </c>
       <c r="B15" t="n">
-        <v>80148</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523880</v>
+        <v>524277</v>
       </c>
       <c r="R15" t="n">
-        <v>7044224</v>
+        <v>7043850</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,12 +2203,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2221,64 +2233,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129303181</v>
+        <v>129295161</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524277</v>
+        <v>524240</v>
       </c>
       <c r="R16" t="n">
-        <v>7043850</v>
+        <v>7043842</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2305,14 +2301,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2321,26 +2322,25 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129294284</v>
+        <v>129303199</v>
       </c>
       <c r="B17" t="n">
         <v>79043</v>
@@ -2371,17 +2371,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524055</v>
+        <v>524280</v>
       </c>
       <c r="R17" t="n">
-        <v>7043952</v>
+        <v>7043899</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2408,21 +2408,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2431,31 +2421,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129292345</v>
+        <v>129303164</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>80148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,34 +2448,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524220</v>
+        <v>523921</v>
       </c>
       <c r="R18" t="n">
-        <v>7043956</v>
+        <v>7044287</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,26 +2505,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2548,48 +2518,23 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129289415</v>
+        <v>129303198</v>
       </c>
       <c r="B19" t="n">
         <v>79043</v>
@@ -2620,17 +2565,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524038</v>
+        <v>524207</v>
       </c>
       <c r="R19" t="n">
-        <v>7044201</v>
+        <v>7043773</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2657,19 +2602,9 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,22 +2619,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129286516</v>
+        <v>129294284</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,56 +2642,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523928</v>
+        <v>524055</v>
       </c>
       <c r="R20" t="n">
-        <v>7044231</v>
+        <v>7043952</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2785,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2795,12 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst 2 livliga talltitor i flerskiktad granskog.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2832,53 +2743,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129294979</v>
+        <v>129292345</v>
       </c>
       <c r="B21" t="n">
-        <v>98627</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524252</v>
+        <v>524220</v>
       </c>
       <c r="R21" t="n">
-        <v>7043871</v>
+        <v>7043956</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2907,7 +2813,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2917,7 +2823,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2932,6 +2843,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2949,48 +2880,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129303149</v>
+        <v>129289415</v>
       </c>
       <c r="B22" t="n">
-        <v>92498</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523933</v>
+        <v>524038</v>
       </c>
       <c r="R22" t="n">
-        <v>7044287</v>
+        <v>7044201</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3017,9 +2948,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3034,22 +2975,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129303199</v>
+        <v>129286516</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,34 +2998,53 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524280</v>
+        <v>523928</v>
       </c>
       <c r="R23" t="n">
-        <v>7043899</v>
+        <v>7044231</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3114,11 +3074,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 2 livliga talltitor i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3127,64 +3102,74 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129303164</v>
+        <v>129294979</v>
       </c>
       <c r="B24" t="n">
-        <v>80148</v>
+        <v>98627</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523921</v>
+        <v>524252</v>
       </c>
       <c r="R24" t="n">
-        <v>7044287</v>
+        <v>7043871</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3211,11 +3196,21 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3224,48 +3219,53 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129303198</v>
+        <v>129303149</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>92498</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524207</v>
+        <v>523933</v>
       </c>
       <c r="R25" t="n">
-        <v>7043773</v>
+        <v>7044287</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4588,50 +4588,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129286799</v>
+        <v>129289835</v>
       </c>
       <c r="B37" t="n">
-        <v>92498</v>
+        <v>80148</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523936</v>
+        <v>524087</v>
       </c>
       <c r="R37" t="n">
-        <v>7044149</v>
+        <v>7044152</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4663,7 +4658,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4673,7 +4668,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4687,7 +4682,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4705,7 +4720,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129287712</v>
+        <v>129286799</v>
       </c>
       <c r="B38" t="n">
         <v>92498</v>
@@ -4745,13 +4760,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523996</v>
+        <v>523936</v>
       </c>
       <c r="R38" t="n">
-        <v>7044263</v>
+        <v>7044149</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4780,7 +4795,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4790,12 +4805,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk.</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4827,48 +4837,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129289835</v>
+        <v>129287712</v>
       </c>
       <c r="B39" t="n">
-        <v>80148</v>
+        <v>92498</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524087</v>
+        <v>523996</v>
       </c>
       <c r="R39" t="n">
-        <v>7044152</v>
+        <v>7044263</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4897,7 +4912,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4907,7 +4922,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4921,27 +4941,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5571,38 +5571,47 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129286184</v>
+        <v>129294365</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5611,13 +5620,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523842</v>
+        <v>524086</v>
       </c>
       <c r="R46" t="n">
-        <v>7044233</v>
+        <v>7043927</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5646,7 +5655,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5656,12 +5665,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Minst 55 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5676,26 +5685,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5713,10 +5702,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129292836</v>
+        <v>129303177</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5724,42 +5713,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524162</v>
+        <v>523950</v>
       </c>
       <c r="R47" t="n">
-        <v>7043929</v>
+        <v>7044075</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5786,26 +5770,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5814,103 +5783,64 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129294365</v>
+        <v>129303155</v>
       </c>
       <c r="B48" t="n">
-        <v>98710</v>
+        <v>80148</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524086</v>
+        <v>524032</v>
       </c>
       <c r="R48" t="n">
-        <v>7043927</v>
+        <v>7044022</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5937,26 +5867,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 55 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5965,31 +5880,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129303177</v>
+        <v>129303206</v>
       </c>
       <c r="B49" t="n">
-        <v>80148</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5997,21 +5907,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6021,10 +5931,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523950</v>
+        <v>523867</v>
       </c>
       <c r="R49" t="n">
-        <v>7044075</v>
+        <v>7044254</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6057,6 +5967,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6083,10 +5998,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129303155</v>
+        <v>129286184</v>
       </c>
       <c r="B50" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6094,37 +6009,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524032</v>
+        <v>523842</v>
       </c>
       <c r="R50" t="n">
-        <v>7044022</v>
+        <v>7044233</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6151,11 +6071,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6164,26 +6099,51 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129303206</v>
+        <v>129292836</v>
       </c>
       <c r="B51" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6191,37 +6151,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523867</v>
+        <v>524162</v>
       </c>
       <c r="R51" t="n">
-        <v>7044254</v>
+        <v>7043929</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6248,14 +6213,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6266,16 +6241,41 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129303159</v>
+        <v>129303080</v>
       </c>
       <c r="B56" t="n">
-        <v>80148</v>
+        <v>91543</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6776,21 +6776,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6800,10 +6800,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524095</v>
+        <v>523920</v>
       </c>
       <c r="R56" t="n">
-        <v>7044035</v>
+        <v>7044284</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6862,10 +6862,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129303080</v>
+        <v>129303159</v>
       </c>
       <c r="B57" t="n">
-        <v>91543</v>
+        <v>80148</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6873,21 +6873,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6897,10 +6897,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523920</v>
+        <v>524095</v>
       </c>
       <c r="R57" t="n">
-        <v>7044284</v>
+        <v>7044035</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7384,10 +7384,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129295685</v>
+        <v>129295010</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7395,42 +7395,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524198</v>
+        <v>524277</v>
       </c>
       <c r="R62" t="n">
-        <v>7043758</v>
+        <v>7043865</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7459,7 +7454,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7469,12 +7464,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7503,12 +7493,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7952,10 +7942,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129303209</v>
+        <v>129294128</v>
       </c>
       <c r="B66" t="n">
-        <v>88943</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7963,34 +7953,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524049</v>
+        <v>523987</v>
       </c>
       <c r="R66" t="n">
-        <v>7044121</v>
+        <v>7044025</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8020,11 +8015,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8033,26 +8043,51 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129303163</v>
+        <v>129295685</v>
       </c>
       <c r="B67" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8060,34 +8095,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524055</v>
+        <v>524198</v>
       </c>
       <c r="R67" t="n">
-        <v>7044066</v>
+        <v>7043758</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8117,11 +8157,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8130,26 +8185,51 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129303166</v>
+        <v>129303209</v>
       </c>
       <c r="B68" t="n">
-        <v>80148</v>
+        <v>88943</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8157,21 +8237,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8181,10 +8261,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523872</v>
+        <v>524049</v>
       </c>
       <c r="R68" t="n">
-        <v>7044252</v>
+        <v>7044121</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8243,10 +8323,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129303133</v>
+        <v>129303163</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8254,21 +8334,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8278,10 +8358,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523992</v>
+        <v>524055</v>
       </c>
       <c r="R69" t="n">
-        <v>7044262</v>
+        <v>7044066</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8314,11 +8394,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8345,10 +8420,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129295010</v>
+        <v>129303166</v>
       </c>
       <c r="B70" t="n">
-        <v>79043</v>
+        <v>80148</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8356,37 +8431,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524277</v>
+        <v>523872</v>
       </c>
       <c r="R70" t="n">
-        <v>7043865</v>
+        <v>7044252</v>
       </c>
       <c r="S70" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8413,21 +8488,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8436,48 +8501,23 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129294128</v>
+        <v>129303081</v>
       </c>
       <c r="B71" t="n">
         <v>57727</v>
@@ -8506,21 +8546,16 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523987</v>
+        <v>524190</v>
       </c>
       <c r="R71" t="n">
-        <v>7044025</v>
+        <v>7043804</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8550,24 +8585,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8578,48 +8603,23 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129303081</v>
+        <v>129303121</v>
       </c>
       <c r="B72" t="n">
         <v>57727</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524190</v>
+        <v>523979</v>
       </c>
       <c r="R72" t="n">
-        <v>7043804</v>
+        <v>7044017</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8721,7 +8721,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129303121</v>
+        <v>129303087</v>
       </c>
       <c r="B73" t="n">
         <v>57727</v>
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523979</v>
+        <v>524219</v>
       </c>
       <c r="R73" t="n">
-        <v>7044017</v>
+        <v>7043705</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8823,7 +8823,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129303087</v>
+        <v>129303133</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524219</v>
+        <v>523992</v>
       </c>
       <c r="R74" t="n">
-        <v>7043705</v>
+        <v>7044262</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8925,32 +8925,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129303188</v>
+        <v>129303137</v>
       </c>
       <c r="B75" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8960,10 +8960,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524104</v>
+        <v>523890</v>
       </c>
       <c r="R75" t="n">
-        <v>7044042</v>
+        <v>7044274</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8996,6 +8996,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9396,32 +9401,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129303137</v>
+        <v>129303188</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9431,10 +9436,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523890</v>
+        <v>524104</v>
       </c>
       <c r="R79" t="n">
-        <v>7044274</v>
+        <v>7044042</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9467,11 +9472,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9498,52 +9498,38 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129291435</v>
+        <v>129294143</v>
       </c>
       <c r="B80" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9552,13 +9538,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524168</v>
+        <v>523985</v>
       </c>
       <c r="R80" t="n">
-        <v>7044018</v>
+        <v>7044028</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9587,7 +9573,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9597,12 +9583,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Minst 70 plantor inom ca 3 m2 yta.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9617,6 +9603,26 @@
       <c r="AH80" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9634,7 +9640,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129303186</v>
+        <v>129291435</v>
       </c>
       <c r="B81" t="n">
         <v>98710</v>
@@ -9664,7 +9670,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9672,8 +9678,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9681,14 +9690,14 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524137</v>
+        <v>524168</v>
       </c>
       <c r="R81" t="n">
-        <v>7043990</v>
+        <v>7044018</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9718,14 +9727,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Minst 70 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9734,19 +9753,23 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -10263,50 +10286,61 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129295984</v>
+        <v>129303186</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524244</v>
+        <v>524137</v>
       </c>
       <c r="R87" t="n">
-        <v>7043732</v>
+        <v>7043990</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10336,24 +10370,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska.</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10362,53 +10386,29 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129294143</v>
+        <v>129295640</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10416,42 +10416,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523985</v>
+        <v>524194</v>
       </c>
       <c r="R88" t="n">
-        <v>7044028</v>
+        <v>7043776</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10480,7 +10475,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10490,12 +10485,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10524,12 +10514,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10547,7 +10537,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129295640</v>
+        <v>129295781</v>
       </c>
       <c r="B89" t="n">
         <v>79043</v>
@@ -10576,19 +10566,24 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524194</v>
+        <v>524196</v>
       </c>
       <c r="R89" t="n">
-        <v>7043776</v>
+        <v>7043740</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10617,7 +10612,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10627,7 +10622,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Med fertila.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10679,10 +10679,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129295781</v>
+        <v>129295984</v>
       </c>
       <c r="B90" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10690,27 +10690,27 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10719,10 +10719,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>524196</v>
+        <v>524244</v>
       </c>
       <c r="R90" t="n">
-        <v>7043740</v>
+        <v>7043732</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar. Med fertila.</t>
+          <t>Ringhack, äldre, på gränsen till färska.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11704,10 +11704,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129290810</v>
+        <v>129303170</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11715,47 +11715,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>524168</v>
+        <v>523868</v>
       </c>
       <c r="R99" t="n">
-        <v>7044054</v>
+        <v>7044208</v>
       </c>
       <c r="S99" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11782,26 +11772,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -11810,51 +11785,26 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129294258</v>
+        <v>129303202</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11862,42 +11812,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>524049</v>
+        <v>524156</v>
       </c>
       <c r="R100" t="n">
-        <v>7043961</v>
+        <v>7043909</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11924,24 +11869,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11952,51 +11887,26 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129303170</v>
+        <v>129303090</v>
       </c>
       <c r="B101" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12004,21 +11914,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12028,10 +11938,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523868</v>
+        <v>524194</v>
       </c>
       <c r="R101" t="n">
-        <v>7044208</v>
+        <v>7043755</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12064,6 +11974,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12090,10 +12005,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129303202</v>
+        <v>129303123</v>
       </c>
       <c r="B102" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12101,21 +12016,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12125,10 +12040,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>524156</v>
+        <v>523980</v>
       </c>
       <c r="R102" t="n">
-        <v>7043909</v>
+        <v>7044026</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12165,7 +12080,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12192,7 +12107,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129303090</v>
+        <v>129303091</v>
       </c>
       <c r="B103" t="n">
         <v>57727</v>
@@ -12227,10 +12142,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>524194</v>
+        <v>524225</v>
       </c>
       <c r="R103" t="n">
-        <v>7043755</v>
+        <v>7043779</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12267,7 +12182,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12294,7 +12209,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129303123</v>
+        <v>129303139</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -12329,10 +12244,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523980</v>
+        <v>523860</v>
       </c>
       <c r="R104" t="n">
-        <v>7044026</v>
+        <v>7044250</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12369,7 +12284,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12396,7 +12311,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129303091</v>
+        <v>129303096</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -12431,10 +12346,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>524225</v>
+        <v>524226</v>
       </c>
       <c r="R105" t="n">
-        <v>7043779</v>
+        <v>7043829</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12498,7 +12413,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129303139</v>
+        <v>129303144</v>
       </c>
       <c r="B106" t="n">
         <v>57727</v>
@@ -12533,10 +12448,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523860</v>
+        <v>523900</v>
       </c>
       <c r="R106" t="n">
-        <v>7044250</v>
+        <v>7044174</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12573,7 +12488,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12600,32 +12515,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129303096</v>
+        <v>129303208</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>92138</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12635,10 +12550,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>524226</v>
+        <v>524022</v>
       </c>
       <c r="R107" t="n">
-        <v>7043829</v>
+        <v>7044005</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12675,7 +12590,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På fälld sälg</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12702,7 +12617,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129303144</v>
+        <v>129290810</v>
       </c>
       <c r="B108" t="n">
         <v>57727</v>
@@ -12731,19 +12646,29 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>523900</v>
+        <v>524168</v>
       </c>
       <c r="R108" t="n">
-        <v>7044174</v>
+        <v>7044054</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12770,14 +12695,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12788,64 +12723,94 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129303208</v>
+        <v>129294258</v>
       </c>
       <c r="B109" t="n">
-        <v>92138</v>
+        <v>57727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>524022</v>
+        <v>524049</v>
       </c>
       <c r="R109" t="n">
-        <v>7044005</v>
+        <v>7043961</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12872,14 +12837,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>På fälld sälg</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12890,16 +12865,41 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -13179,48 +13179,62 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129303110</v>
+        <v>129293149</v>
       </c>
       <c r="B112" t="n">
-        <v>57727</v>
+        <v>98609</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>219795</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524053</v>
+        <v>524014</v>
       </c>
       <c r="R112" t="n">
-        <v>7043929</v>
+        <v>7044008</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13247,14 +13261,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Växer intill en gammal lunglavssälg vid en göl.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13265,78 +13289,69 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129293149</v>
+        <v>129303168</v>
       </c>
       <c r="B113" t="n">
-        <v>98609</v>
+        <v>80148</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219795</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>524014</v>
+        <v>523894</v>
       </c>
       <c r="R113" t="n">
-        <v>7044008</v>
+        <v>7044235</v>
       </c>
       <c r="S113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13363,26 +13378,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Växer intill en gammal lunglavssälg vid en göl.</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -13391,31 +13391,26 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129303168</v>
+        <v>129303122</v>
       </c>
       <c r="B114" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13423,21 +13418,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13447,10 +13442,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>523894</v>
+        <v>523976</v>
       </c>
       <c r="R114" t="n">
-        <v>7044235</v>
+        <v>7044021</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13483,6 +13478,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13509,7 +13509,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129303122</v>
+        <v>129303145</v>
       </c>
       <c r="B115" t="n">
         <v>57727</v>
@@ -13544,10 +13544,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>523976</v>
+        <v>523898</v>
       </c>
       <c r="R115" t="n">
-        <v>7044021</v>
+        <v>7044169</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13611,45 +13611,61 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129303145</v>
+        <v>129303184</v>
       </c>
       <c r="B116" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>523898</v>
+        <v>524159</v>
       </c>
       <c r="R116" t="n">
-        <v>7044169</v>
+        <v>7043990</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13686,7 +13702,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13695,6 +13711,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13713,61 +13730,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129303184</v>
+        <v>129303110</v>
       </c>
       <c r="B117" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524159</v>
+        <v>524053</v>
       </c>
       <c r="R117" t="n">
-        <v>7043990</v>
+        <v>7043929</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13804,7 +13805,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13813,7 +13814,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -14377,10 +14377,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129290684</v>
+        <v>129290529</v>
       </c>
       <c r="B123" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14388,32 +14388,27 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14422,10 +14417,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>524150</v>
+        <v>524152</v>
       </c>
       <c r="R123" t="n">
-        <v>7044038</v>
+        <v>7044077</v>
       </c>
       <c r="S123" t="n">
         <v>12</v>
@@ -14457,7 +14452,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14467,12 +14462,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
+          <t>Fertil lunglav.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14486,27 +14481,27 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -14524,7 +14519,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129295476</v>
+        <v>129290684</v>
       </c>
       <c r="B124" t="n">
         <v>57727</v>
@@ -14555,7 +14550,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -14565,14 +14560,14 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524222</v>
+        <v>524150</v>
       </c>
       <c r="R124" t="n">
-        <v>7043799</v>
+        <v>7044038</v>
       </c>
       <c r="S124" t="n">
         <v>12</v>
@@ -14604,7 +14599,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14614,12 +14609,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14671,10 +14666,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129303160</v>
+        <v>129295476</v>
       </c>
       <c r="B125" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14682,37 +14677,47 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>524077</v>
+        <v>524222</v>
       </c>
       <c r="R125" t="n">
-        <v>7044028</v>
+        <v>7043799</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14739,11 +14744,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -14752,23 +14772,48 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129303176</v>
+        <v>129303157</v>
       </c>
       <c r="B126" t="n">
         <v>80148</v>
@@ -14803,10 +14848,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523949</v>
+        <v>524023</v>
       </c>
       <c r="R126" t="n">
-        <v>7044082</v>
+        <v>7044002</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14865,59 +14910,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129294458</v>
+        <v>129303160</v>
       </c>
       <c r="B127" t="n">
-        <v>98710</v>
+        <v>80148</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>524123</v>
+        <v>524077</v>
       </c>
       <c r="R127" t="n">
-        <v>7043951</v>
+        <v>7044028</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14947,26 +14978,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Minst 26 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -14975,28 +14991,23 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129290529</v>
+        <v>129303176</v>
       </c>
       <c r="B128" t="n">
         <v>80148</v>
@@ -15025,24 +15036,19 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>524152</v>
+        <v>523949</v>
       </c>
       <c r="R128" t="n">
-        <v>7044077</v>
+        <v>7044082</v>
       </c>
       <c r="S128" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15069,26 +15075,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Fertil lunglav.</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -15097,51 +15088,26 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129303157</v>
+        <v>129303094</v>
       </c>
       <c r="B129" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15149,21 +15115,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15173,10 +15139,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524023</v>
+        <v>524244</v>
       </c>
       <c r="R129" t="n">
-        <v>7044002</v>
+        <v>7043795</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15209,6 +15175,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15235,7 +15206,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129303094</v>
+        <v>129303117</v>
       </c>
       <c r="B130" t="n">
         <v>57727</v>
@@ -15270,10 +15241,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524244</v>
+        <v>524002</v>
       </c>
       <c r="R130" t="n">
-        <v>7043795</v>
+        <v>7043990</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15310,7 +15281,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15337,7 +15308,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129303117</v>
+        <v>129303101</v>
       </c>
       <c r="B131" t="n">
         <v>57727</v>
@@ -15372,10 +15343,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>524002</v>
+        <v>524169</v>
       </c>
       <c r="R131" t="n">
-        <v>7043990</v>
+        <v>7043927</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15412,7 +15383,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15439,7 +15410,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129303101</v>
+        <v>129303125</v>
       </c>
       <c r="B132" t="n">
         <v>57727</v>
@@ -15474,10 +15445,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524169</v>
+        <v>523973</v>
       </c>
       <c r="R132" t="n">
-        <v>7043927</v>
+        <v>7044031</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15541,45 +15512,61 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129303125</v>
+        <v>129303194</v>
       </c>
       <c r="B133" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>523973</v>
+        <v>524066</v>
       </c>
       <c r="R133" t="n">
-        <v>7044031</v>
+        <v>7044087</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15616,7 +15603,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15625,6 +15612,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -15643,32 +15631,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129303210</v>
+        <v>129303189</v>
       </c>
       <c r="B134" t="n">
-        <v>100899</v>
+        <v>98710</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15678,10 +15666,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>523999</v>
+        <v>524054</v>
       </c>
       <c r="R134" t="n">
-        <v>7043998</v>
+        <v>7044027</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15740,61 +15728,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129303194</v>
+        <v>129303210</v>
       </c>
       <c r="B135" t="n">
-        <v>98710</v>
+        <v>100899</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524066</v>
+        <v>523999</v>
       </c>
       <c r="R135" t="n">
-        <v>7044087</v>
+        <v>7043998</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15829,18 +15801,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -15859,7 +15825,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129303189</v>
+        <v>129294458</v>
       </c>
       <c r="B136" t="n">
         <v>98710</v>
@@ -15887,17 +15853,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>524054</v>
+        <v>524123</v>
       </c>
       <c r="R136" t="n">
-        <v>7044027</v>
+        <v>7043951</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15927,11 +15907,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Minst 26 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -15940,16 +15935,21 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -18001,52 +18001,38 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129294021</v>
+        <v>129294096</v>
       </c>
       <c r="B155" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -18055,10 +18041,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>523995</v>
+        <v>523971</v>
       </c>
       <c r="R155" t="n">
-        <v>7044066</v>
+        <v>7044037</v>
       </c>
       <c r="S155" t="n">
         <v>8</v>
@@ -18090,7 +18076,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18100,12 +18086,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Minst 50 plantor inom ca 8 m2 yta.</t>
+          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18120,6 +18106,26 @@
       <c r="AH155" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -18137,7 +18143,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129295438</v>
+        <v>129294021</v>
       </c>
       <c r="B156" t="n">
         <v>98710</v>
@@ -18167,7 +18173,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -18180,19 +18186,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>524215</v>
+        <v>523995</v>
       </c>
       <c r="R156" t="n">
-        <v>7043793</v>
+        <v>7044066</v>
       </c>
       <c r="S156" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18221,7 +18232,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18231,12 +18242,12 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 3 m2 yta intill en ringhackad gran.</t>
+          <t>Minst 50 plantor inom ca 8 m2 yta.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18250,7 +18261,7 @@
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -18268,48 +18279,62 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129303205</v>
+        <v>129295438</v>
       </c>
       <c r="B157" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>523935</v>
+        <v>524215</v>
       </c>
       <c r="R157" t="n">
-        <v>7044292</v>
+        <v>7043793</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18336,14 +18361,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Minst 40 plantor inom ca 3 m2 yta intill en ringhackad gran.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18354,26 +18389,31 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129303154</v>
+        <v>129303205</v>
       </c>
       <c r="B158" t="n">
-        <v>80148</v>
+        <v>79043</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18381,21 +18421,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18405,10 +18445,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>523989</v>
+        <v>523935</v>
       </c>
       <c r="R158" t="n">
-        <v>7044014</v>
+        <v>7044292</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18441,6 +18481,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18467,10 +18512,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129303100</v>
+        <v>129303154</v>
       </c>
       <c r="B159" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18478,21 +18523,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18502,10 +18547,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>524235</v>
+        <v>523989</v>
       </c>
       <c r="R159" t="n">
-        <v>7043960</v>
+        <v>7044014</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18538,11 +18583,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18569,7 +18609,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129303143</v>
+        <v>129303100</v>
       </c>
       <c r="B160" t="n">
         <v>57727</v>
@@ -18604,10 +18644,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>523911</v>
+        <v>524235</v>
       </c>
       <c r="R160" t="n">
-        <v>7044178</v>
+        <v>7043960</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18644,7 +18684,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18671,7 +18711,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129303112</v>
+        <v>129303143</v>
       </c>
       <c r="B161" t="n">
         <v>57727</v>
@@ -18706,10 +18746,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>524044</v>
+        <v>523911</v>
       </c>
       <c r="R161" t="n">
-        <v>7043935</v>
+        <v>7044178</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18746,7 +18786,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18773,7 +18813,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129303116</v>
+        <v>129303112</v>
       </c>
       <c r="B162" t="n">
         <v>57727</v>
@@ -18808,10 +18848,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>524033</v>
+        <v>524044</v>
       </c>
       <c r="R162" t="n">
-        <v>7043952</v>
+        <v>7043935</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18875,7 +18915,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129303138</v>
+        <v>129303116</v>
       </c>
       <c r="B163" t="n">
         <v>57727</v>
@@ -18910,10 +18950,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>523879</v>
+        <v>524033</v>
       </c>
       <c r="R163" t="n">
-        <v>7044256</v>
+        <v>7043952</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18950,7 +18990,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18977,7 +19017,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129303131</v>
+        <v>129303138</v>
       </c>
       <c r="B164" t="n">
         <v>57727</v>
@@ -19012,10 +19052,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>524059</v>
+        <v>523879</v>
       </c>
       <c r="R164" t="n">
-        <v>7044016</v>
+        <v>7044256</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19079,7 +19119,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129303128</v>
+        <v>129303131</v>
       </c>
       <c r="B165" t="n">
         <v>57727</v>
@@ -19114,10 +19154,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>524186</v>
+        <v>524059</v>
       </c>
       <c r="R165" t="n">
-        <v>7043943</v>
+        <v>7044016</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19154,7 +19194,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19181,7 +19221,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129294096</v>
+        <v>129303128</v>
       </c>
       <c r="B166" t="n">
         <v>57727</v>
@@ -19210,24 +19250,19 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>523971</v>
+        <v>524186</v>
       </c>
       <c r="R166" t="n">
-        <v>7044037</v>
+        <v>7043943</v>
       </c>
       <c r="S166" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19254,24 +19289,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19282,41 +19307,16 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -22185,10 +22185,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129284163</v>
+        <v>129303158</v>
       </c>
       <c r="B192" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22196,42 +22196,37 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>523881</v>
+        <v>524104</v>
       </c>
       <c r="R192" t="n">
-        <v>7044157</v>
+        <v>7044012</v>
       </c>
       <c r="S192" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22258,26 +22253,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
@@ -22286,48 +22266,23 @@
       </c>
       <c r="AG192" t="b">
         <v>0</v>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129296040</v>
+        <v>129284163</v>
       </c>
       <c r="B193" t="n">
         <v>57727</v>
@@ -22363,17 +22318,17 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>524232</v>
+        <v>523881</v>
       </c>
       <c r="R193" t="n">
-        <v>7043714</v>
+        <v>7044157</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -22402,7 +22357,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -22412,12 +22367,12 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22469,10 +22424,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129303158</v>
+        <v>129296040</v>
       </c>
       <c r="B194" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22480,34 +22435,39 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>524104</v>
+        <v>524232</v>
       </c>
       <c r="R194" t="n">
-        <v>7044012</v>
+        <v>7043714</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22537,11 +22497,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
@@ -22550,16 +22525,41 @@
       </c>
       <c r="AG194" t="b">
         <v>0</v>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129303134</v>
+        <v>129303162</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>80175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523912</v>
+        <v>524071</v>
       </c>
       <c r="R2" t="n">
-        <v>7044281</v>
+        <v>7044020</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129303106</v>
+        <v>129287650</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524060</v>
+        <v>523970</v>
       </c>
       <c r="R3" t="n">
-        <v>7043917</v>
+        <v>7044272</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,14 +840,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129287650</v>
+        <v>129294077</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,37 +890,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523970</v>
+        <v>523957</v>
       </c>
       <c r="R4" t="n">
-        <v>7044272</v>
+        <v>7044053</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +964,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,6 +980,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -986,38 +1021,47 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129294077</v>
+        <v>129293037</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>98655</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>219795</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1026,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523957</v>
+        <v>524020</v>
       </c>
       <c r="R5" t="n">
-        <v>7044053</v>
+        <v>7044025</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,12 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,27 +1129,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1128,62 +1147,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129293037</v>
+        <v>129303207</v>
       </c>
       <c r="B6" t="n">
-        <v>98655</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219795</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524020</v>
+        <v>523916</v>
       </c>
       <c r="R6" t="n">
-        <v>7044025</v>
+        <v>7044193</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,21 +1215,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1233,28 +1228,23 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129303207</v>
+        <v>129303197</v>
       </c>
       <c r="B7" t="n">
         <v>79070</v>
@@ -1289,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523916</v>
+        <v>524192</v>
       </c>
       <c r="R7" t="n">
-        <v>7044193</v>
+        <v>7043748</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129303197</v>
+        <v>129303201</v>
       </c>
       <c r="B8" t="n">
         <v>79070</v>
@@ -1386,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524192</v>
+        <v>524232</v>
       </c>
       <c r="R8" t="n">
-        <v>7043748</v>
+        <v>7043959</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129303201</v>
+        <v>129303134</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524232</v>
+        <v>523912</v>
       </c>
       <c r="R9" t="n">
-        <v>7043959</v>
+        <v>7044281</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,6 +1509,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129303162</v>
+        <v>129303106</v>
       </c>
       <c r="B10" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,21 +1551,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524071</v>
+        <v>524060</v>
       </c>
       <c r="R10" t="n">
-        <v>7044020</v>
+        <v>7043917</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,6 +1611,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2027,45 +2027,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129303165</v>
+        <v>129303181</v>
       </c>
       <c r="B14" t="n">
-        <v>80175</v>
+        <v>98756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523906</v>
+        <v>524277</v>
       </c>
       <c r="R14" t="n">
-        <v>7044257</v>
+        <v>7043850</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2100,12 +2116,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2124,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129303169</v>
+        <v>129303165</v>
       </c>
       <c r="B15" t="n">
         <v>80175</v>
@@ -2159,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523880</v>
+        <v>523906</v>
       </c>
       <c r="R15" t="n">
-        <v>7044224</v>
+        <v>7044257</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,61 +2243,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129303181</v>
+        <v>129303169</v>
       </c>
       <c r="B16" t="n">
-        <v>98756</v>
+        <v>80175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524277</v>
+        <v>523880</v>
       </c>
       <c r="R16" t="n">
-        <v>7043850</v>
+        <v>7044224</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2310,18 +2316,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129303107</v>
+        <v>129287170</v>
       </c>
       <c r="B28" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3569,37 +3569,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524056</v>
+        <v>523927</v>
       </c>
       <c r="R28" t="n">
-        <v>7043920</v>
+        <v>7044151</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3626,14 +3626,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3644,26 +3654,51 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129303108</v>
+        <v>129289352</v>
       </c>
       <c r="B29" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,37 +3706,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524052</v>
+        <v>524002</v>
       </c>
       <c r="R29" t="n">
-        <v>7043922</v>
+        <v>7044191</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3728,14 +3763,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3746,23 +3786,48 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129303097</v>
+        <v>129284656</v>
       </c>
       <c r="B30" t="n">
         <v>57730</v>
@@ -3791,19 +3856,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524306</v>
+        <v>523856</v>
       </c>
       <c r="R30" t="n">
-        <v>7043867</v>
+        <v>7044190</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3830,14 +3900,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, högt upp på en tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,23 +3928,48 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129287170</v>
+        <v>129303200</v>
       </c>
       <c r="B31" t="n">
         <v>79070</v>
@@ -3895,17 +4000,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523927</v>
+        <v>524241</v>
       </c>
       <c r="R31" t="n">
-        <v>7044151</v>
+        <v>7043947</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3932,26 +4037,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3960,89 +4050,80 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129289352</v>
+        <v>129303190</v>
       </c>
       <c r="B32" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524002</v>
+        <v>524085</v>
       </c>
       <c r="R32" t="n">
-        <v>7044191</v>
+        <v>7044079</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4069,19 +4150,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:55</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4090,96 +4166,67 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129284656</v>
+        <v>129303192</v>
       </c>
       <c r="B33" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523856</v>
+        <v>524247</v>
       </c>
       <c r="R33" t="n">
-        <v>7044190</v>
+        <v>7043768</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4206,26 +4253,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, högt upp på en tall.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4234,51 +4266,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129303200</v>
+        <v>129303107</v>
       </c>
       <c r="B34" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4286,21 +4293,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4310,10 +4317,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524241</v>
+        <v>524056</v>
       </c>
       <c r="R34" t="n">
-        <v>7043947</v>
+        <v>7043920</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4346,6 +4353,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4372,61 +4384,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129303190</v>
+        <v>129303108</v>
       </c>
       <c r="B35" t="n">
-        <v>98756</v>
+        <v>57730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524085</v>
+        <v>524052</v>
       </c>
       <c r="R35" t="n">
-        <v>7044079</v>
+        <v>7043922</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4463,7 +4459,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4472,7 +4468,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4491,32 +4486,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129303192</v>
+        <v>129303097</v>
       </c>
       <c r="B36" t="n">
-        <v>98756</v>
+        <v>57730</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4526,10 +4521,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524247</v>
+        <v>524306</v>
       </c>
       <c r="R36" t="n">
-        <v>7043768</v>
+        <v>7043867</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4562,6 +4557,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -9851,50 +9851,64 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129295984</v>
+        <v>129291435</v>
       </c>
       <c r="B83" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524244</v>
+        <v>524168</v>
       </c>
       <c r="R83" t="n">
-        <v>7043732</v>
+        <v>7044018</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9926,7 +9940,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9936,12 +9950,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska.</t>
+          <t>Minst 70 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9956,26 +9970,6 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9993,7 +9987,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129294143</v>
+        <v>129295984</v>
       </c>
       <c r="B84" t="n">
         <v>57730</v>
@@ -10029,17 +10023,17 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523985</v>
+        <v>524244</v>
       </c>
       <c r="R84" t="n">
-        <v>7044028</v>
+        <v>7043732</v>
       </c>
       <c r="S84" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10068,7 +10062,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10078,12 +10072,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på gränsen till färska.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10135,10 +10129,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129295781</v>
+        <v>129294143</v>
       </c>
       <c r="B85" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10146,42 +10140,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524196</v>
+        <v>523985</v>
       </c>
       <c r="R85" t="n">
-        <v>7043740</v>
+        <v>7044028</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10210,7 +10204,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10220,12 +10214,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar. Med fertila.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10254,12 +10248,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10277,64 +10271,50 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129291435</v>
+        <v>129295781</v>
       </c>
       <c r="B86" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524168</v>
+        <v>524196</v>
       </c>
       <c r="R86" t="n">
-        <v>7044018</v>
+        <v>7043740</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10366,7 +10346,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10376,12 +10356,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Minst 70 plantor inom ca 3 m2 yta.</t>
+          <t>Långväxta bålar på flera granar. Med fertila.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10396,6 +10376,26 @@
       <c r="AH86" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10821,10 +10821,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129303161</v>
+        <v>129303127</v>
       </c>
       <c r="B91" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10832,21 +10832,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10856,10 +10856,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>524072</v>
+        <v>523955</v>
       </c>
       <c r="R91" t="n">
-        <v>7044015</v>
+        <v>7044054</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10892,6 +10892,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10918,10 +10923,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129303175</v>
+        <v>129303088</v>
       </c>
       <c r="B92" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10929,21 +10934,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10953,10 +10958,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523926</v>
+        <v>524211</v>
       </c>
       <c r="R92" t="n">
-        <v>7044123</v>
+        <v>7043713</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10989,6 +10994,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11015,50 +11025,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129287621</v>
+        <v>129303115</v>
       </c>
       <c r="B93" t="n">
-        <v>92536</v>
+        <v>57730</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523953</v>
+        <v>524039</v>
       </c>
       <c r="R93" t="n">
-        <v>7044206</v>
+        <v>7043944</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11088,24 +11093,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>I ett fuktstråk.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11116,59 +11111,54 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129294174</v>
+        <v>129287621</v>
       </c>
       <c r="B94" t="n">
-        <v>57730</v>
+        <v>92536</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11177,13 +11167,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523983</v>
+        <v>523953</v>
       </c>
       <c r="R94" t="n">
-        <v>7044020</v>
+        <v>7044206</v>
       </c>
       <c r="S94" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11212,7 +11202,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11222,12 +11212,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>I ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11242,26 +11232,6 @@
       <c r="AH94" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11279,7 +11249,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129303127</v>
+        <v>129294174</v>
       </c>
       <c r="B95" t="n">
         <v>57730</v>
@@ -11308,19 +11278,24 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523955</v>
+        <v>523983</v>
       </c>
       <c r="R95" t="n">
-        <v>7044054</v>
+        <v>7044020</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11347,14 +11322,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11365,26 +11350,51 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129303088</v>
+        <v>129303161</v>
       </c>
       <c r="B96" t="n">
-        <v>57730</v>
+        <v>80175</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11392,21 +11402,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11416,10 +11426,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524211</v>
+        <v>524072</v>
       </c>
       <c r="R96" t="n">
-        <v>7043713</v>
+        <v>7044015</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11452,11 +11462,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11483,10 +11488,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129303115</v>
+        <v>129303175</v>
       </c>
       <c r="B97" t="n">
-        <v>57730</v>
+        <v>80175</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11494,21 +11499,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11518,10 +11523,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>524039</v>
+        <v>523926</v>
       </c>
       <c r="R97" t="n">
-        <v>7043944</v>
+        <v>7044123</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11554,11 +11559,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11704,32 +11704,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129303208</v>
+        <v>129303090</v>
       </c>
       <c r="B99" t="n">
-        <v>92176</v>
+        <v>57730</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11739,10 +11739,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>524022</v>
+        <v>524194</v>
       </c>
       <c r="R99" t="n">
-        <v>7044005</v>
+        <v>7043755</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På fälld sälg</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11806,10 +11806,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129303202</v>
+        <v>129303123</v>
       </c>
       <c r="B100" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11817,21 +11817,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11841,10 +11841,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>524156</v>
+        <v>523980</v>
       </c>
       <c r="R100" t="n">
-        <v>7043909</v>
+        <v>7044026</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11908,10 +11908,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129303170</v>
+        <v>129303091</v>
       </c>
       <c r="B101" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11919,21 +11919,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11943,10 +11943,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523868</v>
+        <v>524225</v>
       </c>
       <c r="R101" t="n">
-        <v>7044208</v>
+        <v>7043779</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11979,6 +11979,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12005,7 +12010,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129290810</v>
+        <v>129303139</v>
       </c>
       <c r="B102" t="n">
         <v>57730</v>
@@ -12034,29 +12039,19 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>524168</v>
+        <v>523860</v>
       </c>
       <c r="R102" t="n">
-        <v>7044054</v>
+        <v>7044250</v>
       </c>
       <c r="S102" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12083,24 +12078,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Äldre</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12111,48 +12096,23 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129294258</v>
+        <v>129303096</v>
       </c>
       <c r="B103" t="n">
         <v>57730</v>
@@ -12181,24 +12141,19 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>524049</v>
+        <v>524226</v>
       </c>
       <c r="R103" t="n">
-        <v>7043961</v>
+        <v>7043829</v>
       </c>
       <c r="S103" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12225,24 +12180,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12253,48 +12198,23 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129303090</v>
+        <v>129303144</v>
       </c>
       <c r="B104" t="n">
         <v>57730</v>
@@ -12329,10 +12249,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>524194</v>
+        <v>523900</v>
       </c>
       <c r="R104" t="n">
-        <v>7043755</v>
+        <v>7044174</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12369,7 +12289,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12396,7 +12316,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129303123</v>
+        <v>129290810</v>
       </c>
       <c r="B105" t="n">
         <v>57730</v>
@@ -12425,19 +12345,29 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523980</v>
+        <v>524168</v>
       </c>
       <c r="R105" t="n">
-        <v>7044026</v>
+        <v>7044054</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12464,14 +12394,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12482,23 +12422,48 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129303091</v>
+        <v>129294258</v>
       </c>
       <c r="B106" t="n">
         <v>57730</v>
@@ -12527,19 +12492,24 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>524225</v>
+        <v>524049</v>
       </c>
       <c r="R106" t="n">
-        <v>7043779</v>
+        <v>7043961</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12566,14 +12536,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12584,48 +12564,73 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129303139</v>
+        <v>129303208</v>
       </c>
       <c r="B107" t="n">
-        <v>57730</v>
+        <v>92176</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12635,10 +12640,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>523860</v>
+        <v>524022</v>
       </c>
       <c r="R107" t="n">
-        <v>7044250</v>
+        <v>7044005</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12675,7 +12680,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Äldre</t>
+          <t>På fälld sälg</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12702,10 +12707,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129303096</v>
+        <v>129303202</v>
       </c>
       <c r="B108" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12713,21 +12718,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12737,10 +12742,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>524226</v>
+        <v>524156</v>
       </c>
       <c r="R108" t="n">
-        <v>7043829</v>
+        <v>7043909</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12777,7 +12782,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12804,10 +12809,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129303144</v>
+        <v>129303170</v>
       </c>
       <c r="B109" t="n">
-        <v>57730</v>
+        <v>80175</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12815,21 +12820,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12839,10 +12844,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>523900</v>
+        <v>523868</v>
       </c>
       <c r="R109" t="n">
-        <v>7044174</v>
+        <v>7044208</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12875,11 +12880,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13037,10 +13037,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129283727</v>
+        <v>129303168</v>
       </c>
       <c r="B111" t="n">
-        <v>57730</v>
+        <v>80175</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13048,39 +13048,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>523881</v>
+        <v>523894</v>
       </c>
       <c r="R111" t="n">
-        <v>7044149</v>
+        <v>7044235</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13110,26 +13105,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, enstaka högt upp på en gran.</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
@@ -13138,103 +13118,64 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129293149</v>
+        <v>129303122</v>
       </c>
       <c r="B112" t="n">
-        <v>98655</v>
+        <v>57730</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219795</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524014</v>
+        <v>523976</v>
       </c>
       <c r="R112" t="n">
-        <v>7044008</v>
+        <v>7044021</v>
       </c>
       <c r="S112" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13261,24 +13202,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Växer intill en gammal lunglavssälg vid en göl.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13289,31 +13220,26 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129303168</v>
+        <v>129303145</v>
       </c>
       <c r="B113" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13321,21 +13247,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13345,10 +13271,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>523894</v>
+        <v>523898</v>
       </c>
       <c r="R113" t="n">
-        <v>7044235</v>
+        <v>7044169</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13381,6 +13307,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13407,7 +13338,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129303122</v>
+        <v>129303110</v>
       </c>
       <c r="B114" t="n">
         <v>57730</v>
@@ -13442,10 +13373,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>523976</v>
+        <v>524053</v>
       </c>
       <c r="R114" t="n">
-        <v>7044021</v>
+        <v>7043929</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13509,45 +13440,61 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129303145</v>
+        <v>129303184</v>
       </c>
       <c r="B115" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>523898</v>
+        <v>524159</v>
       </c>
       <c r="R115" t="n">
-        <v>7044169</v>
+        <v>7043990</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13584,7 +13531,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13593,6 +13540,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13611,7 +13559,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129303110</v>
+        <v>129283727</v>
       </c>
       <c r="B116" t="n">
         <v>57730</v>
@@ -13640,16 +13588,21 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524053</v>
+        <v>523881</v>
       </c>
       <c r="R116" t="n">
-        <v>7043929</v>
+        <v>7044149</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13679,14 +13632,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, färska, enstaka högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13697,53 +13660,78 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129303184</v>
+        <v>129293149</v>
       </c>
       <c r="B117" t="n">
-        <v>98756</v>
+        <v>98655</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -13751,26 +13739,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524159</v>
+        <v>524014</v>
       </c>
       <c r="R117" t="n">
-        <v>7043990</v>
+        <v>7044008</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13797,14 +13783,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Växer intill en gammal lunglavssälg vid en göl.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13813,19 +13809,23 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13974,7 +13974,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129303119</v>
+        <v>129303082</v>
       </c>
       <c r="B119" t="n">
         <v>57730</v>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524000</v>
+        <v>524269</v>
       </c>
       <c r="R119" t="n">
-        <v>7044000</v>
+        <v>7043735</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14076,7 +14076,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129303095</v>
+        <v>129303119</v>
       </c>
       <c r="B120" t="n">
         <v>57730</v>
@@ -14111,10 +14111,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524229</v>
+        <v>524000</v>
       </c>
       <c r="R120" t="n">
-        <v>7043821</v>
+        <v>7044000</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14178,10 +14178,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129303153</v>
+        <v>129303095</v>
       </c>
       <c r="B121" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14189,21 +14189,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14213,10 +14213,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523993</v>
+        <v>524229</v>
       </c>
       <c r="R121" t="n">
-        <v>7044011</v>
+        <v>7043821</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14249,6 +14249,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14275,10 +14280,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129303082</v>
+        <v>129303153</v>
       </c>
       <c r="B122" t="n">
-        <v>57730</v>
+        <v>80175</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14286,21 +14291,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14310,10 +14315,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524269</v>
+        <v>523993</v>
       </c>
       <c r="R122" t="n">
-        <v>7043735</v>
+        <v>7044011</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14346,11 +14351,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14377,47 +14377,38 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129294458</v>
+        <v>129290529</v>
       </c>
       <c r="B123" t="n">
-        <v>98756</v>
+        <v>80175</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14426,13 +14417,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>524123</v>
+        <v>524152</v>
       </c>
       <c r="R123" t="n">
-        <v>7043951</v>
+        <v>7044077</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14461,7 +14452,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14471,12 +14462,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Minst 26 plantor inom ca 2 m2 yta.</t>
+          <t>Fertil lunglav.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14490,7 +14481,27 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -14508,45 +14519,59 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129303094</v>
+        <v>129294458</v>
       </c>
       <c r="B124" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524244</v>
+        <v>524123</v>
       </c>
       <c r="R124" t="n">
-        <v>7043795</v>
+        <v>7043951</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14576,14 +14601,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Minst 26 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14594,23 +14629,28 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129303117</v>
+        <v>129290684</v>
       </c>
       <c r="B125" t="n">
         <v>57730</v>
@@ -14639,19 +14679,29 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>524002</v>
+        <v>524150</v>
       </c>
       <c r="R125" t="n">
-        <v>7043990</v>
+        <v>7044038</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14678,14 +14728,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14696,23 +14756,48 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129303101</v>
+        <v>129295476</v>
       </c>
       <c r="B126" t="n">
         <v>57730</v>
@@ -14741,19 +14826,29 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>524169</v>
+        <v>524222</v>
       </c>
       <c r="R126" t="n">
-        <v>7043927</v>
+        <v>7043799</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14780,14 +14875,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14798,16 +14903,41 @@
       </c>
       <c r="AG126" t="b">
         <v>0</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -15030,32 +15160,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129303160</v>
+        <v>129303210</v>
       </c>
       <c r="B129" t="n">
-        <v>80175</v>
+        <v>100945</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15065,10 +15195,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524077</v>
+        <v>523999</v>
       </c>
       <c r="R129" t="n">
-        <v>7044028</v>
+        <v>7043998</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15127,7 +15257,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129303157</v>
+        <v>129303160</v>
       </c>
       <c r="B130" t="n">
         <v>80175</v>
@@ -15162,10 +15292,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524023</v>
+        <v>524077</v>
       </c>
       <c r="R130" t="n">
-        <v>7044002</v>
+        <v>7044028</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15224,7 +15354,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129303176</v>
+        <v>129303157</v>
       </c>
       <c r="B131" t="n">
         <v>80175</v>
@@ -15259,10 +15389,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>523949</v>
+        <v>524023</v>
       </c>
       <c r="R131" t="n">
-        <v>7044082</v>
+        <v>7044002</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15321,10 +15451,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129303125</v>
+        <v>129303176</v>
       </c>
       <c r="B132" t="n">
-        <v>57730</v>
+        <v>80175</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15332,21 +15462,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15356,10 +15486,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>523973</v>
+        <v>523949</v>
       </c>
       <c r="R132" t="n">
-        <v>7044031</v>
+        <v>7044082</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15392,11 +15522,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15423,10 +15548,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129290529</v>
+        <v>129303094</v>
       </c>
       <c r="B133" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15434,42 +15559,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524152</v>
+        <v>524244</v>
       </c>
       <c r="R133" t="n">
-        <v>7044077</v>
+        <v>7043795</v>
       </c>
       <c r="S133" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15496,24 +15616,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Fertil lunglav.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15524,48 +15634,23 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129290684</v>
+        <v>129303117</v>
       </c>
       <c r="B134" t="n">
         <v>57730</v>
@@ -15594,29 +15679,19 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524150</v>
+        <v>524002</v>
       </c>
       <c r="R134" t="n">
-        <v>7044038</v>
+        <v>7043990</v>
       </c>
       <c r="S134" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15643,24 +15718,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15671,48 +15736,23 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129295476</v>
+        <v>129303101</v>
       </c>
       <c r="B135" t="n">
         <v>57730</v>
@@ -15741,29 +15781,19 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524222</v>
+        <v>524169</v>
       </c>
       <c r="R135" t="n">
-        <v>7043799</v>
+        <v>7043927</v>
       </c>
       <c r="S135" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15790,24 +15820,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15818,73 +15838,48 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129303210</v>
+        <v>129303125</v>
       </c>
       <c r="B136" t="n">
-        <v>100945</v>
+        <v>57730</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15894,10 +15889,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>523999</v>
+        <v>523973</v>
       </c>
       <c r="R136" t="n">
-        <v>7043998</v>
+        <v>7044031</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15930,6 +15925,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15956,53 +15956,48 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129292744</v>
+        <v>129294482</v>
       </c>
       <c r="B137" t="n">
-        <v>92536</v>
+        <v>79070</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>524257</v>
+        <v>524138</v>
       </c>
       <c r="R137" t="n">
-        <v>7043942</v>
+        <v>7043958</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16031,7 +16026,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16041,7 +16036,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16068,47 +16063,38 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129290074</v>
+        <v>129292744</v>
       </c>
       <c r="B138" t="n">
-        <v>98756</v>
+        <v>92536</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -16117,10 +16103,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>524078</v>
+        <v>524257</v>
       </c>
       <c r="R138" t="n">
-        <v>7044092</v>
+        <v>7043942</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16152,7 +16138,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16162,12 +16148,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Minst 20 plantor inom ca 1 m2 yta</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16178,11 +16159,6 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
@@ -16199,7 +16175,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129296451</v>
+        <v>129290074</v>
       </c>
       <c r="B139" t="n">
         <v>98756</v>
@@ -16229,7 +16205,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -16239,27 +16215,22 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>524225</v>
+        <v>524078</v>
       </c>
       <c r="R139" t="n">
-        <v>7043763</v>
+        <v>7044092</v>
       </c>
       <c r="S139" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16288,7 +16259,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16298,12 +16269,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Minst 40 plantor och 2 fröställningar inom ca 0,5 m2 yta i gammal granskog.</t>
+          <t>Minst 20 plantor inom ca 1 m2 yta</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16317,7 +16288,7 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -16335,7 +16306,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129294820</v>
+        <v>129296451</v>
       </c>
       <c r="B140" t="n">
         <v>98756</v>
@@ -16365,7 +16336,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -16378,19 +16349,24 @@
           <t>frukt-/fröspridning</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>524171</v>
+        <v>524225</v>
       </c>
       <c r="R140" t="n">
-        <v>7043952</v>
+        <v>7043763</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16419,7 +16395,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16429,12 +16405,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Minst 25 plantor och 5 fröställningar inom ca 1 m2 yta.</t>
+          <t>Minst 40 plantor och 2 fröställningar inom ca 0,5 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16448,7 +16424,7 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16466,48 +16442,62 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129294482</v>
+        <v>129294820</v>
       </c>
       <c r="B141" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>524138</v>
+        <v>524171</v>
       </c>
       <c r="R141" t="n">
-        <v>7043958</v>
+        <v>7043952</v>
       </c>
       <c r="S141" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16536,7 +16526,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16546,7 +16536,12 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 5 fröställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16557,6 +16552,11 @@
       </c>
       <c r="AG141" t="b">
         <v>0</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
@@ -19517,61 +19517,45 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129303193</v>
+        <v>129290115</v>
       </c>
       <c r="B169" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>524262</v>
+        <v>524105</v>
       </c>
       <c r="R169" t="n">
-        <v>7043772</v>
+        <v>7044094</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19601,14 +19585,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19617,83 +19606,96 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129303185</v>
+        <v>129284399</v>
       </c>
       <c r="B170" t="n">
-        <v>98756</v>
+        <v>57730</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>524154</v>
+        <v>523878</v>
       </c>
       <c r="R170" t="n">
-        <v>7043984</v>
+        <v>7044161</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19720,14 +19722,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Minst 80</t>
+          <t>Ringhack, färska och tydliga, på en gran.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19736,26 +19748,50 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129303178</v>
+        <v>129290296</v>
       </c>
       <c r="B171" t="n">
         <v>98756</v>
@@ -19783,17 +19819,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>524227</v>
+        <v>524120</v>
       </c>
       <c r="R171" t="n">
-        <v>7043726</v>
+        <v>7044089</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19823,11 +19878,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Minst 100 plantor och 4 fröställningar inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
@@ -19836,26 +19906,31 @@
       </c>
       <c r="AG171" t="b">
         <v>0</v>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129290115</v>
+        <v>129303172</v>
       </c>
       <c r="B172" t="n">
-        <v>79070</v>
+        <v>80175</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19863,34 +19938,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>524105</v>
+        <v>523890</v>
       </c>
       <c r="R172" t="n">
-        <v>7044094</v>
+        <v>7044217</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19920,21 +19995,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
@@ -19943,51 +20008,26 @@
       </c>
       <c r="AG172" t="b">
         <v>0</v>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129284399</v>
+        <v>129303156</v>
       </c>
       <c r="B173" t="n">
-        <v>57730</v>
+        <v>80175</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19995,42 +20035,40 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>523878</v>
+        <v>524022</v>
       </c>
       <c r="R173" t="n">
-        <v>7044161</v>
+        <v>7044009</v>
       </c>
       <c r="S173" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -20057,24 +20095,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Ringhack, färska och tydliga, på en gran.</t>
+          <t>På liten gran</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20083,14 +20111,10 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
-      <c r="AH173" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AJ173" t="inlineStr">
         <is>
           <t>gran</t>
@@ -20101,70 +20125,81 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM173" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129303172</v>
+        <v>129303193</v>
       </c>
       <c r="B174" t="n">
-        <v>80175</v>
+        <v>98756</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>523890</v>
+        <v>524262</v>
       </c>
       <c r="R174" t="n">
-        <v>7044217</v>
+        <v>7043772</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20199,12 +20234,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -20223,48 +20264,61 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129303156</v>
+        <v>129303185</v>
       </c>
       <c r="B175" t="n">
-        <v>80175</v>
+        <v>98756</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>524022</v>
+        <v>524154</v>
       </c>
       <c r="R175" t="n">
-        <v>7044009</v>
+        <v>7043984</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20301,7 +20355,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>På liten gran</t>
+          <t>Minst 80</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20313,21 +20367,6 @@
       <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
@@ -20344,32 +20383,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129303126</v>
+        <v>129303178</v>
       </c>
       <c r="B176" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -20379,10 +20418,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>523960</v>
+        <v>524227</v>
       </c>
       <c r="R176" t="n">
-        <v>7044047</v>
+        <v>7043726</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20415,11 +20454,6 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20446,10 +20480,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129303114</v>
+        <v>129303203</v>
       </c>
       <c r="B177" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20457,21 +20491,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -20481,10 +20515,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>524041</v>
+        <v>524206</v>
       </c>
       <c r="R177" t="n">
-        <v>7043942</v>
+        <v>7043945</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20517,11 +20551,6 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20548,64 +20577,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129290296</v>
+        <v>129303147</v>
       </c>
       <c r="B178" t="n">
-        <v>98756</v>
+        <v>57730</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>524120</v>
+        <v>523930</v>
       </c>
       <c r="R178" t="n">
-        <v>7044089</v>
+        <v>7044107</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20635,24 +20645,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 4 fröställningar inom ca 2 m2 yta.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20663,31 +20663,26 @@
       </c>
       <c r="AG178" t="b">
         <v>0</v>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129303203</v>
+        <v>129303146</v>
       </c>
       <c r="B179" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20695,21 +20690,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -20719,10 +20714,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>524206</v>
+        <v>523926</v>
       </c>
       <c r="R179" t="n">
-        <v>7043945</v>
+        <v>7044118</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20755,6 +20750,11 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20781,7 +20781,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129303147</v>
+        <v>129303126</v>
       </c>
       <c r="B180" t="n">
         <v>57730</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>523930</v>
+        <v>523960</v>
       </c>
       <c r="R180" t="n">
-        <v>7044107</v>
+        <v>7044047</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20883,7 +20883,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129303146</v>
+        <v>129303114</v>
       </c>
       <c r="B181" t="n">
         <v>57730</v>
@@ -20918,10 +20918,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>523926</v>
+        <v>524041</v>
       </c>
       <c r="R181" t="n">
-        <v>7044118</v>
+        <v>7043942</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20958,7 +20958,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21862,10 +21862,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129303141</v>
+        <v>129303158</v>
       </c>
       <c r="B189" t="n">
-        <v>57730</v>
+        <v>80175</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21873,21 +21873,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21897,10 +21897,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>523902</v>
+        <v>524104</v>
       </c>
       <c r="R189" t="n">
-        <v>7044224</v>
+        <v>7044012</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21933,11 +21933,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21964,7 +21959,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129303140</v>
+        <v>129303141</v>
       </c>
       <c r="B190" t="n">
         <v>57730</v>
@@ -21999,10 +21994,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>523866</v>
+        <v>523902</v>
       </c>
       <c r="R190" t="n">
-        <v>7044256</v>
+        <v>7044224</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -22039,7 +22034,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22066,7 +22061,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129284163</v>
+        <v>129303140</v>
       </c>
       <c r="B191" t="n">
         <v>57730</v>
@@ -22095,24 +22090,19 @@
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>523881</v>
+        <v>523866</v>
       </c>
       <c r="R191" t="n">
-        <v>7044157</v>
+        <v>7044256</v>
       </c>
       <c r="S191" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -22139,24 +22129,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22167,48 +22147,23 @@
       </c>
       <c r="AG191" t="b">
         <v>0</v>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO191" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129296040</v>
+        <v>129284163</v>
       </c>
       <c r="B192" t="n">
         <v>57730</v>
@@ -22244,17 +22199,17 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>524232</v>
+        <v>523881</v>
       </c>
       <c r="R192" t="n">
-        <v>7043714</v>
+        <v>7044157</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22283,7 +22238,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -22293,12 +22248,12 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22350,10 +22305,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129303158</v>
+        <v>129296040</v>
       </c>
       <c r="B193" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22361,34 +22316,39 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>524104</v>
+        <v>524232</v>
       </c>
       <c r="R193" t="n">
-        <v>7044012</v>
+        <v>7043714</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22418,11 +22378,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
@@ -22431,16 +22406,41 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129303162</v>
+        <v>129303207</v>
       </c>
       <c r="B4" t="n">
-        <v>80181</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524071</v>
+        <v>523916</v>
       </c>
       <c r="R4" t="n">
-        <v>7044020</v>
+        <v>7044193</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129303207</v>
+        <v>129303197</v>
       </c>
       <c r="B5" t="n">
         <v>79076</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523916</v>
+        <v>524192</v>
       </c>
       <c r="R5" t="n">
-        <v>7044193</v>
+        <v>7043748</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1102,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129303197</v>
+        <v>129303201</v>
       </c>
       <c r="B6" t="n">
         <v>79076</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524192</v>
+        <v>524232</v>
       </c>
       <c r="R6" t="n">
-        <v>7043748</v>
+        <v>7043959</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129303201</v>
+        <v>129303162</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>80181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524232</v>
+        <v>524071</v>
       </c>
       <c r="R7" t="n">
-        <v>7043959</v>
+        <v>7044020</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,64 +1296,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129303181</v>
+        <v>129295161</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524277</v>
+        <v>524240</v>
       </c>
       <c r="R8" t="n">
-        <v>7043850</v>
+        <v>7043842</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,14 +1364,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,29 +1385,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129295161</v>
+        <v>129289927</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>80181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1426,37 +1414,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524240</v>
+        <v>524085</v>
       </c>
       <c r="R9" t="n">
-        <v>7043842</v>
+        <v>7044128</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1485,7 +1478,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1495,7 +1488,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,6 +1504,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1522,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129289927</v>
+        <v>129303165</v>
       </c>
       <c r="B10" t="n">
         <v>80181</v>
@@ -1551,24 +1574,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524085</v>
+        <v>523906</v>
       </c>
       <c r="R10" t="n">
-        <v>7044128</v>
+        <v>7044257</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1595,26 +1613,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en grov sälglåga.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1623,48 +1626,23 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129303165</v>
+        <v>129303169</v>
       </c>
       <c r="B11" t="n">
         <v>80181</v>
@@ -1699,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523906</v>
+        <v>523880</v>
       </c>
       <c r="R11" t="n">
-        <v>7044257</v>
+        <v>7044224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,45 +1739,61 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129303169</v>
+        <v>129303181</v>
       </c>
       <c r="B12" t="n">
-        <v>80181</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523880</v>
+        <v>524277</v>
       </c>
       <c r="R12" t="n">
-        <v>7044224</v>
+        <v>7043850</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,12 +1828,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1994,64 +1994,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129303183</v>
+        <v>129294979</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>98686</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524194</v>
+        <v>524252</v>
       </c>
       <c r="R14" t="n">
-        <v>7043977</v>
+        <v>7043871</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2078,14 +2067,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,29 +2088,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129294284</v>
+        <v>129303164</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,37 +2122,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524055</v>
+        <v>523921</v>
       </c>
       <c r="R15" t="n">
-        <v>7043952</v>
+        <v>7044287</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2181,21 +2179,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2204,66 +2192,77 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129292345</v>
+        <v>129303183</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524220</v>
+        <v>524194</v>
       </c>
       <c r="R16" t="n">
-        <v>7043956</v>
+        <v>7043977</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,24 +2292,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,53 +2308,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129289415</v>
+        <v>129286516</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>57896</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,37 +2338,56 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524038</v>
+        <v>523928</v>
       </c>
       <c r="R17" t="n">
-        <v>7044201</v>
+        <v>7044231</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2432,7 +2416,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2442,7 +2426,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 2 livliga talltitor i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2453,6 +2442,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2469,64 +2463,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129286516</v>
+        <v>129303149</v>
       </c>
       <c r="B18" t="n">
-        <v>57896</v>
+        <v>92543</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523928</v>
+        <v>523933</v>
       </c>
       <c r="R18" t="n">
-        <v>7044231</v>
+        <v>7044287</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,26 +2531,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 2 livliga talltitor i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2584,74 +2544,64 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129294979</v>
+        <v>129303199</v>
       </c>
       <c r="B19" t="n">
-        <v>98686</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524252</v>
+        <v>524280</v>
       </c>
       <c r="R19" t="n">
-        <v>7043871</v>
+        <v>7043899</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2678,21 +2628,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2701,53 +2641,48 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129303149</v>
+        <v>129303198</v>
       </c>
       <c r="B20" t="n">
-        <v>92543</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2757,10 +2692,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523933</v>
+        <v>524207</v>
       </c>
       <c r="R20" t="n">
-        <v>7044287</v>
+        <v>7043773</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2819,10 +2754,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129303164</v>
+        <v>129294284</v>
       </c>
       <c r="B21" t="n">
-        <v>80181</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,37 +2765,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523921</v>
+        <v>524055</v>
       </c>
       <c r="R21" t="n">
-        <v>7044287</v>
+        <v>7043952</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2887,11 +2822,21 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2900,23 +2845,28 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129303199</v>
+        <v>129292345</v>
       </c>
       <c r="B22" t="n">
         <v>79076</v>
@@ -2947,14 +2897,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524280</v>
+        <v>524220</v>
       </c>
       <c r="R22" t="n">
-        <v>7043899</v>
+        <v>7043956</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2984,11 +2934,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2997,23 +2962,48 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129303198</v>
+        <v>129289415</v>
       </c>
       <c r="B23" t="n">
         <v>79076</v>
@@ -3044,17 +3034,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524207</v>
+        <v>524038</v>
       </c>
       <c r="R23" t="n">
-        <v>7043773</v>
+        <v>7044201</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3081,9 +3071,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3098,12 +3098,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -5669,7 +5669,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129303188</v>
+        <v>129296356</v>
       </c>
       <c r="B47" t="n">
         <v>98769</v>
@@ -5697,17 +5697,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524104</v>
+        <v>524233</v>
       </c>
       <c r="R47" t="n">
-        <v>7044042</v>
+        <v>7043754</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5737,11 +5756,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 4 m2 yta intill ett par stora block.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5750,23 +5784,28 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129296356</v>
+        <v>129295240</v>
       </c>
       <c r="B48" t="n">
         <v>98769</v>
@@ -5796,7 +5835,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5820,13 +5859,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524233</v>
+        <v>524251</v>
       </c>
       <c r="R48" t="n">
-        <v>7043754</v>
+        <v>7043829</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5855,7 +5894,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5865,12 +5904,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Minst 18 plantor inom ca 4 m2 yta intill ett par stora block.</t>
+          <t>Minst 100 plantor och 2 fröställningar inom ca1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5902,67 +5941,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129295240</v>
+        <v>129303196</v>
       </c>
       <c r="B49" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524251</v>
+        <v>524193</v>
       </c>
       <c r="R49" t="n">
-        <v>7043829</v>
+        <v>7043741</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5989,24 +6009,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 2 fröställningar inom ca1,5 m2 yta.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6017,53 +6027,48 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129303196</v>
+        <v>129303188</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6073,10 +6078,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524193</v>
+        <v>524104</v>
       </c>
       <c r="R50" t="n">
-        <v>7043741</v>
+        <v>7044042</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6109,11 +6114,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6140,7 +6140,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129295781</v>
+        <v>129303195</v>
       </c>
       <c r="B51" t="n">
         <v>79076</v>
@@ -6169,21 +6169,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524196</v>
+        <v>524202</v>
       </c>
       <c r="R51" t="n">
-        <v>7043740</v>
+        <v>7043730</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6213,24 +6208,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar. Med fertila.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6241,105 +6226,66 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129291435</v>
+        <v>129295781</v>
       </c>
       <c r="B52" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524168</v>
+        <v>524196</v>
       </c>
       <c r="R52" t="n">
-        <v>7044018</v>
+        <v>7043740</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6371,7 +6317,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6381,12 +6327,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 70 plantor inom ca 3 m2 yta.</t>
+          <t>Långväxta bålar på flera granar. Med fertila.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6401,6 +6347,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6418,48 +6384,67 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129295640</v>
+        <v>129291435</v>
       </c>
       <c r="B53" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524194</v>
+        <v>524168</v>
       </c>
       <c r="R53" t="n">
-        <v>7043776</v>
+        <v>7044018</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6488,7 +6473,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6498,7 +6483,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6513,26 +6503,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6550,7 +6520,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129303195</v>
+        <v>129295640</v>
       </c>
       <c r="B54" t="n">
         <v>79076</v>
@@ -6581,17 +6551,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524202</v>
+        <v>524194</v>
       </c>
       <c r="R54" t="n">
-        <v>7043730</v>
+        <v>7043776</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6618,14 +6588,19 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6636,16 +6611,41 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6771,45 +6771,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129303161</v>
+        <v>129287621</v>
       </c>
       <c r="B56" t="n">
-        <v>80181</v>
+        <v>92543</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524072</v>
+        <v>523953</v>
       </c>
       <c r="R56" t="n">
-        <v>7044015</v>
+        <v>7044206</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6839,11 +6844,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6852,23 +6872,28 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129303175</v>
+        <v>129303161</v>
       </c>
       <c r="B57" t="n">
         <v>80181</v>
@@ -6903,10 +6928,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523926</v>
+        <v>524072</v>
       </c>
       <c r="R57" t="n">
-        <v>7044123</v>
+        <v>7044015</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6965,61 +6990,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129303179</v>
+        <v>129303175</v>
       </c>
       <c r="B58" t="n">
-        <v>98769</v>
+        <v>80181</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524233</v>
+        <v>523926</v>
       </c>
       <c r="R58" t="n">
-        <v>7043783</v>
+        <v>7044123</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7054,18 +7063,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7084,50 +7087,61 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129287621</v>
+        <v>129303179</v>
       </c>
       <c r="B59" t="n">
-        <v>92543</v>
+        <v>98769</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523953</v>
+        <v>524233</v>
       </c>
       <c r="R59" t="n">
-        <v>7044206</v>
+        <v>7043783</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7157,24 +7171,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>I ett fuktstråk.</t>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7183,33 +7187,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129303170</v>
+        <v>129303202</v>
       </c>
       <c r="B60" t="n">
-        <v>80181</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7217,21 +7217,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7241,10 +7241,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523868</v>
+        <v>524156</v>
       </c>
       <c r="R60" t="n">
-        <v>7044208</v>
+        <v>7043909</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7277,6 +7277,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7405,10 +7410,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129303202</v>
+        <v>129303170</v>
       </c>
       <c r="B62" t="n">
-        <v>79076</v>
+        <v>80181</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7416,21 +7421,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7440,10 +7445,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524156</v>
+        <v>523868</v>
       </c>
       <c r="R62" t="n">
-        <v>7043909</v>
+        <v>7044208</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7476,11 +7481,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7507,47 +7507,47 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129293975</v>
+        <v>129293149</v>
       </c>
       <c r="B63" t="n">
-        <v>57896</v>
+        <v>98668</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>219795</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7556,13 +7556,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523999</v>
+        <v>524014</v>
       </c>
       <c r="R63" t="n">
-        <v>7044073</v>
+        <v>7044008</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Minst 1 talltita i flerskiktad gammal granskog.</t>
+          <t>Växer intill en gammal lunglavssälg vid en göl.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7638,62 +7638,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129293149</v>
+        <v>129303168</v>
       </c>
       <c r="B64" t="n">
-        <v>98668</v>
+        <v>80181</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219795</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524014</v>
+        <v>523894</v>
       </c>
       <c r="R64" t="n">
-        <v>7044008</v>
+        <v>7044235</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7720,26 +7706,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Växer intill en gammal lunglavssälg vid en göl.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7748,31 +7719,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129303168</v>
+        <v>129293975</v>
       </c>
       <c r="B65" t="n">
-        <v>80181</v>
+        <v>57896</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7780,34 +7746,48 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523894</v>
+        <v>523999</v>
       </c>
       <c r="R65" t="n">
-        <v>7044235</v>
+        <v>7044073</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7837,11 +7817,26 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minst 1 talltita i flerskiktad gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7850,16 +7845,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -15058,7 +15058,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129295685</v>
+        <v>129303087</v>
       </c>
       <c r="B129" t="n">
         <v>57736</v>
@@ -15087,21 +15087,16 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524198</v>
+        <v>524219</v>
       </c>
       <c r="R129" t="n">
-        <v>7043758</v>
+        <v>7043705</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15131,24 +15126,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15159,48 +15144,23 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129283648</v>
+        <v>129303133</v>
       </c>
       <c r="B130" t="n">
         <v>57736</v>
@@ -15229,21 +15189,16 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>523885</v>
+        <v>523992</v>
       </c>
       <c r="R130" t="n">
-        <v>7044152</v>
+        <v>7044262</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15273,24 +15228,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15301,48 +15246,23 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129285070</v>
+        <v>129303121</v>
       </c>
       <c r="B131" t="n">
         <v>57736</v>
@@ -15371,24 +15291,19 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>523844</v>
+        <v>523979</v>
       </c>
       <c r="R131" t="n">
-        <v>7044210</v>
+        <v>7044017</v>
       </c>
       <c r="S131" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15415,24 +15330,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15443,48 +15348,23 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129285747</v>
+        <v>129303081</v>
       </c>
       <c r="B132" t="n">
         <v>57736</v>
@@ -15513,24 +15393,19 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>523850</v>
+        <v>524190</v>
       </c>
       <c r="R132" t="n">
-        <v>7044210</v>
+        <v>7043804</v>
       </c>
       <c r="S132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15557,24 +15432,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15585,48 +15450,23 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129294128</v>
+        <v>129295685</v>
       </c>
       <c r="B133" t="n">
         <v>57736</v>
@@ -15657,19 +15497,19 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>523987</v>
+        <v>524198</v>
       </c>
       <c r="R133" t="n">
-        <v>7044025</v>
+        <v>7043758</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15701,7 +15541,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15711,12 +15551,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15768,7 +15608,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129303087</v>
+        <v>129283648</v>
       </c>
       <c r="B134" t="n">
         <v>57736</v>
@@ -15797,16 +15637,21 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524219</v>
+        <v>523885</v>
       </c>
       <c r="R134" t="n">
-        <v>7043705</v>
+        <v>7044152</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15836,14 +15681,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15854,23 +15709,48 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129303133</v>
+        <v>129285070</v>
       </c>
       <c r="B135" t="n">
         <v>57736</v>
@@ -15899,19 +15779,24 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>523992</v>
+        <v>523844</v>
       </c>
       <c r="R135" t="n">
-        <v>7044262</v>
+        <v>7044210</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15938,14 +15823,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15956,23 +15851,48 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129303121</v>
+        <v>129285747</v>
       </c>
       <c r="B136" t="n">
         <v>57736</v>
@@ -16001,19 +15921,24 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>523979</v>
+        <v>523850</v>
       </c>
       <c r="R136" t="n">
-        <v>7044017</v>
+        <v>7044210</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16040,14 +15965,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16058,23 +15993,48 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129303081</v>
+        <v>129294128</v>
       </c>
       <c r="B137" t="n">
         <v>57736</v>
@@ -16103,16 +16063,21 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>524190</v>
+        <v>523987</v>
       </c>
       <c r="R137" t="n">
-        <v>7043804</v>
+        <v>7044025</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16142,14 +16107,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16160,16 +16135,41 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16562,7 +16562,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129303093</v>
+        <v>129303098</v>
       </c>
       <c r="B141" t="n">
         <v>57736</v>
@@ -16597,10 +16597,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>524246</v>
+        <v>524297</v>
       </c>
       <c r="R141" t="n">
-        <v>7043787</v>
+        <v>7043866</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16637,7 +16637,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16664,7 +16664,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129303092</v>
+        <v>129303093</v>
       </c>
       <c r="B142" t="n">
         <v>57736</v>
@@ -16699,10 +16699,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>524227</v>
+        <v>524246</v>
       </c>
       <c r="R142" t="n">
-        <v>7043799</v>
+        <v>7043787</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16739,7 +16739,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16766,7 +16766,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129303148</v>
+        <v>129303092</v>
       </c>
       <c r="B143" t="n">
         <v>57736</v>
@@ -16801,10 +16801,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>523952</v>
+        <v>524227</v>
       </c>
       <c r="R143" t="n">
-        <v>7044072</v>
+        <v>7043799</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16868,7 +16868,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129303098</v>
+        <v>129303148</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -16903,10 +16903,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>524297</v>
+        <v>523952</v>
       </c>
       <c r="R144" t="n">
-        <v>7043866</v>
+        <v>7044072</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16970,7 +16970,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129294174</v>
+        <v>129303127</v>
       </c>
       <c r="B145" t="n">
         <v>57736</v>
@@ -16999,24 +16999,19 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>523983</v>
+        <v>523955</v>
       </c>
       <c r="R145" t="n">
-        <v>7044020</v>
+        <v>7044054</v>
       </c>
       <c r="S145" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17043,24 +17038,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17071,48 +17056,23 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129303127</v>
+        <v>129303088</v>
       </c>
       <c r="B146" t="n">
         <v>57736</v>
@@ -17147,10 +17107,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>523955</v>
+        <v>524211</v>
       </c>
       <c r="R146" t="n">
-        <v>7044054</v>
+        <v>7043713</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17187,7 +17147,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17214,7 +17174,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129303088</v>
+        <v>129303115</v>
       </c>
       <c r="B147" t="n">
         <v>57736</v>
@@ -17249,10 +17209,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>524211</v>
+        <v>524039</v>
       </c>
       <c r="R147" t="n">
-        <v>7043713</v>
+        <v>7043944</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17289,7 +17249,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17316,7 +17276,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129303115</v>
+        <v>129294174</v>
       </c>
       <c r="B148" t="n">
         <v>57736</v>
@@ -17345,19 +17305,24 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>524039</v>
+        <v>523983</v>
       </c>
       <c r="R148" t="n">
-        <v>7043944</v>
+        <v>7044020</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17384,14 +17349,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17402,16 +17377,41 @@
       </c>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -19215,7 +19215,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129303117</v>
+        <v>129290684</v>
       </c>
       <c r="B165" t="n">
         <v>57736</v>
@@ -19244,19 +19244,29 @@
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>524002</v>
+        <v>524150</v>
       </c>
       <c r="R165" t="n">
-        <v>7043990</v>
+        <v>7044038</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19283,14 +19293,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19301,23 +19321,48 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129303094</v>
+        <v>129295476</v>
       </c>
       <c r="B166" t="n">
         <v>57736</v>
@@ -19346,19 +19391,29 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>524244</v>
+        <v>524222</v>
       </c>
       <c r="R166" t="n">
-        <v>7043795</v>
+        <v>7043799</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19385,14 +19440,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19403,23 +19468,48 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303101</v>
+        <v>129303117</v>
       </c>
       <c r="B167" t="n">
         <v>57736</v>
@@ -19454,10 +19544,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>524169</v>
+        <v>524002</v>
       </c>
       <c r="R167" t="n">
-        <v>7043927</v>
+        <v>7043990</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19494,7 +19584,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19521,7 +19611,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129303125</v>
+        <v>129303094</v>
       </c>
       <c r="B168" t="n">
         <v>57736</v>
@@ -19556,10 +19646,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>523973</v>
+        <v>524244</v>
       </c>
       <c r="R168" t="n">
-        <v>7044031</v>
+        <v>7043795</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19596,7 +19686,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19623,7 +19713,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129290684</v>
+        <v>129303101</v>
       </c>
       <c r="B169" t="n">
         <v>57736</v>
@@ -19652,29 +19742,19 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>524150</v>
+        <v>524169</v>
       </c>
       <c r="R169" t="n">
-        <v>7044038</v>
+        <v>7043927</v>
       </c>
       <c r="S169" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19701,24 +19781,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19729,48 +19799,23 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129295476</v>
+        <v>129303125</v>
       </c>
       <c r="B170" t="n">
         <v>57736</v>
@@ -19799,29 +19844,19 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>524222</v>
+        <v>523973</v>
       </c>
       <c r="R170" t="n">
-        <v>7043799</v>
+        <v>7044031</v>
       </c>
       <c r="S170" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19848,24 +19883,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19876,41 +19901,16 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -12822,7 +12822,7 @@
         <v>129376007</v>
       </c>
       <c r="B109" t="n">
-        <v>91959</v>
+        <v>91964</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129303106</v>
+        <v>129294077</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -12949,19 +12949,24 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>524060</v>
+        <v>523957</v>
       </c>
       <c r="R110" t="n">
-        <v>7043917</v>
+        <v>7044053</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12988,14 +12993,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13006,16 +13021,41 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -13124,7 +13164,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129294077</v>
+        <v>129303106</v>
       </c>
       <c r="B112" t="n">
         <v>57736</v>
@@ -13153,24 +13193,19 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>523957</v>
+        <v>524060</v>
       </c>
       <c r="R112" t="n">
-        <v>7044053</v>
+        <v>7043917</v>
       </c>
       <c r="S112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13197,24 +13232,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13225,41 +13250,16 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -13368,7 +13368,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129303107</v>
+        <v>129284656</v>
       </c>
       <c r="B114" t="n">
         <v>57736</v>
@@ -13397,19 +13397,24 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>524056</v>
+        <v>523856</v>
       </c>
       <c r="R114" t="n">
-        <v>7043920</v>
+        <v>7044190</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13436,14 +13441,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre, högt upp på en tall.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13454,23 +13469,48 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129303108</v>
+        <v>129303107</v>
       </c>
       <c r="B115" t="n">
         <v>57736</v>
@@ -13505,10 +13545,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524052</v>
+        <v>524056</v>
       </c>
       <c r="R115" t="n">
-        <v>7043922</v>
+        <v>7043920</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13545,7 +13585,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13674,7 +13714,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129284656</v>
+        <v>129303108</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -13703,24 +13743,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>523856</v>
+        <v>524052</v>
       </c>
       <c r="R117" t="n">
-        <v>7044190</v>
+        <v>7043922</v>
       </c>
       <c r="S117" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13747,24 +13782,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, högt upp på en tall.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13775,41 +13800,16 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13918,7 +13918,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129303118</v>
+        <v>129303120</v>
       </c>
       <c r="B119" t="n">
         <v>57736</v>
@@ -13953,10 +13953,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524000</v>
+        <v>523983</v>
       </c>
       <c r="R119" t="n">
-        <v>7043995</v>
+        <v>7044011</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13993,7 +13993,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14020,7 +14020,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129303120</v>
+        <v>129303118</v>
       </c>
       <c r="B120" t="n">
         <v>57736</v>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>523983</v>
+        <v>524000</v>
       </c>
       <c r="R120" t="n">
-        <v>7044011</v>
+        <v>7043995</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14122,7 +14122,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129303124</v>
+        <v>129286184</v>
       </c>
       <c r="B121" t="n">
         <v>57736</v>
@@ -14151,19 +14151,24 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523976</v>
+        <v>523842</v>
       </c>
       <c r="R121" t="n">
-        <v>7044029</v>
+        <v>7044233</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14190,14 +14195,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14208,23 +14223,48 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129303129</v>
+        <v>129292836</v>
       </c>
       <c r="B122" t="n">
         <v>57736</v>
@@ -14253,19 +14293,24 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524088</v>
+        <v>524162</v>
       </c>
       <c r="R122" t="n">
-        <v>7044015</v>
+        <v>7043929</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14292,14 +14337,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14310,23 +14365,48 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129286184</v>
+        <v>129303129</v>
       </c>
       <c r="B123" t="n">
         <v>57736</v>
@@ -14355,24 +14435,19 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>523842</v>
+        <v>524088</v>
       </c>
       <c r="R123" t="n">
-        <v>7044233</v>
+        <v>7044015</v>
       </c>
       <c r="S123" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14399,24 +14474,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14427,48 +14492,23 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129292836</v>
+        <v>129303124</v>
       </c>
       <c r="B124" t="n">
         <v>57736</v>
@@ -14497,24 +14537,19 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524162</v>
+        <v>523976</v>
       </c>
       <c r="R124" t="n">
-        <v>7043929</v>
+        <v>7044029</v>
       </c>
       <c r="S124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14541,24 +14576,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14569,41 +14594,16 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -14752,7 +14752,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129303135</v>
+        <v>129303136</v>
       </c>
       <c r="B126" t="n">
         <v>57736</v>
@@ -14787,10 +14787,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523902</v>
+        <v>523897</v>
       </c>
       <c r="R126" t="n">
-        <v>7044288</v>
+        <v>7044281</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14827,7 +14827,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14854,7 +14854,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129303136</v>
+        <v>129303135</v>
       </c>
       <c r="B127" t="n">
         <v>57736</v>
@@ -14889,10 +14889,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523897</v>
+        <v>523902</v>
       </c>
       <c r="R127" t="n">
-        <v>7044281</v>
+        <v>7044288</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15058,7 +15058,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129303087</v>
+        <v>129303133</v>
       </c>
       <c r="B129" t="n">
         <v>57736</v>
@@ -15093,10 +15093,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524219</v>
+        <v>523992</v>
       </c>
       <c r="R129" t="n">
-        <v>7043705</v>
+        <v>7044262</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15133,7 +15133,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15160,7 +15160,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129303133</v>
+        <v>129303081</v>
       </c>
       <c r="B130" t="n">
         <v>57736</v>
@@ -15195,10 +15195,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>523992</v>
+        <v>524190</v>
       </c>
       <c r="R130" t="n">
-        <v>7044262</v>
+        <v>7043804</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15364,7 +15364,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129303081</v>
+        <v>129303087</v>
       </c>
       <c r="B132" t="n">
         <v>57736</v>
@@ -15399,10 +15399,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524190</v>
+        <v>524219</v>
       </c>
       <c r="R132" t="n">
-        <v>7043804</v>
+        <v>7043705</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16562,7 +16562,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129303098</v>
+        <v>129303092</v>
       </c>
       <c r="B141" t="n">
         <v>57736</v>
@@ -16597,10 +16597,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>524297</v>
+        <v>524227</v>
       </c>
       <c r="R141" t="n">
-        <v>7043866</v>
+        <v>7043799</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16637,7 +16637,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16664,7 +16664,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129303093</v>
+        <v>129303148</v>
       </c>
       <c r="B142" t="n">
         <v>57736</v>
@@ -16699,10 +16699,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>524246</v>
+        <v>523952</v>
       </c>
       <c r="R142" t="n">
-        <v>7043787</v>
+        <v>7044072</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16739,7 +16739,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16766,7 +16766,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129303092</v>
+        <v>129303098</v>
       </c>
       <c r="B143" t="n">
         <v>57736</v>
@@ -16801,10 +16801,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>524227</v>
+        <v>524297</v>
       </c>
       <c r="R143" t="n">
-        <v>7043799</v>
+        <v>7043866</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16868,7 +16868,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129303148</v>
+        <v>129303093</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -16903,10 +16903,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>523952</v>
+        <v>524246</v>
       </c>
       <c r="R144" t="n">
-        <v>7044072</v>
+        <v>7043787</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17707,7 +17707,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129303091</v>
+        <v>129303090</v>
       </c>
       <c r="B151" t="n">
         <v>57736</v>
@@ -17742,10 +17742,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>524225</v>
+        <v>524194</v>
       </c>
       <c r="R151" t="n">
-        <v>7043779</v>
+        <v>7043755</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17782,7 +17782,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17809,7 +17809,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129303139</v>
+        <v>129303123</v>
       </c>
       <c r="B152" t="n">
         <v>57736</v>
@@ -17844,10 +17844,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>523860</v>
+        <v>523980</v>
       </c>
       <c r="R152" t="n">
-        <v>7044250</v>
+        <v>7044026</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17884,7 +17884,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17911,7 +17911,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129303123</v>
+        <v>129303091</v>
       </c>
       <c r="B153" t="n">
         <v>57736</v>
@@ -17946,10 +17946,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>523980</v>
+        <v>524225</v>
       </c>
       <c r="R153" t="n">
-        <v>7044026</v>
+        <v>7043779</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18013,7 +18013,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129303090</v>
+        <v>129303096</v>
       </c>
       <c r="B154" t="n">
         <v>57736</v>
@@ -18048,10 +18048,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>524194</v>
+        <v>524226</v>
       </c>
       <c r="R154" t="n">
-        <v>7043755</v>
+        <v>7043829</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18088,7 +18088,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18115,7 +18115,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129303096</v>
+        <v>129303144</v>
       </c>
       <c r="B155" t="n">
         <v>57736</v>
@@ -18150,10 +18150,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>524226</v>
+        <v>523900</v>
       </c>
       <c r="R155" t="n">
-        <v>7043829</v>
+        <v>7044174</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18217,7 +18217,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129303144</v>
+        <v>129303139</v>
       </c>
       <c r="B156" t="n">
         <v>57736</v>
@@ -18252,10 +18252,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>523900</v>
+        <v>523860</v>
       </c>
       <c r="R156" t="n">
-        <v>7044174</v>
+        <v>7044250</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18292,7 +18292,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18319,7 +18319,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129303145</v>
+        <v>129303122</v>
       </c>
       <c r="B157" t="n">
         <v>57736</v>
@@ -18354,10 +18354,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>523898</v>
+        <v>523976</v>
       </c>
       <c r="R157" t="n">
-        <v>7044169</v>
+        <v>7044021</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18421,7 +18421,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129303122</v>
+        <v>129303145</v>
       </c>
       <c r="B158" t="n">
         <v>57736</v>
@@ -18456,10 +18456,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>523976</v>
+        <v>523898</v>
       </c>
       <c r="R158" t="n">
-        <v>7044021</v>
+        <v>7044169</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18496,7 +18496,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18767,7 +18767,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129291995</v>
+        <v>129303119</v>
       </c>
       <c r="B161" t="n">
         <v>57736</v>
@@ -18796,21 +18796,16 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>524225</v>
+        <v>524000</v>
       </c>
       <c r="R161" t="n">
-        <v>7043980</v>
+        <v>7044000</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18840,24 +18835,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18868,41 +18853,16 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
@@ -19113,7 +19073,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129303119</v>
+        <v>129291995</v>
       </c>
       <c r="B164" t="n">
         <v>57736</v>
@@ -19142,16 +19102,21 @@
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>524000</v>
+        <v>524225</v>
       </c>
       <c r="R164" t="n">
-        <v>7044000</v>
+        <v>7043980</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19181,14 +19146,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19199,16 +19174,41 @@
       </c>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -19509,7 +19509,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303117</v>
+        <v>129303094</v>
       </c>
       <c r="B167" t="n">
         <v>57736</v>
@@ -19544,10 +19544,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>524002</v>
+        <v>524244</v>
       </c>
       <c r="R167" t="n">
-        <v>7043990</v>
+        <v>7043795</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19611,7 +19611,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129303094</v>
+        <v>129303117</v>
       </c>
       <c r="B168" t="n">
         <v>57736</v>
@@ -19646,10 +19646,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>524244</v>
+        <v>524002</v>
       </c>
       <c r="R168" t="n">
-        <v>7043795</v>
+        <v>7043990</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19917,7 +19917,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129303113</v>
+        <v>129303130</v>
       </c>
       <c r="B171" t="n">
         <v>57736</v>
@@ -19952,10 +19952,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>524042</v>
+        <v>524087</v>
       </c>
       <c r="R171" t="n">
-        <v>7043944</v>
+        <v>7044036</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20121,7 +20121,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129303142</v>
+        <v>129303113</v>
       </c>
       <c r="B173" t="n">
         <v>57736</v>
@@ -20156,10 +20156,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>523900</v>
+        <v>524042</v>
       </c>
       <c r="R173" t="n">
-        <v>7044204</v>
+        <v>7043944</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20223,7 +20223,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129303105</v>
+        <v>129303109</v>
       </c>
       <c r="B174" t="n">
         <v>57736</v>
@@ -20258,10 +20258,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>524079</v>
+        <v>524053</v>
       </c>
       <c r="R174" t="n">
-        <v>7043891</v>
+        <v>7043923</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20325,7 +20325,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129303109</v>
+        <v>129303105</v>
       </c>
       <c r="B175" t="n">
         <v>57736</v>
@@ -20360,10 +20360,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>524053</v>
+        <v>524079</v>
       </c>
       <c r="R175" t="n">
-        <v>7043923</v>
+        <v>7043891</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20400,7 +20400,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20427,7 +20427,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129303130</v>
+        <v>129303142</v>
       </c>
       <c r="B176" t="n">
         <v>57736</v>
@@ -20462,10 +20462,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>524087</v>
+        <v>523900</v>
       </c>
       <c r="R176" t="n">
-        <v>7044036</v>
+        <v>7044204</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20502,7 +20502,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20671,7 +20671,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129303131</v>
+        <v>129303100</v>
       </c>
       <c r="B178" t="n">
         <v>57736</v>
@@ -20706,10 +20706,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>524059</v>
+        <v>524235</v>
       </c>
       <c r="R178" t="n">
-        <v>7044016</v>
+        <v>7043960</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20773,7 +20773,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129303100</v>
+        <v>129303143</v>
       </c>
       <c r="B179" t="n">
         <v>57736</v>
@@ -20808,10 +20808,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>524235</v>
+        <v>523911</v>
       </c>
       <c r="R179" t="n">
-        <v>7043960</v>
+        <v>7044178</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20848,7 +20848,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20875,7 +20875,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129303143</v>
+        <v>129303112</v>
       </c>
       <c r="B180" t="n">
         <v>57736</v>
@@ -20910,10 +20910,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>523911</v>
+        <v>524044</v>
       </c>
       <c r="R180" t="n">
-        <v>7044178</v>
+        <v>7043935</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20950,7 +20950,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20977,7 +20977,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129303128</v>
+        <v>129303116</v>
       </c>
       <c r="B181" t="n">
         <v>57736</v>
@@ -21012,10 +21012,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>524186</v>
+        <v>524033</v>
       </c>
       <c r="R181" t="n">
-        <v>7043943</v>
+        <v>7043952</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21079,7 +21079,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129303116</v>
+        <v>129303138</v>
       </c>
       <c r="B182" t="n">
         <v>57736</v>
@@ -21114,10 +21114,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>524033</v>
+        <v>523879</v>
       </c>
       <c r="R182" t="n">
-        <v>7043952</v>
+        <v>7044256</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21181,7 +21181,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129303112</v>
+        <v>129303131</v>
       </c>
       <c r="B183" t="n">
         <v>57736</v>
@@ -21216,10 +21216,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>524044</v>
+        <v>524059</v>
       </c>
       <c r="R183" t="n">
-        <v>7043935</v>
+        <v>7044016</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21256,7 +21256,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21283,7 +21283,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129303138</v>
+        <v>129303128</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -21318,10 +21318,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>523879</v>
+        <v>524186</v>
       </c>
       <c r="R184" t="n">
-        <v>7044256</v>
+        <v>7043943</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21358,7 +21358,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21385,7 +21385,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129284399</v>
+        <v>129303147</v>
       </c>
       <c r="B185" t="n">
         <v>57736</v>
@@ -21414,24 +21414,19 @@
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>523878</v>
+        <v>523930</v>
       </c>
       <c r="R185" t="n">
-        <v>7044161</v>
+        <v>7044107</v>
       </c>
       <c r="S185" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21458,24 +21453,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Ringhack, färska och tydliga, på en gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21486,41 +21471,16 @@
       </c>
       <c r="AG185" t="b">
         <v>0</v>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -21629,7 +21589,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129303114</v>
+        <v>129303126</v>
       </c>
       <c r="B187" t="n">
         <v>57736</v>
@@ -21664,10 +21624,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>524041</v>
+        <v>523960</v>
       </c>
       <c r="R187" t="n">
-        <v>7043942</v>
+        <v>7044047</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21704,7 +21664,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21731,7 +21691,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129303147</v>
+        <v>129303114</v>
       </c>
       <c r="B188" t="n">
         <v>57736</v>
@@ -21766,10 +21726,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>523930</v>
+        <v>524041</v>
       </c>
       <c r="R188" t="n">
-        <v>7044107</v>
+        <v>7043942</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21806,7 +21766,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21833,7 +21793,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129303126</v>
+        <v>129284399</v>
       </c>
       <c r="B189" t="n">
         <v>57736</v>
@@ -21862,19 +21822,24 @@
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>523960</v>
+        <v>523878</v>
       </c>
       <c r="R189" t="n">
-        <v>7044047</v>
+        <v>7044161</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21901,14 +21866,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack, färska och tydliga, på en gran.</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21919,16 +21894,41 @@
       </c>
       <c r="AG189" t="b">
         <v>0</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -12920,7 +12920,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129294077</v>
+        <v>129303134</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -12949,24 +12949,19 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>523957</v>
+        <v>523912</v>
       </c>
       <c r="R110" t="n">
-        <v>7044053</v>
+        <v>7044281</v>
       </c>
       <c r="S110" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12993,24 +12988,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13021,48 +13006,23 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129303134</v>
+        <v>129303106</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -13097,10 +13057,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>523912</v>
+        <v>524060</v>
       </c>
       <c r="R111" t="n">
-        <v>7044281</v>
+        <v>7043917</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13137,7 +13097,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13164,7 +13124,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129303106</v>
+        <v>129294077</v>
       </c>
       <c r="B112" t="n">
         <v>57736</v>
@@ -13193,19 +13153,24 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524060</v>
+        <v>523957</v>
       </c>
       <c r="R112" t="n">
-        <v>7043917</v>
+        <v>7044053</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13232,14 +13197,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13250,16 +13225,41 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -13368,7 +13368,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129284656</v>
+        <v>129303107</v>
       </c>
       <c r="B114" t="n">
         <v>57736</v>
@@ -13397,24 +13397,19 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>523856</v>
+        <v>524056</v>
       </c>
       <c r="R114" t="n">
-        <v>7044190</v>
+        <v>7043920</v>
       </c>
       <c r="S114" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13441,24 +13436,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, högt upp på en tall.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13469,48 +13454,23 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129303107</v>
+        <v>129303108</v>
       </c>
       <c r="B115" t="n">
         <v>57736</v>
@@ -13545,10 +13505,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524056</v>
+        <v>524052</v>
       </c>
       <c r="R115" t="n">
-        <v>7043920</v>
+        <v>7043922</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13585,7 +13545,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13714,7 +13674,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129303108</v>
+        <v>129284656</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -13743,19 +13703,24 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524052</v>
+        <v>523856</v>
       </c>
       <c r="R117" t="n">
-        <v>7043922</v>
+        <v>7044190</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13782,14 +13747,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, högt upp på en tall.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13800,16 +13775,41 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -14122,7 +14122,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129286184</v>
+        <v>129303124</v>
       </c>
       <c r="B121" t="n">
         <v>57736</v>
@@ -14151,24 +14151,19 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523842</v>
+        <v>523976</v>
       </c>
       <c r="R121" t="n">
-        <v>7044233</v>
+        <v>7044029</v>
       </c>
       <c r="S121" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14195,24 +14190,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14223,48 +14208,23 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129292836</v>
+        <v>129303129</v>
       </c>
       <c r="B122" t="n">
         <v>57736</v>
@@ -14293,24 +14253,19 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524162</v>
+        <v>524088</v>
       </c>
       <c r="R122" t="n">
-        <v>7043929</v>
+        <v>7044015</v>
       </c>
       <c r="S122" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14337,24 +14292,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14365,48 +14310,23 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129303129</v>
+        <v>129286184</v>
       </c>
       <c r="B123" t="n">
         <v>57736</v>
@@ -14435,19 +14355,24 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>524088</v>
+        <v>523842</v>
       </c>
       <c r="R123" t="n">
-        <v>7044015</v>
+        <v>7044233</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14474,14 +14399,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14492,23 +14427,48 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129303124</v>
+        <v>129292836</v>
       </c>
       <c r="B124" t="n">
         <v>57736</v>
@@ -14537,19 +14497,24 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>523976</v>
+        <v>524162</v>
       </c>
       <c r="R124" t="n">
-        <v>7044029</v>
+        <v>7043929</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14576,14 +14541,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14594,16 +14569,41 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -15058,7 +15058,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129303133</v>
+        <v>129295685</v>
       </c>
       <c r="B129" t="n">
         <v>57736</v>
@@ -15087,16 +15087,21 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>523992</v>
+        <v>524198</v>
       </c>
       <c r="R129" t="n">
-        <v>7044262</v>
+        <v>7043758</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15126,14 +15131,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15144,23 +15159,48 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129303081</v>
+        <v>129285747</v>
       </c>
       <c r="B130" t="n">
         <v>57736</v>
@@ -15189,19 +15229,24 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524190</v>
+        <v>523850</v>
       </c>
       <c r="R130" t="n">
-        <v>7043804</v>
+        <v>7044210</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15228,14 +15273,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15246,23 +15301,48 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129303121</v>
+        <v>129283648</v>
       </c>
       <c r="B131" t="n">
         <v>57736</v>
@@ -15291,16 +15371,21 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>523979</v>
+        <v>523885</v>
       </c>
       <c r="R131" t="n">
-        <v>7044017</v>
+        <v>7044152</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15330,14 +15415,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15348,23 +15443,48 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129303087</v>
+        <v>129285070</v>
       </c>
       <c r="B132" t="n">
         <v>57736</v>
@@ -15393,19 +15513,24 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524219</v>
+        <v>523844</v>
       </c>
       <c r="R132" t="n">
-        <v>7043705</v>
+        <v>7044210</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15432,14 +15557,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15450,23 +15585,48 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129295685</v>
+        <v>129294128</v>
       </c>
       <c r="B133" t="n">
         <v>57736</v>
@@ -15497,19 +15657,19 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524198</v>
+        <v>523987</v>
       </c>
       <c r="R133" t="n">
-        <v>7043758</v>
+        <v>7044025</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15541,7 +15701,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15551,12 +15711,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15608,7 +15768,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129283648</v>
+        <v>129303133</v>
       </c>
       <c r="B134" t="n">
         <v>57736</v>
@@ -15637,21 +15797,16 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>523885</v>
+        <v>523992</v>
       </c>
       <c r="R134" t="n">
-        <v>7044152</v>
+        <v>7044262</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15681,24 +15836,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15709,48 +15854,23 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129285070</v>
+        <v>129303081</v>
       </c>
       <c r="B135" t="n">
         <v>57736</v>
@@ -15779,24 +15899,19 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>523844</v>
+        <v>524190</v>
       </c>
       <c r="R135" t="n">
-        <v>7044210</v>
+        <v>7043804</v>
       </c>
       <c r="S135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15823,24 +15938,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15851,48 +15956,23 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129285747</v>
+        <v>129303121</v>
       </c>
       <c r="B136" t="n">
         <v>57736</v>
@@ -15921,24 +16001,19 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>523850</v>
+        <v>523979</v>
       </c>
       <c r="R136" t="n">
-        <v>7044210</v>
+        <v>7044017</v>
       </c>
       <c r="S136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15965,24 +16040,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15993,48 +16058,23 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129294128</v>
+        <v>129303087</v>
       </c>
       <c r="B137" t="n">
         <v>57736</v>
@@ -16063,21 +16103,16 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>523987</v>
+        <v>524219</v>
       </c>
       <c r="R137" t="n">
-        <v>7044025</v>
+        <v>7043705</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16107,24 +16142,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16135,41 +16160,16 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16970,7 +16970,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129303127</v>
+        <v>129294174</v>
       </c>
       <c r="B145" t="n">
         <v>57736</v>
@@ -16999,19 +16999,24 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>523955</v>
+        <v>523983</v>
       </c>
       <c r="R145" t="n">
-        <v>7044054</v>
+        <v>7044020</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17038,14 +17043,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17056,23 +17071,48 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129303088</v>
+        <v>129303127</v>
       </c>
       <c r="B146" t="n">
         <v>57736</v>
@@ -17107,10 +17147,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>524211</v>
+        <v>523955</v>
       </c>
       <c r="R146" t="n">
-        <v>7043713</v>
+        <v>7044054</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17147,7 +17187,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17174,7 +17214,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129303115</v>
+        <v>129303088</v>
       </c>
       <c r="B147" t="n">
         <v>57736</v>
@@ -17209,10 +17249,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>524039</v>
+        <v>524211</v>
       </c>
       <c r="R147" t="n">
-        <v>7043944</v>
+        <v>7043713</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17249,7 +17289,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17276,7 +17316,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129294174</v>
+        <v>129303115</v>
       </c>
       <c r="B148" t="n">
         <v>57736</v>
@@ -17305,24 +17345,19 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>523983</v>
+        <v>524039</v>
       </c>
       <c r="R148" t="n">
-        <v>7044020</v>
+        <v>7043944</v>
       </c>
       <c r="S148" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17349,24 +17384,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17377,48 +17402,23 @@
       </c>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129290810</v>
+        <v>129303090</v>
       </c>
       <c r="B149" t="n">
         <v>57736</v>
@@ -17447,29 +17447,19 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>524168</v>
+        <v>524194</v>
       </c>
       <c r="R149" t="n">
-        <v>7044054</v>
+        <v>7043755</v>
       </c>
       <c r="S149" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17496,24 +17486,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17524,48 +17504,23 @@
       </c>
       <c r="AG149" t="b">
         <v>0</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129294258</v>
+        <v>129303123</v>
       </c>
       <c r="B150" t="n">
         <v>57736</v>
@@ -17594,24 +17549,19 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>524049</v>
+        <v>523980</v>
       </c>
       <c r="R150" t="n">
-        <v>7043961</v>
+        <v>7044026</v>
       </c>
       <c r="S150" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17638,24 +17588,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17666,48 +17606,23 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129303090</v>
+        <v>129303091</v>
       </c>
       <c r="B151" t="n">
         <v>57736</v>
@@ -17742,10 +17657,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>524194</v>
+        <v>524225</v>
       </c>
       <c r="R151" t="n">
-        <v>7043755</v>
+        <v>7043779</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17782,7 +17697,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17809,7 +17724,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129303123</v>
+        <v>129303139</v>
       </c>
       <c r="B152" t="n">
         <v>57736</v>
@@ -17844,10 +17759,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>523980</v>
+        <v>523860</v>
       </c>
       <c r="R152" t="n">
-        <v>7044026</v>
+        <v>7044250</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17884,7 +17799,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17911,7 +17826,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129303091</v>
+        <v>129303096</v>
       </c>
       <c r="B153" t="n">
         <v>57736</v>
@@ -17946,10 +17861,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>524225</v>
+        <v>524226</v>
       </c>
       <c r="R153" t="n">
-        <v>7043779</v>
+        <v>7043829</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18013,7 +17928,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129303096</v>
+        <v>129303144</v>
       </c>
       <c r="B154" t="n">
         <v>57736</v>
@@ -18048,10 +17963,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>524226</v>
+        <v>523900</v>
       </c>
       <c r="R154" t="n">
-        <v>7043829</v>
+        <v>7044174</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18088,7 +18003,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18115,7 +18030,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129303144</v>
+        <v>129290810</v>
       </c>
       <c r="B155" t="n">
         <v>57736</v>
@@ -18144,19 +18059,29 @@
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>523900</v>
+        <v>524168</v>
       </c>
       <c r="R155" t="n">
-        <v>7044174</v>
+        <v>7044054</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18183,14 +18108,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18201,23 +18136,48 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129303139</v>
+        <v>129294258</v>
       </c>
       <c r="B156" t="n">
         <v>57736</v>
@@ -18246,19 +18206,24 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>523860</v>
+        <v>524049</v>
       </c>
       <c r="R156" t="n">
-        <v>7044250</v>
+        <v>7043961</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18285,14 +18250,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18303,23 +18278,48 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129303122</v>
+        <v>129283727</v>
       </c>
       <c r="B157" t="n">
         <v>57736</v>
@@ -18348,16 +18348,21 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>523976</v>
+        <v>523881</v>
       </c>
       <c r="R157" t="n">
-        <v>7044021</v>
+        <v>7044149</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18387,14 +18392,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, färska, enstaka högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18405,23 +18420,48 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129303145</v>
+        <v>129303122</v>
       </c>
       <c r="B158" t="n">
         <v>57736</v>
@@ -18456,10 +18496,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>523898</v>
+        <v>523976</v>
       </c>
       <c r="R158" t="n">
-        <v>7044169</v>
+        <v>7044021</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18496,7 +18536,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18523,7 +18563,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129303110</v>
+        <v>129303145</v>
       </c>
       <c r="B159" t="n">
         <v>57736</v>
@@ -18558,10 +18598,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>524053</v>
+        <v>523898</v>
       </c>
       <c r="R159" t="n">
-        <v>7043929</v>
+        <v>7044169</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18598,7 +18638,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18625,7 +18665,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129283727</v>
+        <v>129303110</v>
       </c>
       <c r="B160" t="n">
         <v>57736</v>
@@ -18654,21 +18694,16 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>523881</v>
+        <v>524053</v>
       </c>
       <c r="R160" t="n">
-        <v>7044149</v>
+        <v>7043929</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18698,24 +18733,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka högt upp på en gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18726,48 +18751,23 @@
       </c>
       <c r="AG160" t="b">
         <v>0</v>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129303119</v>
+        <v>129291995</v>
       </c>
       <c r="B161" t="n">
         <v>57736</v>
@@ -18796,16 +18796,21 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>524000</v>
+        <v>524225</v>
       </c>
       <c r="R161" t="n">
-        <v>7044000</v>
+        <v>7043980</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18835,14 +18840,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18853,23 +18868,48 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129303095</v>
+        <v>129303119</v>
       </c>
       <c r="B162" t="n">
         <v>57736</v>
@@ -18904,10 +18944,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>524229</v>
+        <v>524000</v>
       </c>
       <c r="R162" t="n">
-        <v>7043821</v>
+        <v>7044000</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18971,7 +19011,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129303082</v>
+        <v>129303095</v>
       </c>
       <c r="B163" t="n">
         <v>57736</v>
@@ -19006,10 +19046,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>524269</v>
+        <v>524229</v>
       </c>
       <c r="R163" t="n">
-        <v>7043735</v>
+        <v>7043821</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19046,7 +19086,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19073,7 +19113,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129291995</v>
+        <v>129303082</v>
       </c>
       <c r="B164" t="n">
         <v>57736</v>
@@ -19102,21 +19142,16 @@
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>524225</v>
+        <v>524269</v>
       </c>
       <c r="R164" t="n">
-        <v>7043980</v>
+        <v>7043735</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19146,24 +19181,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19174,41 +19199,16 @@
       </c>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -20223,7 +20223,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129303109</v>
+        <v>129303142</v>
       </c>
       <c r="B174" t="n">
         <v>57736</v>
@@ -20258,10 +20258,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>524053</v>
+        <v>523900</v>
       </c>
       <c r="R174" t="n">
-        <v>7043923</v>
+        <v>7044204</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20325,7 +20325,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129303105</v>
+        <v>129303109</v>
       </c>
       <c r="B175" t="n">
         <v>57736</v>
@@ -20360,10 +20360,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>524079</v>
+        <v>524053</v>
       </c>
       <c r="R175" t="n">
-        <v>7043891</v>
+        <v>7043923</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20400,7 +20400,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20427,7 +20427,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129303142</v>
+        <v>129303105</v>
       </c>
       <c r="B176" t="n">
         <v>57736</v>
@@ -20462,10 +20462,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>523900</v>
+        <v>524079</v>
       </c>
       <c r="R176" t="n">
-        <v>7044204</v>
+        <v>7043891</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20502,7 +20502,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20529,7 +20529,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129294096</v>
+        <v>129303100</v>
       </c>
       <c r="B177" t="n">
         <v>57736</v>
@@ -20558,24 +20558,19 @@
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>523971</v>
+        <v>524235</v>
       </c>
       <c r="R177" t="n">
-        <v>7044037</v>
+        <v>7043960</v>
       </c>
       <c r="S177" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20602,24 +20597,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20630,48 +20615,23 @@
       </c>
       <c r="AG177" t="b">
         <v>0</v>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129303100</v>
+        <v>129303143</v>
       </c>
       <c r="B178" t="n">
         <v>57736</v>
@@ -20706,10 +20666,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>524235</v>
+        <v>523911</v>
       </c>
       <c r="R178" t="n">
-        <v>7043960</v>
+        <v>7044178</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20746,7 +20706,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20773,7 +20733,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129303143</v>
+        <v>129303112</v>
       </c>
       <c r="B179" t="n">
         <v>57736</v>
@@ -20808,10 +20768,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>523911</v>
+        <v>524044</v>
       </c>
       <c r="R179" t="n">
-        <v>7044178</v>
+        <v>7043935</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20848,7 +20808,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20875,7 +20835,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129303112</v>
+        <v>129303116</v>
       </c>
       <c r="B180" t="n">
         <v>57736</v>
@@ -20910,10 +20870,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>524044</v>
+        <v>524033</v>
       </c>
       <c r="R180" t="n">
-        <v>7043935</v>
+        <v>7043952</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20977,7 +20937,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129303116</v>
+        <v>129303138</v>
       </c>
       <c r="B181" t="n">
         <v>57736</v>
@@ -21012,10 +20972,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>524033</v>
+        <v>523879</v>
       </c>
       <c r="R181" t="n">
-        <v>7043952</v>
+        <v>7044256</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21052,7 +21012,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21079,7 +21039,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129303138</v>
+        <v>129303131</v>
       </c>
       <c r="B182" t="n">
         <v>57736</v>
@@ -21114,10 +21074,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>523879</v>
+        <v>524059</v>
       </c>
       <c r="R182" t="n">
-        <v>7044256</v>
+        <v>7044016</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21181,7 +21141,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129303131</v>
+        <v>129303128</v>
       </c>
       <c r="B183" t="n">
         <v>57736</v>
@@ -21216,10 +21176,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>524059</v>
+        <v>524186</v>
       </c>
       <c r="R183" t="n">
-        <v>7044016</v>
+        <v>7043943</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21256,7 +21216,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21283,7 +21243,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129303128</v>
+        <v>129294096</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -21312,19 +21272,24 @@
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>524186</v>
+        <v>523971</v>
       </c>
       <c r="R184" t="n">
-        <v>7043943</v>
+        <v>7044037</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21351,14 +21316,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21369,16 +21344,41 @@
       </c>
       <c r="AG184" t="b">
         <v>0</v>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -12920,7 +12920,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129303134</v>
+        <v>129294077</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -12949,19 +12949,24 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>523912</v>
+        <v>523957</v>
       </c>
       <c r="R110" t="n">
-        <v>7044281</v>
+        <v>7044053</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12988,14 +12993,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13006,23 +13021,48 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129303106</v>
+        <v>129303134</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -13057,10 +13097,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>524060</v>
+        <v>523912</v>
       </c>
       <c r="R111" t="n">
-        <v>7043917</v>
+        <v>7044281</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13097,7 +13137,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13124,7 +13164,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129294077</v>
+        <v>129303106</v>
       </c>
       <c r="B112" t="n">
         <v>57736</v>
@@ -13153,24 +13193,19 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>523957</v>
+        <v>524060</v>
       </c>
       <c r="R112" t="n">
-        <v>7044053</v>
+        <v>7043917</v>
       </c>
       <c r="S112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13197,24 +13232,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13225,41 +13250,16 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -13368,7 +13368,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129303107</v>
+        <v>129284656</v>
       </c>
       <c r="B114" t="n">
         <v>57736</v>
@@ -13397,19 +13397,24 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>524056</v>
+        <v>523856</v>
       </c>
       <c r="R114" t="n">
-        <v>7043920</v>
+        <v>7044190</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13436,14 +13441,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre, högt upp på en tall.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13454,23 +13469,48 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129303108</v>
+        <v>129303107</v>
       </c>
       <c r="B115" t="n">
         <v>57736</v>
@@ -13505,10 +13545,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524052</v>
+        <v>524056</v>
       </c>
       <c r="R115" t="n">
-        <v>7043922</v>
+        <v>7043920</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13545,7 +13585,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13572,7 +13612,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129303097</v>
+        <v>129303108</v>
       </c>
       <c r="B116" t="n">
         <v>57736</v>
@@ -13607,10 +13647,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524306</v>
+        <v>524052</v>
       </c>
       <c r="R116" t="n">
-        <v>7043867</v>
+        <v>7043922</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13647,7 +13687,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13674,7 +13714,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129284656</v>
+        <v>129303097</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -13703,24 +13743,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>523856</v>
+        <v>524306</v>
       </c>
       <c r="R117" t="n">
-        <v>7044190</v>
+        <v>7043867</v>
       </c>
       <c r="S117" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13747,24 +13782,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, högt upp på en tall.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13775,41 +13800,16 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -14122,7 +14122,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129303124</v>
+        <v>129286184</v>
       </c>
       <c r="B121" t="n">
         <v>57736</v>
@@ -14151,19 +14151,24 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523976</v>
+        <v>523842</v>
       </c>
       <c r="R121" t="n">
-        <v>7044029</v>
+        <v>7044233</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14190,14 +14195,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14208,23 +14223,48 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129303129</v>
+        <v>129292836</v>
       </c>
       <c r="B122" t="n">
         <v>57736</v>
@@ -14253,19 +14293,24 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524088</v>
+        <v>524162</v>
       </c>
       <c r="R122" t="n">
-        <v>7044015</v>
+        <v>7043929</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14292,14 +14337,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14310,23 +14365,48 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129286184</v>
+        <v>129303124</v>
       </c>
       <c r="B123" t="n">
         <v>57736</v>
@@ -14355,24 +14435,19 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>523842</v>
+        <v>523976</v>
       </c>
       <c r="R123" t="n">
-        <v>7044233</v>
+        <v>7044029</v>
       </c>
       <c r="S123" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14399,24 +14474,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14427,48 +14492,23 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129292836</v>
+        <v>129303129</v>
       </c>
       <c r="B124" t="n">
         <v>57736</v>
@@ -14497,24 +14537,19 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524162</v>
+        <v>524088</v>
       </c>
       <c r="R124" t="n">
-        <v>7043929</v>
+        <v>7044015</v>
       </c>
       <c r="S124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14541,24 +14576,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14569,41 +14594,16 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -15200,7 +15200,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129285747</v>
+        <v>129283648</v>
       </c>
       <c r="B130" t="n">
         <v>57736</v>
@@ -15231,7 +15231,7 @@
       <c r="I130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -15240,13 +15240,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>523850</v>
+        <v>523885</v>
       </c>
       <c r="R130" t="n">
-        <v>7044210</v>
+        <v>7044152</v>
       </c>
       <c r="S130" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15285,12 +15285,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15304,7 +15304,7 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
@@ -15342,7 +15342,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129283648</v>
+        <v>129285070</v>
       </c>
       <c r="B131" t="n">
         <v>57736</v>
@@ -15382,13 +15382,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>523885</v>
+        <v>523844</v>
       </c>
       <c r="R131" t="n">
-        <v>7044152</v>
+        <v>7044210</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15427,12 +15427,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
@@ -15484,7 +15484,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129285070</v>
+        <v>129285747</v>
       </c>
       <c r="B132" t="n">
         <v>57736</v>
@@ -15515,7 +15515,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15524,7 +15524,7 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>523844</v>
+        <v>523850</v>
       </c>
       <c r="R132" t="n">
         <v>7044210</v>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15569,12 +15569,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16278,7 +16278,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129295984</v>
+        <v>129303092</v>
       </c>
       <c r="B139" t="n">
         <v>57736</v>
@@ -16307,21 +16307,16 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>524244</v>
+        <v>524227</v>
       </c>
       <c r="R139" t="n">
-        <v>7043732</v>
+        <v>7043799</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16351,24 +16346,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16379,48 +16364,23 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129294143</v>
+        <v>129303148</v>
       </c>
       <c r="B140" t="n">
         <v>57736</v>
@@ -16449,24 +16409,19 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>523985</v>
+        <v>523952</v>
       </c>
       <c r="R140" t="n">
-        <v>7044028</v>
+        <v>7044072</v>
       </c>
       <c r="S140" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16493,24 +16448,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16521,48 +16466,23 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129303092</v>
+        <v>129303098</v>
       </c>
       <c r="B141" t="n">
         <v>57736</v>
@@ -16597,10 +16517,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>524227</v>
+        <v>524297</v>
       </c>
       <c r="R141" t="n">
-        <v>7043799</v>
+        <v>7043866</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16637,7 +16557,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16664,7 +16584,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129303148</v>
+        <v>129303093</v>
       </c>
       <c r="B142" t="n">
         <v>57736</v>
@@ -16699,10 +16619,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>523952</v>
+        <v>524246</v>
       </c>
       <c r="R142" t="n">
-        <v>7044072</v>
+        <v>7043787</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16739,7 +16659,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16766,7 +16686,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129303098</v>
+        <v>129295984</v>
       </c>
       <c r="B143" t="n">
         <v>57736</v>
@@ -16795,16 +16715,21 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>524297</v>
+        <v>524244</v>
       </c>
       <c r="R143" t="n">
-        <v>7043866</v>
+        <v>7043732</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16834,14 +16759,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på gränsen till färska.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16852,23 +16787,48 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129303093</v>
+        <v>129294143</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -16897,19 +16857,24 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>524246</v>
+        <v>523985</v>
       </c>
       <c r="R144" t="n">
-        <v>7043787</v>
+        <v>7044028</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16936,14 +16901,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16954,23 +16929,48 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129294174</v>
+        <v>129303088</v>
       </c>
       <c r="B145" t="n">
         <v>57736</v>
@@ -16999,24 +16999,19 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>523983</v>
+        <v>524211</v>
       </c>
       <c r="R145" t="n">
-        <v>7044020</v>
+        <v>7043713</v>
       </c>
       <c r="S145" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17043,24 +17038,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17071,48 +17056,23 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129303127</v>
+        <v>129303115</v>
       </c>
       <c r="B146" t="n">
         <v>57736</v>
@@ -17147,10 +17107,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>523955</v>
+        <v>524039</v>
       </c>
       <c r="R146" t="n">
-        <v>7044054</v>
+        <v>7043944</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17187,7 +17147,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17214,7 +17174,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129303088</v>
+        <v>129294174</v>
       </c>
       <c r="B147" t="n">
         <v>57736</v>
@@ -17243,19 +17203,24 @@
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>524211</v>
+        <v>523983</v>
       </c>
       <c r="R147" t="n">
-        <v>7043713</v>
+        <v>7044020</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -17282,14 +17247,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17300,23 +17275,48 @@
       </c>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129303115</v>
+        <v>129303127</v>
       </c>
       <c r="B148" t="n">
         <v>57736</v>
@@ -17351,10 +17351,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>524039</v>
+        <v>523955</v>
       </c>
       <c r="R148" t="n">
-        <v>7043944</v>
+        <v>7044054</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18767,7 +18767,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129291995</v>
+        <v>129303095</v>
       </c>
       <c r="B161" t="n">
         <v>57736</v>
@@ -18796,21 +18796,16 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>524225</v>
+        <v>524229</v>
       </c>
       <c r="R161" t="n">
-        <v>7043980</v>
+        <v>7043821</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18840,24 +18835,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18868,48 +18853,23 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129303119</v>
+        <v>129303082</v>
       </c>
       <c r="B162" t="n">
         <v>57736</v>
@@ -18944,10 +18904,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>524000</v>
+        <v>524269</v>
       </c>
       <c r="R162" t="n">
-        <v>7044000</v>
+        <v>7043735</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18984,7 +18944,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19011,7 +18971,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129303095</v>
+        <v>129291995</v>
       </c>
       <c r="B163" t="n">
         <v>57736</v>
@@ -19040,16 +19000,21 @@
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>524229</v>
+        <v>524225</v>
       </c>
       <c r="R163" t="n">
-        <v>7043821</v>
+        <v>7043980</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19079,14 +19044,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19097,23 +19072,48 @@
       </c>
       <c r="AG163" t="b">
         <v>0</v>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129303082</v>
+        <v>129303119</v>
       </c>
       <c r="B164" t="n">
         <v>57736</v>
@@ -19148,10 +19148,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>524269</v>
+        <v>524000</v>
       </c>
       <c r="R164" t="n">
-        <v>7043735</v>
+        <v>7044000</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19188,7 +19188,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19917,7 +19917,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129303130</v>
+        <v>129303113</v>
       </c>
       <c r="B171" t="n">
         <v>57736</v>
@@ -19952,10 +19952,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>524087</v>
+        <v>524042</v>
       </c>
       <c r="R171" t="n">
-        <v>7044036</v>
+        <v>7043944</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20019,7 +20019,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129303104</v>
+        <v>129303142</v>
       </c>
       <c r="B172" t="n">
         <v>57736</v>
@@ -20054,10 +20054,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>524081</v>
+        <v>523900</v>
       </c>
       <c r="R172" t="n">
-        <v>7043892</v>
+        <v>7044204</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20121,7 +20121,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129303113</v>
+        <v>129303109</v>
       </c>
       <c r="B173" t="n">
         <v>57736</v>
@@ -20156,10 +20156,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>524042</v>
+        <v>524053</v>
       </c>
       <c r="R173" t="n">
-        <v>7043944</v>
+        <v>7043923</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20223,7 +20223,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129303142</v>
+        <v>129303130</v>
       </c>
       <c r="B174" t="n">
         <v>57736</v>
@@ -20258,10 +20258,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>523900</v>
+        <v>524087</v>
       </c>
       <c r="R174" t="n">
-        <v>7044204</v>
+        <v>7044036</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20325,7 +20325,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129303109</v>
+        <v>129303104</v>
       </c>
       <c r="B175" t="n">
         <v>57736</v>
@@ -20360,10 +20360,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>524053</v>
+        <v>524081</v>
       </c>
       <c r="R175" t="n">
-        <v>7043923</v>
+        <v>7043892</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20400,7 +20400,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20529,7 +20529,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129303100</v>
+        <v>129294096</v>
       </c>
       <c r="B177" t="n">
         <v>57736</v>
@@ -20558,19 +20558,24 @@
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>524235</v>
+        <v>523971</v>
       </c>
       <c r="R177" t="n">
-        <v>7043960</v>
+        <v>7044037</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20597,14 +20602,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20615,23 +20630,48 @@
       </c>
       <c r="AG177" t="b">
         <v>0</v>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129303143</v>
+        <v>129303100</v>
       </c>
       <c r="B178" t="n">
         <v>57736</v>
@@ -20666,10 +20706,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>523911</v>
+        <v>524235</v>
       </c>
       <c r="R178" t="n">
-        <v>7044178</v>
+        <v>7043960</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20706,7 +20746,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20733,7 +20773,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129303112</v>
+        <v>129303143</v>
       </c>
       <c r="B179" t="n">
         <v>57736</v>
@@ -20768,10 +20808,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>524044</v>
+        <v>523911</v>
       </c>
       <c r="R179" t="n">
-        <v>7043935</v>
+        <v>7044178</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20808,7 +20848,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20835,7 +20875,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129303116</v>
+        <v>129303112</v>
       </c>
       <c r="B180" t="n">
         <v>57736</v>
@@ -20870,10 +20910,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>524033</v>
+        <v>524044</v>
       </c>
       <c r="R180" t="n">
-        <v>7043952</v>
+        <v>7043935</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20937,7 +20977,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129303138</v>
+        <v>129303116</v>
       </c>
       <c r="B181" t="n">
         <v>57736</v>
@@ -20972,10 +21012,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>523879</v>
+        <v>524033</v>
       </c>
       <c r="R181" t="n">
-        <v>7044256</v>
+        <v>7043952</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21012,7 +21052,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21039,7 +21079,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129303131</v>
+        <v>129303138</v>
       </c>
       <c r="B182" t="n">
         <v>57736</v>
@@ -21074,10 +21114,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>524059</v>
+        <v>523879</v>
       </c>
       <c r="R182" t="n">
-        <v>7044016</v>
+        <v>7044256</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21141,7 +21181,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129303128</v>
+        <v>129303131</v>
       </c>
       <c r="B183" t="n">
         <v>57736</v>
@@ -21176,10 +21216,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>524186</v>
+        <v>524059</v>
       </c>
       <c r="R183" t="n">
-        <v>7043943</v>
+        <v>7044016</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21216,7 +21256,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21243,7 +21283,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129294096</v>
+        <v>129303128</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -21272,24 +21312,19 @@
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>523971</v>
+        <v>524186</v>
       </c>
       <c r="R184" t="n">
-        <v>7044037</v>
+        <v>7043943</v>
       </c>
       <c r="S184" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21316,24 +21351,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21344,48 +21369,23 @@
       </c>
       <c r="AG184" t="b">
         <v>0</v>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129303147</v>
+        <v>129284399</v>
       </c>
       <c r="B185" t="n">
         <v>57736</v>
@@ -21414,19 +21414,24 @@
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>523930</v>
+        <v>523878</v>
       </c>
       <c r="R185" t="n">
-        <v>7044107</v>
+        <v>7044161</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21453,14 +21458,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska och tydliga, på en gran.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21471,23 +21486,48 @@
       </c>
       <c r="AG185" t="b">
         <v>0</v>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129303146</v>
+        <v>129303147</v>
       </c>
       <c r="B186" t="n">
         <v>57736</v>
@@ -21522,10 +21562,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>523926</v>
+        <v>523930</v>
       </c>
       <c r="R186" t="n">
-        <v>7044118</v>
+        <v>7044107</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21562,7 +21602,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21589,7 +21629,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129303126</v>
+        <v>129303146</v>
       </c>
       <c r="B187" t="n">
         <v>57736</v>
@@ -21624,10 +21664,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>523960</v>
+        <v>523926</v>
       </c>
       <c r="R187" t="n">
-        <v>7044047</v>
+        <v>7044118</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21664,7 +21704,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21691,7 +21731,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129303114</v>
+        <v>129303126</v>
       </c>
       <c r="B188" t="n">
         <v>57736</v>
@@ -21726,10 +21766,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>524041</v>
+        <v>523960</v>
       </c>
       <c r="R188" t="n">
-        <v>7043942</v>
+        <v>7044047</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21766,7 +21806,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21793,7 +21833,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129284399</v>
+        <v>129303114</v>
       </c>
       <c r="B189" t="n">
         <v>57736</v>
@@ -21822,24 +21862,19 @@
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>523878</v>
+        <v>524041</v>
       </c>
       <c r="R189" t="n">
-        <v>7044161</v>
+        <v>7043942</v>
       </c>
       <c r="S189" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21866,24 +21901,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Ringhack, färska och tydliga, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21894,41 +21919,16 @@
       </c>
       <c r="AG189" t="b">
         <v>0</v>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO189" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -22179,7 +22179,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129284163</v>
+        <v>129303141</v>
       </c>
       <c r="B192" t="n">
         <v>57736</v>
@@ -22208,24 +22208,19 @@
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>523881</v>
+        <v>523902</v>
       </c>
       <c r="R192" t="n">
-        <v>7044157</v>
+        <v>7044224</v>
       </c>
       <c r="S192" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22252,24 +22247,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22280,48 +22265,23 @@
       </c>
       <c r="AG192" t="b">
         <v>0</v>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129296040</v>
+        <v>129303140</v>
       </c>
       <c r="B193" t="n">
         <v>57736</v>
@@ -22350,21 +22310,16 @@
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>524232</v>
+        <v>523866</v>
       </c>
       <c r="R193" t="n">
-        <v>7043714</v>
+        <v>7044256</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22394,24 +22349,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22422,48 +22367,23 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO193" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129303141</v>
+        <v>129284163</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -22492,19 +22412,24 @@
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>523902</v>
+        <v>523881</v>
       </c>
       <c r="R194" t="n">
-        <v>7044224</v>
+        <v>7044157</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22531,14 +22456,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22549,23 +22484,48 @@
       </c>
       <c r="AG194" t="b">
         <v>0</v>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129303140</v>
+        <v>129296040</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -22594,16 +22554,21 @@
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>523866</v>
+        <v>524232</v>
       </c>
       <c r="R195" t="n">
-        <v>7044256</v>
+        <v>7043714</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22633,14 +22598,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22651,16 +22626,41 @@
       </c>
       <c r="AG195" t="b">
         <v>0</v>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -13062,7 +13062,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129303134</v>
+        <v>129303106</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>523912</v>
+        <v>524060</v>
       </c>
       <c r="R111" t="n">
-        <v>7044281</v>
+        <v>7043917</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13164,7 +13164,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129303106</v>
+        <v>129303134</v>
       </c>
       <c r="B112" t="n">
         <v>57736</v>
@@ -13199,10 +13199,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524060</v>
+        <v>523912</v>
       </c>
       <c r="R112" t="n">
-        <v>7043917</v>
+        <v>7044281</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13239,7 +13239,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13368,7 +13368,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129284656</v>
+        <v>129303107</v>
       </c>
       <c r="B114" t="n">
         <v>57736</v>
@@ -13397,24 +13397,19 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>523856</v>
+        <v>524056</v>
       </c>
       <c r="R114" t="n">
-        <v>7044190</v>
+        <v>7043920</v>
       </c>
       <c r="S114" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13441,24 +13436,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, högt upp på en tall.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13469,48 +13454,23 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129303107</v>
+        <v>129303108</v>
       </c>
       <c r="B115" t="n">
         <v>57736</v>
@@ -13545,10 +13505,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524056</v>
+        <v>524052</v>
       </c>
       <c r="R115" t="n">
-        <v>7043920</v>
+        <v>7043922</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13585,7 +13545,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13612,7 +13572,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129303108</v>
+        <v>129303097</v>
       </c>
       <c r="B116" t="n">
         <v>57736</v>
@@ -13647,10 +13607,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524052</v>
+        <v>524306</v>
       </c>
       <c r="R116" t="n">
-        <v>7043922</v>
+        <v>7043867</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13687,7 +13647,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13714,7 +13674,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129303097</v>
+        <v>129284656</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -13743,19 +13703,24 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524306</v>
+        <v>523856</v>
       </c>
       <c r="R117" t="n">
-        <v>7043867</v>
+        <v>7044190</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13782,14 +13747,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, högt upp på en tall.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13800,16 +13775,41 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13918,7 +13918,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129303120</v>
+        <v>129303118</v>
       </c>
       <c r="B119" t="n">
         <v>57736</v>
@@ -13953,10 +13953,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>523983</v>
+        <v>524000</v>
       </c>
       <c r="R119" t="n">
-        <v>7044011</v>
+        <v>7043995</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13993,7 +13993,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14020,7 +14020,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129303118</v>
+        <v>129303120</v>
       </c>
       <c r="B120" t="n">
         <v>57736</v>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524000</v>
+        <v>523983</v>
       </c>
       <c r="R120" t="n">
-        <v>7043995</v>
+        <v>7044011</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14752,7 +14752,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129303136</v>
+        <v>129303135</v>
       </c>
       <c r="B126" t="n">
         <v>57736</v>
@@ -14787,10 +14787,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523897</v>
+        <v>523902</v>
       </c>
       <c r="R126" t="n">
-        <v>7044281</v>
+        <v>7044288</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14827,7 +14827,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14854,7 +14854,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129303135</v>
+        <v>129303136</v>
       </c>
       <c r="B127" t="n">
         <v>57736</v>
@@ -14889,10 +14889,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523902</v>
+        <v>523897</v>
       </c>
       <c r="R127" t="n">
-        <v>7044288</v>
+        <v>7044281</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15768,7 +15768,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129303133</v>
+        <v>129303087</v>
       </c>
       <c r="B134" t="n">
         <v>57736</v>
@@ -15803,10 +15803,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>523992</v>
+        <v>524219</v>
       </c>
       <c r="R134" t="n">
-        <v>7044262</v>
+        <v>7043705</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15843,7 +15843,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15870,7 +15870,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129303081</v>
+        <v>129303133</v>
       </c>
       <c r="B135" t="n">
         <v>57736</v>
@@ -15905,10 +15905,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524190</v>
+        <v>523992</v>
       </c>
       <c r="R135" t="n">
-        <v>7043804</v>
+        <v>7044262</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16074,7 +16074,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129303087</v>
+        <v>129303081</v>
       </c>
       <c r="B137" t="n">
         <v>57736</v>
@@ -16109,10 +16109,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>524219</v>
+        <v>524190</v>
       </c>
       <c r="R137" t="n">
-        <v>7043705</v>
+        <v>7043804</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16149,7 +16149,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16278,7 +16278,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129303092</v>
+        <v>129295984</v>
       </c>
       <c r="B139" t="n">
         <v>57736</v>
@@ -16307,16 +16307,21 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>524227</v>
+        <v>524244</v>
       </c>
       <c r="R139" t="n">
-        <v>7043799</v>
+        <v>7043732</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16346,14 +16351,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på gränsen till färska.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16364,23 +16379,48 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129303148</v>
+        <v>129294143</v>
       </c>
       <c r="B140" t="n">
         <v>57736</v>
@@ -16409,19 +16449,24 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>523952</v>
+        <v>523985</v>
       </c>
       <c r="R140" t="n">
-        <v>7044072</v>
+        <v>7044028</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16448,14 +16493,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16466,16 +16521,41 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -16686,7 +16766,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129295984</v>
+        <v>129303092</v>
       </c>
       <c r="B143" t="n">
         <v>57736</v>
@@ -16715,21 +16795,16 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>524244</v>
+        <v>524227</v>
       </c>
       <c r="R143" t="n">
-        <v>7043732</v>
+        <v>7043799</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16759,24 +16834,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16787,48 +16852,23 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129294143</v>
+        <v>129303148</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -16857,24 +16897,19 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>523985</v>
+        <v>523952</v>
       </c>
       <c r="R144" t="n">
-        <v>7044028</v>
+        <v>7044072</v>
       </c>
       <c r="S144" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16901,24 +16936,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16929,48 +16954,23 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129303088</v>
+        <v>129303127</v>
       </c>
       <c r="B145" t="n">
         <v>57736</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>524211</v>
+        <v>523955</v>
       </c>
       <c r="R145" t="n">
-        <v>7043713</v>
+        <v>7044054</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17072,7 +17072,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129303115</v>
+        <v>129303088</v>
       </c>
       <c r="B146" t="n">
         <v>57736</v>
@@ -17107,10 +17107,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>524039</v>
+        <v>524211</v>
       </c>
       <c r="R146" t="n">
-        <v>7043944</v>
+        <v>7043713</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17174,7 +17174,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129294174</v>
+        <v>129303115</v>
       </c>
       <c r="B147" t="n">
         <v>57736</v>
@@ -17203,24 +17203,19 @@
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>523983</v>
+        <v>524039</v>
       </c>
       <c r="R147" t="n">
-        <v>7044020</v>
+        <v>7043944</v>
       </c>
       <c r="S147" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -17247,24 +17242,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17275,48 +17260,23 @@
       </c>
       <c r="AG147" t="b">
         <v>0</v>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129303127</v>
+        <v>129294174</v>
       </c>
       <c r="B148" t="n">
         <v>57736</v>
@@ -17345,19 +17305,24 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>523955</v>
+        <v>523983</v>
       </c>
       <c r="R148" t="n">
-        <v>7044054</v>
+        <v>7044020</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17384,14 +17349,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17402,23 +17377,48 @@
       </c>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129303090</v>
+        <v>129290810</v>
       </c>
       <c r="B149" t="n">
         <v>57736</v>
@@ -17447,19 +17447,29 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>524194</v>
+        <v>524168</v>
       </c>
       <c r="R149" t="n">
-        <v>7043755</v>
+        <v>7044054</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17486,14 +17496,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17504,23 +17524,48 @@
       </c>
       <c r="AG149" t="b">
         <v>0</v>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129303123</v>
+        <v>129294258</v>
       </c>
       <c r="B150" t="n">
         <v>57736</v>
@@ -17549,19 +17594,24 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>523980</v>
+        <v>524049</v>
       </c>
       <c r="R150" t="n">
-        <v>7044026</v>
+        <v>7043961</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17588,14 +17638,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17606,16 +17666,41 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -17826,7 +17911,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129303096</v>
+        <v>129303123</v>
       </c>
       <c r="B153" t="n">
         <v>57736</v>
@@ -17861,10 +17946,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>524226</v>
+        <v>523980</v>
       </c>
       <c r="R153" t="n">
-        <v>7043829</v>
+        <v>7044026</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17901,7 +17986,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17928,7 +18013,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129303144</v>
+        <v>129303090</v>
       </c>
       <c r="B154" t="n">
         <v>57736</v>
@@ -17963,10 +18048,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>523900</v>
+        <v>524194</v>
       </c>
       <c r="R154" t="n">
-        <v>7044174</v>
+        <v>7043755</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18003,7 +18088,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18030,7 +18115,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129290810</v>
+        <v>129303096</v>
       </c>
       <c r="B155" t="n">
         <v>57736</v>
@@ -18059,29 +18144,19 @@
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>524168</v>
+        <v>524226</v>
       </c>
       <c r="R155" t="n">
-        <v>7044054</v>
+        <v>7043829</v>
       </c>
       <c r="S155" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18108,24 +18183,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18136,48 +18201,23 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129294258</v>
+        <v>129303144</v>
       </c>
       <c r="B156" t="n">
         <v>57736</v>
@@ -18206,24 +18246,19 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>524049</v>
+        <v>523900</v>
       </c>
       <c r="R156" t="n">
-        <v>7043961</v>
+        <v>7044174</v>
       </c>
       <c r="S156" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18250,24 +18285,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18278,48 +18303,23 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129283727</v>
+        <v>129303145</v>
       </c>
       <c r="B157" t="n">
         <v>57736</v>
@@ -18348,21 +18348,16 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>523881</v>
+        <v>523898</v>
       </c>
       <c r="R157" t="n">
-        <v>7044149</v>
+        <v>7044169</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18392,24 +18387,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka högt upp på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18420,41 +18405,16 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -18563,7 +18523,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129303145</v>
+        <v>129303110</v>
       </c>
       <c r="B159" t="n">
         <v>57736</v>
@@ -18598,10 +18558,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>523898</v>
+        <v>524053</v>
       </c>
       <c r="R159" t="n">
-        <v>7044169</v>
+        <v>7043929</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18638,7 +18598,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18665,7 +18625,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129303110</v>
+        <v>129283727</v>
       </c>
       <c r="B160" t="n">
         <v>57736</v>
@@ -18694,16 +18654,21 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>524053</v>
+        <v>523881</v>
       </c>
       <c r="R160" t="n">
-        <v>7043929</v>
+        <v>7044149</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18733,14 +18698,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, färska, enstaka högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18751,23 +18726,48 @@
       </c>
       <c r="AG160" t="b">
         <v>0</v>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129303095</v>
+        <v>129291995</v>
       </c>
       <c r="B161" t="n">
         <v>57736</v>
@@ -18796,16 +18796,21 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>524229</v>
+        <v>524225</v>
       </c>
       <c r="R161" t="n">
-        <v>7043821</v>
+        <v>7043980</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18835,14 +18840,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18853,23 +18868,48 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129303082</v>
+        <v>129303095</v>
       </c>
       <c r="B162" t="n">
         <v>57736</v>
@@ -18904,10 +18944,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>524269</v>
+        <v>524229</v>
       </c>
       <c r="R162" t="n">
-        <v>7043735</v>
+        <v>7043821</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18944,7 +18984,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18971,7 +19011,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129291995</v>
+        <v>129303082</v>
       </c>
       <c r="B163" t="n">
         <v>57736</v>
@@ -19000,21 +19040,16 @@
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>524225</v>
+        <v>524269</v>
       </c>
       <c r="R163" t="n">
-        <v>7043980</v>
+        <v>7043735</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19044,24 +19079,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19072,41 +19097,16 @@
       </c>
       <c r="AG163" t="b">
         <v>0</v>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM163" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -19509,7 +19509,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303094</v>
+        <v>129303117</v>
       </c>
       <c r="B167" t="n">
         <v>57736</v>
@@ -19544,10 +19544,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>524244</v>
+        <v>524002</v>
       </c>
       <c r="R167" t="n">
-        <v>7043795</v>
+        <v>7043990</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19611,7 +19611,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129303117</v>
+        <v>129303094</v>
       </c>
       <c r="B168" t="n">
         <v>57736</v>
@@ -19646,10 +19646,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>524002</v>
+        <v>524244</v>
       </c>
       <c r="R168" t="n">
-        <v>7043990</v>
+        <v>7043795</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20019,7 +20019,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129303142</v>
+        <v>129303104</v>
       </c>
       <c r="B172" t="n">
         <v>57736</v>
@@ -20054,10 +20054,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>523900</v>
+        <v>524081</v>
       </c>
       <c r="R172" t="n">
-        <v>7044204</v>
+        <v>7043892</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20121,7 +20121,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129303109</v>
+        <v>129303142</v>
       </c>
       <c r="B173" t="n">
         <v>57736</v>
@@ -20156,10 +20156,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>524053</v>
+        <v>523900</v>
       </c>
       <c r="R173" t="n">
-        <v>7043923</v>
+        <v>7044204</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20223,7 +20223,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129303130</v>
+        <v>129303105</v>
       </c>
       <c r="B174" t="n">
         <v>57736</v>
@@ -20258,10 +20258,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>524087</v>
+        <v>524079</v>
       </c>
       <c r="R174" t="n">
-        <v>7044036</v>
+        <v>7043891</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20325,7 +20325,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129303104</v>
+        <v>129303109</v>
       </c>
       <c r="B175" t="n">
         <v>57736</v>
@@ -20360,10 +20360,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>524081</v>
+        <v>524053</v>
       </c>
       <c r="R175" t="n">
-        <v>7043892</v>
+        <v>7043923</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20400,7 +20400,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20427,7 +20427,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129303105</v>
+        <v>129303130</v>
       </c>
       <c r="B176" t="n">
         <v>57736</v>
@@ -20462,10 +20462,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>524079</v>
+        <v>524087</v>
       </c>
       <c r="R176" t="n">
-        <v>7043891</v>
+        <v>7044036</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20502,7 +20502,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20671,7 +20671,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129303100</v>
+        <v>129303131</v>
       </c>
       <c r="B178" t="n">
         <v>57736</v>
@@ -20706,10 +20706,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>524235</v>
+        <v>524059</v>
       </c>
       <c r="R178" t="n">
-        <v>7043960</v>
+        <v>7044016</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20773,7 +20773,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129303143</v>
+        <v>129303100</v>
       </c>
       <c r="B179" t="n">
         <v>57736</v>
@@ -20808,10 +20808,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>523911</v>
+        <v>524235</v>
       </c>
       <c r="R179" t="n">
-        <v>7044178</v>
+        <v>7043960</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20848,7 +20848,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20875,7 +20875,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129303112</v>
+        <v>129303143</v>
       </c>
       <c r="B180" t="n">
         <v>57736</v>
@@ -20910,10 +20910,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>524044</v>
+        <v>523911</v>
       </c>
       <c r="R180" t="n">
-        <v>7043935</v>
+        <v>7044178</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20950,7 +20950,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20977,7 +20977,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129303116</v>
+        <v>129303128</v>
       </c>
       <c r="B181" t="n">
         <v>57736</v>
@@ -21012,10 +21012,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>524033</v>
+        <v>524186</v>
       </c>
       <c r="R181" t="n">
-        <v>7043952</v>
+        <v>7043943</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21079,7 +21079,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129303138</v>
+        <v>129303116</v>
       </c>
       <c r="B182" t="n">
         <v>57736</v>
@@ -21114,10 +21114,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>523879</v>
+        <v>524033</v>
       </c>
       <c r="R182" t="n">
-        <v>7044256</v>
+        <v>7043952</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21181,7 +21181,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129303131</v>
+        <v>129303112</v>
       </c>
       <c r="B183" t="n">
         <v>57736</v>
@@ -21216,10 +21216,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>524059</v>
+        <v>524044</v>
       </c>
       <c r="R183" t="n">
-        <v>7044016</v>
+        <v>7043935</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21256,7 +21256,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21283,7 +21283,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129303128</v>
+        <v>129303138</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -21318,10 +21318,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>524186</v>
+        <v>523879</v>
       </c>
       <c r="R184" t="n">
-        <v>7043943</v>
+        <v>7044256</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21358,7 +21358,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21527,7 +21527,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129303147</v>
+        <v>129303146</v>
       </c>
       <c r="B186" t="n">
         <v>57736</v>
@@ -21562,10 +21562,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>523930</v>
+        <v>523926</v>
       </c>
       <c r="R186" t="n">
-        <v>7044107</v>
+        <v>7044118</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21602,7 +21602,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21629,7 +21629,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129303146</v>
+        <v>129303114</v>
       </c>
       <c r="B187" t="n">
         <v>57736</v>
@@ -21664,10 +21664,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>523926</v>
+        <v>524041</v>
       </c>
       <c r="R187" t="n">
-        <v>7044118</v>
+        <v>7043942</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21704,7 +21704,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21731,7 +21731,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129303126</v>
+        <v>129303147</v>
       </c>
       <c r="B188" t="n">
         <v>57736</v>
@@ -21766,10 +21766,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>523960</v>
+        <v>523930</v>
       </c>
       <c r="R188" t="n">
-        <v>7044047</v>
+        <v>7044107</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21806,7 +21806,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21833,7 +21833,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129303114</v>
+        <v>129303126</v>
       </c>
       <c r="B189" t="n">
         <v>57736</v>
@@ -21868,10 +21868,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>524041</v>
+        <v>523960</v>
       </c>
       <c r="R189" t="n">
-        <v>7043942</v>
+        <v>7044047</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21908,7 +21908,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -13062,7 +13062,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129303106</v>
+        <v>129303134</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>524060</v>
+        <v>523912</v>
       </c>
       <c r="R111" t="n">
-        <v>7043917</v>
+        <v>7044281</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13164,7 +13164,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129303134</v>
+        <v>129303106</v>
       </c>
       <c r="B112" t="n">
         <v>57736</v>
@@ -13199,10 +13199,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>523912</v>
+        <v>524060</v>
       </c>
       <c r="R112" t="n">
-        <v>7044281</v>
+        <v>7043917</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13239,7 +13239,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13368,7 +13368,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129303107</v>
+        <v>129284656</v>
       </c>
       <c r="B114" t="n">
         <v>57736</v>
@@ -13397,19 +13397,24 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>524056</v>
+        <v>523856</v>
       </c>
       <c r="R114" t="n">
-        <v>7043920</v>
+        <v>7044190</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13436,14 +13441,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre, högt upp på en tall.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13454,23 +13469,48 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129303108</v>
+        <v>129303107</v>
       </c>
       <c r="B115" t="n">
         <v>57736</v>
@@ -13505,10 +13545,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524052</v>
+        <v>524056</v>
       </c>
       <c r="R115" t="n">
-        <v>7043922</v>
+        <v>7043920</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13545,7 +13585,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13572,7 +13612,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129303097</v>
+        <v>129303108</v>
       </c>
       <c r="B116" t="n">
         <v>57736</v>
@@ -13607,10 +13647,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524306</v>
+        <v>524052</v>
       </c>
       <c r="R116" t="n">
-        <v>7043867</v>
+        <v>7043922</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13647,7 +13687,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13674,7 +13714,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129284656</v>
+        <v>129303097</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -13703,24 +13743,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>523856</v>
+        <v>524306</v>
       </c>
       <c r="R117" t="n">
-        <v>7044190</v>
+        <v>7043867</v>
       </c>
       <c r="S117" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13747,24 +13782,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, högt upp på en tall.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13775,41 +13800,16 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13918,7 +13918,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129303118</v>
+        <v>129303120</v>
       </c>
       <c r="B119" t="n">
         <v>57736</v>
@@ -13953,10 +13953,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524000</v>
+        <v>523983</v>
       </c>
       <c r="R119" t="n">
-        <v>7043995</v>
+        <v>7044011</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13993,7 +13993,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14020,7 +14020,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129303120</v>
+        <v>129303118</v>
       </c>
       <c r="B120" t="n">
         <v>57736</v>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>523983</v>
+        <v>524000</v>
       </c>
       <c r="R120" t="n">
-        <v>7044011</v>
+        <v>7043995</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14610,7 +14610,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129290167</v>
+        <v>129303136</v>
       </c>
       <c r="B125" t="n">
         <v>57736</v>
@@ -14639,21 +14639,16 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>524109</v>
+        <v>523897</v>
       </c>
       <c r="R125" t="n">
-        <v>7044093</v>
+        <v>7044281</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14683,24 +14678,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14711,41 +14696,16 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -14854,7 +14814,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129303136</v>
+        <v>129303111</v>
       </c>
       <c r="B127" t="n">
         <v>57736</v>
@@ -14889,10 +14849,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523897</v>
+        <v>524047</v>
       </c>
       <c r="R127" t="n">
-        <v>7044281</v>
+        <v>7043931</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14956,7 +14916,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129303111</v>
+        <v>129290167</v>
       </c>
       <c r="B128" t="n">
         <v>57736</v>
@@ -14985,16 +14945,21 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>524047</v>
+        <v>524109</v>
       </c>
       <c r="R128" t="n">
-        <v>7043931</v>
+        <v>7044093</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15024,14 +14989,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gammal gran.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15042,23 +15017,48 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129295685</v>
+        <v>129303133</v>
       </c>
       <c r="B129" t="n">
         <v>57736</v>
@@ -15087,21 +15087,16 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524198</v>
+        <v>523992</v>
       </c>
       <c r="R129" t="n">
-        <v>7043758</v>
+        <v>7044262</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15131,24 +15126,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15159,48 +15144,23 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129283648</v>
+        <v>129303081</v>
       </c>
       <c r="B130" t="n">
         <v>57736</v>
@@ -15229,21 +15189,16 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>523885</v>
+        <v>524190</v>
       </c>
       <c r="R130" t="n">
-        <v>7044152</v>
+        <v>7043804</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15273,24 +15228,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15301,48 +15246,23 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129285070</v>
+        <v>129303121</v>
       </c>
       <c r="B131" t="n">
         <v>57736</v>
@@ -15371,24 +15291,19 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>523844</v>
+        <v>523979</v>
       </c>
       <c r="R131" t="n">
-        <v>7044210</v>
+        <v>7044017</v>
       </c>
       <c r="S131" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15415,24 +15330,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15443,48 +15348,23 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129285747</v>
+        <v>129303087</v>
       </c>
       <c r="B132" t="n">
         <v>57736</v>
@@ -15513,24 +15393,19 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>523850</v>
+        <v>524219</v>
       </c>
       <c r="R132" t="n">
-        <v>7044210</v>
+        <v>7043705</v>
       </c>
       <c r="S132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15557,24 +15432,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15585,48 +15450,23 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129294128</v>
+        <v>129295685</v>
       </c>
       <c r="B133" t="n">
         <v>57736</v>
@@ -15657,19 +15497,19 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>523987</v>
+        <v>524198</v>
       </c>
       <c r="R133" t="n">
-        <v>7044025</v>
+        <v>7043758</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15701,7 +15541,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15711,12 +15551,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15768,7 +15608,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129303087</v>
+        <v>129283648</v>
       </c>
       <c r="B134" t="n">
         <v>57736</v>
@@ -15797,16 +15637,21 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524219</v>
+        <v>523885</v>
       </c>
       <c r="R134" t="n">
-        <v>7043705</v>
+        <v>7044152</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15836,14 +15681,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15854,23 +15709,48 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129303133</v>
+        <v>129285070</v>
       </c>
       <c r="B135" t="n">
         <v>57736</v>
@@ -15899,19 +15779,24 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>523992</v>
+        <v>523844</v>
       </c>
       <c r="R135" t="n">
-        <v>7044262</v>
+        <v>7044210</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15938,14 +15823,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15956,23 +15851,48 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129303121</v>
+        <v>129285747</v>
       </c>
       <c r="B136" t="n">
         <v>57736</v>
@@ -16001,19 +15921,24 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>523979</v>
+        <v>523850</v>
       </c>
       <c r="R136" t="n">
-        <v>7044017</v>
+        <v>7044210</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16040,14 +15965,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16058,23 +15993,48 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129303081</v>
+        <v>129294128</v>
       </c>
       <c r="B137" t="n">
         <v>57736</v>
@@ -16103,16 +16063,21 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>524190</v>
+        <v>523987</v>
       </c>
       <c r="R137" t="n">
-        <v>7043804</v>
+        <v>7044025</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16142,14 +16107,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16160,16 +16135,41 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16278,7 +16278,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129295984</v>
+        <v>129303092</v>
       </c>
       <c r="B139" t="n">
         <v>57736</v>
@@ -16307,21 +16307,16 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>524244</v>
+        <v>524227</v>
       </c>
       <c r="R139" t="n">
-        <v>7043732</v>
+        <v>7043799</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16351,24 +16346,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16379,48 +16364,23 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129294143</v>
+        <v>129303148</v>
       </c>
       <c r="B140" t="n">
         <v>57736</v>
@@ -16449,24 +16409,19 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>523985</v>
+        <v>523952</v>
       </c>
       <c r="R140" t="n">
-        <v>7044028</v>
+        <v>7044072</v>
       </c>
       <c r="S140" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16493,24 +16448,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16521,41 +16466,16 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -16766,7 +16686,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129303092</v>
+        <v>129295984</v>
       </c>
       <c r="B143" t="n">
         <v>57736</v>
@@ -16795,16 +16715,21 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>524227</v>
+        <v>524244</v>
       </c>
       <c r="R143" t="n">
-        <v>7043799</v>
+        <v>7043732</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16834,14 +16759,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på gränsen till färska.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16852,23 +16787,48 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129303148</v>
+        <v>129294143</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -16897,19 +16857,24 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>523952</v>
+        <v>523985</v>
       </c>
       <c r="R144" t="n">
-        <v>7044072</v>
+        <v>7044028</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16936,14 +16901,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16954,23 +16929,48 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129303127</v>
+        <v>129294174</v>
       </c>
       <c r="B145" t="n">
         <v>57736</v>
@@ -16999,19 +16999,24 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>523955</v>
+        <v>523983</v>
       </c>
       <c r="R145" t="n">
-        <v>7044054</v>
+        <v>7044020</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17038,14 +17043,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17056,23 +17071,48 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129303088</v>
+        <v>129303127</v>
       </c>
       <c r="B146" t="n">
         <v>57736</v>
@@ -17107,10 +17147,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>524211</v>
+        <v>523955</v>
       </c>
       <c r="R146" t="n">
-        <v>7043713</v>
+        <v>7044054</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17147,7 +17187,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17174,7 +17214,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129303115</v>
+        <v>129303088</v>
       </c>
       <c r="B147" t="n">
         <v>57736</v>
@@ -17209,10 +17249,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>524039</v>
+        <v>524211</v>
       </c>
       <c r="R147" t="n">
-        <v>7043944</v>
+        <v>7043713</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17249,7 +17289,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17276,7 +17316,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129294174</v>
+        <v>129303115</v>
       </c>
       <c r="B148" t="n">
         <v>57736</v>
@@ -17305,24 +17345,19 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>523983</v>
+        <v>524039</v>
       </c>
       <c r="R148" t="n">
-        <v>7044020</v>
+        <v>7043944</v>
       </c>
       <c r="S148" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17349,24 +17384,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17377,48 +17402,23 @@
       </c>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129290810</v>
+        <v>129303090</v>
       </c>
       <c r="B149" t="n">
         <v>57736</v>
@@ -17447,29 +17447,19 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>524168</v>
+        <v>524194</v>
       </c>
       <c r="R149" t="n">
-        <v>7044054</v>
+        <v>7043755</v>
       </c>
       <c r="S149" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17496,24 +17486,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17524,48 +17504,23 @@
       </c>
       <c r="AG149" t="b">
         <v>0</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129294258</v>
+        <v>129303123</v>
       </c>
       <c r="B150" t="n">
         <v>57736</v>
@@ -17594,24 +17549,19 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>524049</v>
+        <v>523980</v>
       </c>
       <c r="R150" t="n">
-        <v>7043961</v>
+        <v>7044026</v>
       </c>
       <c r="S150" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17638,24 +17588,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17666,41 +17606,16 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -17911,7 +17826,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129303123</v>
+        <v>129303096</v>
       </c>
       <c r="B153" t="n">
         <v>57736</v>
@@ -17946,10 +17861,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>523980</v>
+        <v>524226</v>
       </c>
       <c r="R153" t="n">
-        <v>7044026</v>
+        <v>7043829</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17986,7 +17901,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18013,7 +17928,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129303090</v>
+        <v>129303144</v>
       </c>
       <c r="B154" t="n">
         <v>57736</v>
@@ -18048,10 +17963,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>524194</v>
+        <v>523900</v>
       </c>
       <c r="R154" t="n">
-        <v>7043755</v>
+        <v>7044174</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18088,7 +18003,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18115,7 +18030,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129303096</v>
+        <v>129290810</v>
       </c>
       <c r="B155" t="n">
         <v>57736</v>
@@ -18144,19 +18059,29 @@
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>524226</v>
+        <v>524168</v>
       </c>
       <c r="R155" t="n">
-        <v>7043829</v>
+        <v>7044054</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18183,14 +18108,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18201,23 +18136,48 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129303144</v>
+        <v>129294258</v>
       </c>
       <c r="B156" t="n">
         <v>57736</v>
@@ -18246,19 +18206,24 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>523900</v>
+        <v>524049</v>
       </c>
       <c r="R156" t="n">
-        <v>7044174</v>
+        <v>7043961</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18285,14 +18250,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18303,23 +18278,48 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129303145</v>
+        <v>129283727</v>
       </c>
       <c r="B157" t="n">
         <v>57736</v>
@@ -18348,16 +18348,21 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>523898</v>
+        <v>523881</v>
       </c>
       <c r="R157" t="n">
-        <v>7044169</v>
+        <v>7044149</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18387,14 +18392,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska, enstaka högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18405,16 +18420,41 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -18523,7 +18563,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129303110</v>
+        <v>129303145</v>
       </c>
       <c r="B159" t="n">
         <v>57736</v>
@@ -18558,10 +18598,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>524053</v>
+        <v>523898</v>
       </c>
       <c r="R159" t="n">
-        <v>7043929</v>
+        <v>7044169</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18598,7 +18638,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18625,7 +18665,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129283727</v>
+        <v>129303110</v>
       </c>
       <c r="B160" t="n">
         <v>57736</v>
@@ -18654,21 +18694,16 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>523881</v>
+        <v>524053</v>
       </c>
       <c r="R160" t="n">
-        <v>7044149</v>
+        <v>7043929</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18698,24 +18733,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka högt upp på en gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18726,41 +18751,16 @@
       </c>
       <c r="AG160" t="b">
         <v>0</v>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -18909,7 +18909,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129303095</v>
+        <v>129303119</v>
       </c>
       <c r="B162" t="n">
         <v>57736</v>
@@ -18944,10 +18944,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>524229</v>
+        <v>524000</v>
       </c>
       <c r="R162" t="n">
-        <v>7043821</v>
+        <v>7044000</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19011,7 +19011,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129303082</v>
+        <v>129303095</v>
       </c>
       <c r="B163" t="n">
         <v>57736</v>
@@ -19046,10 +19046,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>524269</v>
+        <v>524229</v>
       </c>
       <c r="R163" t="n">
-        <v>7043735</v>
+        <v>7043821</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19086,7 +19086,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19113,7 +19113,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129303119</v>
+        <v>129303082</v>
       </c>
       <c r="B164" t="n">
         <v>57736</v>
@@ -19148,10 +19148,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>524000</v>
+        <v>524269</v>
       </c>
       <c r="R164" t="n">
-        <v>7044000</v>
+        <v>7043735</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19188,7 +19188,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19215,7 +19215,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129290684</v>
+        <v>129303094</v>
       </c>
       <c r="B165" t="n">
         <v>57736</v>
@@ -19244,29 +19244,19 @@
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>524150</v>
+        <v>524244</v>
       </c>
       <c r="R165" t="n">
-        <v>7044038</v>
+        <v>7043795</v>
       </c>
       <c r="S165" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19293,24 +19283,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19321,48 +19301,23 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129295476</v>
+        <v>129303117</v>
       </c>
       <c r="B166" t="n">
         <v>57736</v>
@@ -19391,29 +19346,19 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>524222</v>
+        <v>524002</v>
       </c>
       <c r="R166" t="n">
-        <v>7043799</v>
+        <v>7043990</v>
       </c>
       <c r="S166" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19440,24 +19385,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19468,48 +19403,23 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303117</v>
+        <v>129303101</v>
       </c>
       <c r="B167" t="n">
         <v>57736</v>
@@ -19544,10 +19454,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>524002</v>
+        <v>524169</v>
       </c>
       <c r="R167" t="n">
-        <v>7043990</v>
+        <v>7043927</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19584,7 +19494,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19611,7 +19521,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129303094</v>
+        <v>129303125</v>
       </c>
       <c r="B168" t="n">
         <v>57736</v>
@@ -19646,10 +19556,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>524244</v>
+        <v>523973</v>
       </c>
       <c r="R168" t="n">
-        <v>7043795</v>
+        <v>7044031</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19686,7 +19596,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19713,7 +19623,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129303101</v>
+        <v>129290684</v>
       </c>
       <c r="B169" t="n">
         <v>57736</v>
@@ -19742,19 +19652,29 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>524169</v>
+        <v>524150</v>
       </c>
       <c r="R169" t="n">
-        <v>7043927</v>
+        <v>7044038</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19781,14 +19701,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19799,23 +19729,48 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129303125</v>
+        <v>129295476</v>
       </c>
       <c r="B170" t="n">
         <v>57736</v>
@@ -19844,19 +19799,29 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>523973</v>
+        <v>524222</v>
       </c>
       <c r="R170" t="n">
-        <v>7044031</v>
+        <v>7043799</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19883,14 +19848,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19901,23 +19876,48 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129303113</v>
+        <v>129303130</v>
       </c>
       <c r="B171" t="n">
         <v>57736</v>
@@ -19952,10 +19952,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>524042</v>
+        <v>524087</v>
       </c>
       <c r="R171" t="n">
-        <v>7043944</v>
+        <v>7044036</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20121,7 +20121,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129303142</v>
+        <v>129303113</v>
       </c>
       <c r="B173" t="n">
         <v>57736</v>
@@ -20156,10 +20156,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>523900</v>
+        <v>524042</v>
       </c>
       <c r="R173" t="n">
-        <v>7044204</v>
+        <v>7043944</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20223,7 +20223,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129303105</v>
+        <v>129303142</v>
       </c>
       <c r="B174" t="n">
         <v>57736</v>
@@ -20258,10 +20258,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>524079</v>
+        <v>523900</v>
       </c>
       <c r="R174" t="n">
-        <v>7043891</v>
+        <v>7044204</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20427,7 +20427,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129303130</v>
+        <v>129303105</v>
       </c>
       <c r="B176" t="n">
         <v>57736</v>
@@ -20462,10 +20462,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>524087</v>
+        <v>524079</v>
       </c>
       <c r="R176" t="n">
-        <v>7044036</v>
+        <v>7043891</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20502,7 +20502,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20671,7 +20671,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129303131</v>
+        <v>129303100</v>
       </c>
       <c r="B178" t="n">
         <v>57736</v>
@@ -20706,10 +20706,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>524059</v>
+        <v>524235</v>
       </c>
       <c r="R178" t="n">
-        <v>7044016</v>
+        <v>7043960</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20773,7 +20773,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129303100</v>
+        <v>129303143</v>
       </c>
       <c r="B179" t="n">
         <v>57736</v>
@@ -20808,10 +20808,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>524235</v>
+        <v>523911</v>
       </c>
       <c r="R179" t="n">
-        <v>7043960</v>
+        <v>7044178</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20848,7 +20848,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20875,7 +20875,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129303143</v>
+        <v>129303112</v>
       </c>
       <c r="B180" t="n">
         <v>57736</v>
@@ -20910,10 +20910,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>523911</v>
+        <v>524044</v>
       </c>
       <c r="R180" t="n">
-        <v>7044178</v>
+        <v>7043935</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20950,7 +20950,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20977,7 +20977,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129303128</v>
+        <v>129303116</v>
       </c>
       <c r="B181" t="n">
         <v>57736</v>
@@ -21012,10 +21012,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>524186</v>
+        <v>524033</v>
       </c>
       <c r="R181" t="n">
-        <v>7043943</v>
+        <v>7043952</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21079,7 +21079,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129303116</v>
+        <v>129303138</v>
       </c>
       <c r="B182" t="n">
         <v>57736</v>
@@ -21114,10 +21114,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>524033</v>
+        <v>523879</v>
       </c>
       <c r="R182" t="n">
-        <v>7043952</v>
+        <v>7044256</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21181,7 +21181,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129303112</v>
+        <v>129303131</v>
       </c>
       <c r="B183" t="n">
         <v>57736</v>
@@ -21216,10 +21216,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>524044</v>
+        <v>524059</v>
       </c>
       <c r="R183" t="n">
-        <v>7043935</v>
+        <v>7044016</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21256,7 +21256,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21283,7 +21283,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129303138</v>
+        <v>129303128</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -21318,10 +21318,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>523879</v>
+        <v>524186</v>
       </c>
       <c r="R184" t="n">
-        <v>7044256</v>
+        <v>7043943</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21358,7 +21358,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21385,7 +21385,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129284399</v>
+        <v>129303147</v>
       </c>
       <c r="B185" t="n">
         <v>57736</v>
@@ -21414,24 +21414,19 @@
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>523878</v>
+        <v>523930</v>
       </c>
       <c r="R185" t="n">
-        <v>7044161</v>
+        <v>7044107</v>
       </c>
       <c r="S185" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21458,24 +21453,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Ringhack, färska och tydliga, på en gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21486,41 +21471,16 @@
       </c>
       <c r="AG185" t="b">
         <v>0</v>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -21629,7 +21589,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129303114</v>
+        <v>129303126</v>
       </c>
       <c r="B187" t="n">
         <v>57736</v>
@@ -21664,10 +21624,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>524041</v>
+        <v>523960</v>
       </c>
       <c r="R187" t="n">
-        <v>7043942</v>
+        <v>7044047</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21704,7 +21664,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21731,7 +21691,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129303147</v>
+        <v>129303114</v>
       </c>
       <c r="B188" t="n">
         <v>57736</v>
@@ -21766,10 +21726,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>523930</v>
+        <v>524041</v>
       </c>
       <c r="R188" t="n">
-        <v>7044107</v>
+        <v>7043942</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21806,7 +21766,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21833,7 +21793,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129303126</v>
+        <v>129284399</v>
       </c>
       <c r="B189" t="n">
         <v>57736</v>
@@ -21862,19 +21822,24 @@
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>523960</v>
+        <v>523878</v>
       </c>
       <c r="R189" t="n">
-        <v>7044047</v>
+        <v>7044161</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21901,14 +21866,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack, färska och tydliga, på en gran.</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21919,16 +21894,41 @@
       </c>
       <c r="AG189" t="b">
         <v>0</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -22179,7 +22179,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129303141</v>
+        <v>129284163</v>
       </c>
       <c r="B192" t="n">
         <v>57736</v>
@@ -22208,19 +22208,24 @@
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>523902</v>
+        <v>523881</v>
       </c>
       <c r="R192" t="n">
-        <v>7044224</v>
+        <v>7044157</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22247,14 +22252,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22265,23 +22280,48 @@
       </c>
       <c r="AG192" t="b">
         <v>0</v>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129303140</v>
+        <v>129296040</v>
       </c>
       <c r="B193" t="n">
         <v>57736</v>
@@ -22310,16 +22350,21 @@
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>523866</v>
+        <v>524232</v>
       </c>
       <c r="R193" t="n">
-        <v>7044256</v>
+        <v>7043714</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22349,14 +22394,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22367,23 +22422,48 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129284163</v>
+        <v>129303141</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -22412,24 +22492,19 @@
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>523881</v>
+        <v>523902</v>
       </c>
       <c r="R194" t="n">
-        <v>7044157</v>
+        <v>7044224</v>
       </c>
       <c r="S194" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22456,24 +22531,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22484,48 +22549,23 @@
       </c>
       <c r="AG194" t="b">
         <v>0</v>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO194" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129296040</v>
+        <v>129303140</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -22554,21 +22594,16 @@
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>524232</v>
+        <v>523866</v>
       </c>
       <c r="R195" t="n">
-        <v>7043714</v>
+        <v>7044256</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22598,24 +22633,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22626,41 +22651,16 @@
       </c>
       <c r="AG195" t="b">
         <v>0</v>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO195" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -15058,7 +15058,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129303133</v>
+        <v>129295685</v>
       </c>
       <c r="B129" t="n">
         <v>57736</v>
@@ -15087,16 +15087,21 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>523992</v>
+        <v>524198</v>
       </c>
       <c r="R129" t="n">
-        <v>7044262</v>
+        <v>7043758</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15126,14 +15131,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15144,23 +15159,48 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129303081</v>
+        <v>129283648</v>
       </c>
       <c r="B130" t="n">
         <v>57736</v>
@@ -15189,16 +15229,21 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524190</v>
+        <v>523885</v>
       </c>
       <c r="R130" t="n">
-        <v>7043804</v>
+        <v>7044152</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15228,14 +15273,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15246,23 +15301,48 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129303121</v>
+        <v>129285070</v>
       </c>
       <c r="B131" t="n">
         <v>57736</v>
@@ -15291,19 +15371,24 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>523979</v>
+        <v>523844</v>
       </c>
       <c r="R131" t="n">
-        <v>7044017</v>
+        <v>7044210</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15330,14 +15415,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15348,23 +15443,48 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129303087</v>
+        <v>129285747</v>
       </c>
       <c r="B132" t="n">
         <v>57736</v>
@@ -15393,19 +15513,24 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524219</v>
+        <v>523850</v>
       </c>
       <c r="R132" t="n">
-        <v>7043705</v>
+        <v>7044210</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15432,14 +15557,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15450,23 +15585,48 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129295685</v>
+        <v>129294128</v>
       </c>
       <c r="B133" t="n">
         <v>57736</v>
@@ -15497,19 +15657,19 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524198</v>
+        <v>523987</v>
       </c>
       <c r="R133" t="n">
-        <v>7043758</v>
+        <v>7044025</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15541,7 +15701,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15551,12 +15711,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15608,7 +15768,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129283648</v>
+        <v>129303133</v>
       </c>
       <c r="B134" t="n">
         <v>57736</v>
@@ -15637,21 +15797,16 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>523885</v>
+        <v>523992</v>
       </c>
       <c r="R134" t="n">
-        <v>7044152</v>
+        <v>7044262</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15681,24 +15836,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15709,48 +15854,23 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129285070</v>
+        <v>129303081</v>
       </c>
       <c r="B135" t="n">
         <v>57736</v>
@@ -15779,24 +15899,19 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>523844</v>
+        <v>524190</v>
       </c>
       <c r="R135" t="n">
-        <v>7044210</v>
+        <v>7043804</v>
       </c>
       <c r="S135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15823,24 +15938,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15851,48 +15956,23 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129285747</v>
+        <v>129303121</v>
       </c>
       <c r="B136" t="n">
         <v>57736</v>
@@ -15921,24 +16001,19 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>523850</v>
+        <v>523979</v>
       </c>
       <c r="R136" t="n">
-        <v>7044210</v>
+        <v>7044017</v>
       </c>
       <c r="S136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15965,24 +16040,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15993,48 +16058,23 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129294128</v>
+        <v>129303087</v>
       </c>
       <c r="B137" t="n">
         <v>57736</v>
@@ -16063,21 +16103,16 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>523987</v>
+        <v>524219</v>
       </c>
       <c r="R137" t="n">
-        <v>7044025</v>
+        <v>7043705</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16107,24 +16142,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16135,41 +16160,16 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -19215,7 +19215,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129303094</v>
+        <v>129290684</v>
       </c>
       <c r="B165" t="n">
         <v>57736</v>
@@ -19244,19 +19244,29 @@
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>524244</v>
+        <v>524150</v>
       </c>
       <c r="R165" t="n">
-        <v>7043795</v>
+        <v>7044038</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19283,14 +19293,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19301,23 +19321,48 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129303117</v>
+        <v>129295476</v>
       </c>
       <c r="B166" t="n">
         <v>57736</v>
@@ -19346,19 +19391,29 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>524002</v>
+        <v>524222</v>
       </c>
       <c r="R166" t="n">
-        <v>7043990</v>
+        <v>7043799</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19385,14 +19440,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19403,23 +19468,48 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303101</v>
+        <v>129303094</v>
       </c>
       <c r="B167" t="n">
         <v>57736</v>
@@ -19454,10 +19544,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>524169</v>
+        <v>524244</v>
       </c>
       <c r="R167" t="n">
-        <v>7043927</v>
+        <v>7043795</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19494,7 +19584,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19521,7 +19611,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129303125</v>
+        <v>129303117</v>
       </c>
       <c r="B168" t="n">
         <v>57736</v>
@@ -19556,10 +19646,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>523973</v>
+        <v>524002</v>
       </c>
       <c r="R168" t="n">
-        <v>7044031</v>
+        <v>7043990</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19596,7 +19686,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19623,7 +19713,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129290684</v>
+        <v>129303101</v>
       </c>
       <c r="B169" t="n">
         <v>57736</v>
@@ -19652,29 +19742,19 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>524150</v>
+        <v>524169</v>
       </c>
       <c r="R169" t="n">
-        <v>7044038</v>
+        <v>7043927</v>
       </c>
       <c r="S169" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19701,24 +19781,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19729,48 +19799,23 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129295476</v>
+        <v>129303125</v>
       </c>
       <c r="B170" t="n">
         <v>57736</v>
@@ -19799,29 +19844,19 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>524222</v>
+        <v>523973</v>
       </c>
       <c r="R170" t="n">
-        <v>7043799</v>
+        <v>7044031</v>
       </c>
       <c r="S170" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19848,24 +19883,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19876,41 +19901,16 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -20529,7 +20529,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129294096</v>
+        <v>129303100</v>
       </c>
       <c r="B177" t="n">
         <v>57736</v>
@@ -20558,24 +20558,19 @@
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>523971</v>
+        <v>524235</v>
       </c>
       <c r="R177" t="n">
-        <v>7044037</v>
+        <v>7043960</v>
       </c>
       <c r="S177" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20602,24 +20597,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20630,48 +20615,23 @@
       </c>
       <c r="AG177" t="b">
         <v>0</v>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129303100</v>
+        <v>129303143</v>
       </c>
       <c r="B178" t="n">
         <v>57736</v>
@@ -20706,10 +20666,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>524235</v>
+        <v>523911</v>
       </c>
       <c r="R178" t="n">
-        <v>7043960</v>
+        <v>7044178</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20746,7 +20706,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20773,7 +20733,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129303143</v>
+        <v>129303112</v>
       </c>
       <c r="B179" t="n">
         <v>57736</v>
@@ -20808,10 +20768,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>523911</v>
+        <v>524044</v>
       </c>
       <c r="R179" t="n">
-        <v>7044178</v>
+        <v>7043935</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20848,7 +20808,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20875,7 +20835,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129303112</v>
+        <v>129303116</v>
       </c>
       <c r="B180" t="n">
         <v>57736</v>
@@ -20910,10 +20870,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>524044</v>
+        <v>524033</v>
       </c>
       <c r="R180" t="n">
-        <v>7043935</v>
+        <v>7043952</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20977,7 +20937,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129303116</v>
+        <v>129303138</v>
       </c>
       <c r="B181" t="n">
         <v>57736</v>
@@ -21012,10 +20972,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>524033</v>
+        <v>523879</v>
       </c>
       <c r="R181" t="n">
-        <v>7043952</v>
+        <v>7044256</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21052,7 +21012,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21079,7 +21039,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129303138</v>
+        <v>129303131</v>
       </c>
       <c r="B182" t="n">
         <v>57736</v>
@@ -21114,10 +21074,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>523879</v>
+        <v>524059</v>
       </c>
       <c r="R182" t="n">
-        <v>7044256</v>
+        <v>7044016</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21181,7 +21141,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129303131</v>
+        <v>129303128</v>
       </c>
       <c r="B183" t="n">
         <v>57736</v>
@@ -21216,10 +21176,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>524059</v>
+        <v>524186</v>
       </c>
       <c r="R183" t="n">
-        <v>7044016</v>
+        <v>7043943</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21256,7 +21216,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21283,7 +21243,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129303128</v>
+        <v>129294096</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -21312,19 +21272,24 @@
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>524186</v>
+        <v>523971</v>
       </c>
       <c r="R184" t="n">
-        <v>7043943</v>
+        <v>7044037</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21351,14 +21316,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21369,23 +21344,48 @@
       </c>
       <c r="AG184" t="b">
         <v>0</v>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129303147</v>
+        <v>129284399</v>
       </c>
       <c r="B185" t="n">
         <v>57736</v>
@@ -21414,19 +21414,24 @@
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>523930</v>
+        <v>523878</v>
       </c>
       <c r="R185" t="n">
-        <v>7044107</v>
+        <v>7044161</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21453,14 +21458,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska och tydliga, på en gran.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21471,23 +21486,48 @@
       </c>
       <c r="AG185" t="b">
         <v>0</v>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129303146</v>
+        <v>129303147</v>
       </c>
       <c r="B186" t="n">
         <v>57736</v>
@@ -21522,10 +21562,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>523926</v>
+        <v>523930</v>
       </c>
       <c r="R186" t="n">
-        <v>7044118</v>
+        <v>7044107</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21562,7 +21602,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21589,7 +21629,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129303126</v>
+        <v>129303146</v>
       </c>
       <c r="B187" t="n">
         <v>57736</v>
@@ -21624,10 +21664,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>523960</v>
+        <v>523926</v>
       </c>
       <c r="R187" t="n">
-        <v>7044047</v>
+        <v>7044118</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21664,7 +21704,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21691,7 +21731,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129303114</v>
+        <v>129303126</v>
       </c>
       <c r="B188" t="n">
         <v>57736</v>
@@ -21726,10 +21766,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>524041</v>
+        <v>523960</v>
       </c>
       <c r="R188" t="n">
-        <v>7043942</v>
+        <v>7044047</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21766,7 +21806,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21793,7 +21833,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129284399</v>
+        <v>129303114</v>
       </c>
       <c r="B189" t="n">
         <v>57736</v>
@@ -21822,24 +21862,19 @@
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>523878</v>
+        <v>524041</v>
       </c>
       <c r="R189" t="n">
-        <v>7044161</v>
+        <v>7043942</v>
       </c>
       <c r="S189" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21866,24 +21901,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Ringhack, färska och tydliga, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21894,48 +21919,23 @@
       </c>
       <c r="AG189" t="b">
         <v>0</v>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO189" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129290433</v>
+        <v>129303103</v>
       </c>
       <c r="B190" t="n">
         <v>57736</v>
@@ -21964,24 +21964,19 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>524140</v>
+        <v>524143</v>
       </c>
       <c r="R190" t="n">
-        <v>7044077</v>
+        <v>7043912</v>
       </c>
       <c r="S190" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -22008,24 +22003,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, tydliga på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22036,48 +22021,23 @@
       </c>
       <c r="AG190" t="b">
         <v>0</v>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO190" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129303103</v>
+        <v>129290433</v>
       </c>
       <c r="B191" t="n">
         <v>57736</v>
@@ -22106,19 +22066,24 @@
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>524143</v>
+        <v>524140</v>
       </c>
       <c r="R191" t="n">
-        <v>7043912</v>
+        <v>7044077</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -22145,14 +22110,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, tydliga på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22163,16 +22138,41 @@
       </c>
       <c r="AG191" t="b">
         <v>0</v>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -12920,7 +12920,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129294077</v>
+        <v>129303134</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -12949,24 +12949,19 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>523957</v>
+        <v>523912</v>
       </c>
       <c r="R110" t="n">
-        <v>7044053</v>
+        <v>7044281</v>
       </c>
       <c r="S110" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12993,24 +12988,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13021,48 +13006,23 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129303134</v>
+        <v>129303106</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -13097,10 +13057,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>523912</v>
+        <v>524060</v>
       </c>
       <c r="R111" t="n">
-        <v>7044281</v>
+        <v>7043917</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13137,7 +13097,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13164,7 +13124,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129303106</v>
+        <v>129294077</v>
       </c>
       <c r="B112" t="n">
         <v>57736</v>
@@ -13193,19 +13153,24 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524060</v>
+        <v>523957</v>
       </c>
       <c r="R112" t="n">
-        <v>7043917</v>
+        <v>7044053</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13232,14 +13197,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13250,16 +13225,41 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -14122,7 +14122,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129286184</v>
+        <v>129303124</v>
       </c>
       <c r="B121" t="n">
         <v>57736</v>
@@ -14151,24 +14151,19 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523842</v>
+        <v>523976</v>
       </c>
       <c r="R121" t="n">
-        <v>7044233</v>
+        <v>7044029</v>
       </c>
       <c r="S121" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14195,24 +14190,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14223,48 +14208,23 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129292836</v>
+        <v>129303129</v>
       </c>
       <c r="B122" t="n">
         <v>57736</v>
@@ -14293,24 +14253,19 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524162</v>
+        <v>524088</v>
       </c>
       <c r="R122" t="n">
-        <v>7043929</v>
+        <v>7044015</v>
       </c>
       <c r="S122" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14337,24 +14292,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14365,48 +14310,23 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129303124</v>
+        <v>129286184</v>
       </c>
       <c r="B123" t="n">
         <v>57736</v>
@@ -14435,19 +14355,24 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>523976</v>
+        <v>523842</v>
       </c>
       <c r="R123" t="n">
-        <v>7044029</v>
+        <v>7044233</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14474,14 +14399,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14492,23 +14427,48 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129303129</v>
+        <v>129292836</v>
       </c>
       <c r="B124" t="n">
         <v>57736</v>
@@ -14537,19 +14497,24 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524088</v>
+        <v>524162</v>
       </c>
       <c r="R124" t="n">
-        <v>7044015</v>
+        <v>7043929</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14576,14 +14541,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14594,16 +14569,41 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -16278,7 +16278,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129303092</v>
+        <v>129294143</v>
       </c>
       <c r="B139" t="n">
         <v>57736</v>
@@ -16307,19 +16307,24 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>524227</v>
+        <v>523985</v>
       </c>
       <c r="R139" t="n">
-        <v>7043799</v>
+        <v>7044028</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16346,14 +16351,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16364,23 +16379,48 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129303148</v>
+        <v>129303092</v>
       </c>
       <c r="B140" t="n">
         <v>57736</v>
@@ -16415,10 +16455,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>523952</v>
+        <v>524227</v>
       </c>
       <c r="R140" t="n">
-        <v>7044072</v>
+        <v>7043799</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16455,7 +16495,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16482,7 +16522,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129303098</v>
+        <v>129303148</v>
       </c>
       <c r="B141" t="n">
         <v>57736</v>
@@ -16517,10 +16557,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>524297</v>
+        <v>523952</v>
       </c>
       <c r="R141" t="n">
-        <v>7043866</v>
+        <v>7044072</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16557,7 +16597,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16584,7 +16624,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129303093</v>
+        <v>129303098</v>
       </c>
       <c r="B142" t="n">
         <v>57736</v>
@@ -16619,10 +16659,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>524246</v>
+        <v>524297</v>
       </c>
       <c r="R142" t="n">
-        <v>7043787</v>
+        <v>7043866</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16659,7 +16699,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16686,7 +16726,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129295984</v>
+        <v>129303093</v>
       </c>
       <c r="B143" t="n">
         <v>57736</v>
@@ -16715,21 +16755,16 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>524244</v>
+        <v>524246</v>
       </c>
       <c r="R143" t="n">
-        <v>7043732</v>
+        <v>7043787</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16759,24 +16794,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16787,48 +16812,23 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129294143</v>
+        <v>129295984</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -16864,17 +16864,17 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>523985</v>
+        <v>524244</v>
       </c>
       <c r="R144" t="n">
-        <v>7044028</v>
+        <v>7043732</v>
       </c>
       <c r="S144" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16913,12 +16913,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på gränsen till färska.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -19215,7 +19215,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129290684</v>
+        <v>129303094</v>
       </c>
       <c r="B165" t="n">
         <v>57736</v>
@@ -19244,29 +19244,19 @@
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>524150</v>
+        <v>524244</v>
       </c>
       <c r="R165" t="n">
-        <v>7044038</v>
+        <v>7043795</v>
       </c>
       <c r="S165" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19293,24 +19283,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19321,48 +19301,23 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129295476</v>
+        <v>129303117</v>
       </c>
       <c r="B166" t="n">
         <v>57736</v>
@@ -19391,29 +19346,19 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>524222</v>
+        <v>524002</v>
       </c>
       <c r="R166" t="n">
-        <v>7043799</v>
+        <v>7043990</v>
       </c>
       <c r="S166" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19440,24 +19385,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19468,48 +19403,23 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303094</v>
+        <v>129303101</v>
       </c>
       <c r="B167" t="n">
         <v>57736</v>
@@ -19544,10 +19454,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>524244</v>
+        <v>524169</v>
       </c>
       <c r="R167" t="n">
-        <v>7043795</v>
+        <v>7043927</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19584,7 +19494,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19611,7 +19521,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129303117</v>
+        <v>129303125</v>
       </c>
       <c r="B168" t="n">
         <v>57736</v>
@@ -19646,10 +19556,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>524002</v>
+        <v>523973</v>
       </c>
       <c r="R168" t="n">
-        <v>7043990</v>
+        <v>7044031</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19686,7 +19596,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19713,7 +19623,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129303101</v>
+        <v>129295476</v>
       </c>
       <c r="B169" t="n">
         <v>57736</v>
@@ -19742,19 +19652,29 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>524169</v>
+        <v>524222</v>
       </c>
       <c r="R169" t="n">
-        <v>7043927</v>
+        <v>7043799</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19781,14 +19701,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19799,23 +19729,48 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129303125</v>
+        <v>129290684</v>
       </c>
       <c r="B170" t="n">
         <v>57736</v>
@@ -19844,19 +19799,29 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>523973</v>
+        <v>524150</v>
       </c>
       <c r="R170" t="n">
-        <v>7044031</v>
+        <v>7044038</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19883,14 +19848,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19901,16 +19876,41 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -21935,7 +21935,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129303103</v>
+        <v>129290433</v>
       </c>
       <c r="B190" t="n">
         <v>57736</v>
@@ -21964,19 +21964,24 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>524143</v>
+        <v>524140</v>
       </c>
       <c r="R190" t="n">
-        <v>7043912</v>
+        <v>7044077</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -22003,14 +22008,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, tydliga på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22021,23 +22036,48 @@
       </c>
       <c r="AG190" t="b">
         <v>0</v>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129290433</v>
+        <v>129303103</v>
       </c>
       <c r="B191" t="n">
         <v>57736</v>
@@ -22066,24 +22106,19 @@
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>524140</v>
+        <v>524143</v>
       </c>
       <c r="R191" t="n">
-        <v>7044077</v>
+        <v>7043912</v>
       </c>
       <c r="S191" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -22110,24 +22145,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, tydliga på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22138,48 +22163,23 @@
       </c>
       <c r="AG191" t="b">
         <v>0</v>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO191" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129284163</v>
+        <v>129303141</v>
       </c>
       <c r="B192" t="n">
         <v>57736</v>
@@ -22208,24 +22208,19 @@
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>523881</v>
+        <v>523902</v>
       </c>
       <c r="R192" t="n">
-        <v>7044157</v>
+        <v>7044224</v>
       </c>
       <c r="S192" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22252,24 +22247,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22280,48 +22265,23 @@
       </c>
       <c r="AG192" t="b">
         <v>0</v>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129296040</v>
+        <v>129303140</v>
       </c>
       <c r="B193" t="n">
         <v>57736</v>
@@ -22350,21 +22310,16 @@
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>524232</v>
+        <v>523866</v>
       </c>
       <c r="R193" t="n">
-        <v>7043714</v>
+        <v>7044256</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22394,24 +22349,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22422,48 +22367,23 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO193" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129303141</v>
+        <v>129284163</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -22492,19 +22412,24 @@
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>523902</v>
+        <v>523881</v>
       </c>
       <c r="R194" t="n">
-        <v>7044224</v>
+        <v>7044157</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22531,14 +22456,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22549,23 +22484,48 @@
       </c>
       <c r="AG194" t="b">
         <v>0</v>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129303140</v>
+        <v>129296040</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -22594,16 +22554,21 @@
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>523866</v>
+        <v>524232</v>
       </c>
       <c r="R195" t="n">
-        <v>7044256</v>
+        <v>7043714</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22633,14 +22598,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22651,16 +22626,41 @@
       </c>
       <c r="AG195" t="b">
         <v>0</v>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -14610,7 +14610,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129303136</v>
+        <v>129290167</v>
       </c>
       <c r="B125" t="n">
         <v>57736</v>
@@ -14639,16 +14639,21 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523897</v>
+        <v>524109</v>
       </c>
       <c r="R125" t="n">
-        <v>7044281</v>
+        <v>7044093</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14678,14 +14683,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gammal gran.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14696,23 +14711,48 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129303135</v>
+        <v>129303136</v>
       </c>
       <c r="B126" t="n">
         <v>57736</v>
@@ -14747,10 +14787,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523902</v>
+        <v>523897</v>
       </c>
       <c r="R126" t="n">
-        <v>7044288</v>
+        <v>7044281</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14787,7 +14827,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14814,7 +14854,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129303111</v>
+        <v>129303135</v>
       </c>
       <c r="B127" t="n">
         <v>57736</v>
@@ -14849,10 +14889,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>524047</v>
+        <v>523902</v>
       </c>
       <c r="R127" t="n">
-        <v>7043931</v>
+        <v>7044288</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14889,7 +14929,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14916,7 +14956,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129290167</v>
+        <v>129303111</v>
       </c>
       <c r="B128" t="n">
         <v>57736</v>
@@ -14945,21 +14985,16 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>524109</v>
+        <v>524047</v>
       </c>
       <c r="R128" t="n">
-        <v>7044093</v>
+        <v>7043931</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14989,24 +15024,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15017,41 +15042,16 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -19215,7 +19215,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129303094</v>
+        <v>129290684</v>
       </c>
       <c r="B165" t="n">
         <v>57736</v>
@@ -19244,19 +19244,29 @@
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>524244</v>
+        <v>524150</v>
       </c>
       <c r="R165" t="n">
-        <v>7043795</v>
+        <v>7044038</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19283,14 +19293,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19301,23 +19321,48 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129303117</v>
+        <v>129295476</v>
       </c>
       <c r="B166" t="n">
         <v>57736</v>
@@ -19346,19 +19391,29 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>524002</v>
+        <v>524222</v>
       </c>
       <c r="R166" t="n">
-        <v>7043990</v>
+        <v>7043799</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19385,14 +19440,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19403,23 +19468,48 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303101</v>
+        <v>129303094</v>
       </c>
       <c r="B167" t="n">
         <v>57736</v>
@@ -19454,10 +19544,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>524169</v>
+        <v>524244</v>
       </c>
       <c r="R167" t="n">
-        <v>7043927</v>
+        <v>7043795</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19494,7 +19584,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19521,7 +19611,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129303125</v>
+        <v>129303117</v>
       </c>
       <c r="B168" t="n">
         <v>57736</v>
@@ -19556,10 +19646,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>523973</v>
+        <v>524002</v>
       </c>
       <c r="R168" t="n">
-        <v>7044031</v>
+        <v>7043990</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19596,7 +19686,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19623,7 +19713,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129295476</v>
+        <v>129303101</v>
       </c>
       <c r="B169" t="n">
         <v>57736</v>
@@ -19652,29 +19742,19 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>524222</v>
+        <v>524169</v>
       </c>
       <c r="R169" t="n">
-        <v>7043799</v>
+        <v>7043927</v>
       </c>
       <c r="S169" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19701,24 +19781,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19729,48 +19799,23 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129290684</v>
+        <v>129303125</v>
       </c>
       <c r="B170" t="n">
         <v>57736</v>
@@ -19799,29 +19844,19 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>524150</v>
+        <v>523973</v>
       </c>
       <c r="R170" t="n">
-        <v>7044038</v>
+        <v>7044031</v>
       </c>
       <c r="S170" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19848,24 +19883,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19876,41 +19901,16 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -22179,7 +22179,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129303141</v>
+        <v>129284163</v>
       </c>
       <c r="B192" t="n">
         <v>57736</v>
@@ -22208,19 +22208,24 @@
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>523902</v>
+        <v>523881</v>
       </c>
       <c r="R192" t="n">
-        <v>7044224</v>
+        <v>7044157</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22247,14 +22252,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22265,23 +22280,48 @@
       </c>
       <c r="AG192" t="b">
         <v>0</v>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129303140</v>
+        <v>129296040</v>
       </c>
       <c r="B193" t="n">
         <v>57736</v>
@@ -22310,16 +22350,21 @@
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>523866</v>
+        <v>524232</v>
       </c>
       <c r="R193" t="n">
-        <v>7044256</v>
+        <v>7043714</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22349,14 +22394,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22367,23 +22422,48 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129284163</v>
+        <v>129303141</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -22412,24 +22492,19 @@
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>523881</v>
+        <v>523902</v>
       </c>
       <c r="R194" t="n">
-        <v>7044157</v>
+        <v>7044224</v>
       </c>
       <c r="S194" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22456,24 +22531,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22484,48 +22549,23 @@
       </c>
       <c r="AG194" t="b">
         <v>0</v>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO194" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129296040</v>
+        <v>129303140</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -22554,21 +22594,16 @@
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>524232</v>
+        <v>523866</v>
       </c>
       <c r="R195" t="n">
-        <v>7043714</v>
+        <v>7044256</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22598,24 +22633,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22626,41 +22651,16 @@
       </c>
       <c r="AG195" t="b">
         <v>0</v>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO195" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -16278,7 +16278,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129294143</v>
+        <v>129295984</v>
       </c>
       <c r="B139" t="n">
         <v>57736</v>
@@ -16314,17 +16314,17 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>523985</v>
+        <v>524244</v>
       </c>
       <c r="R139" t="n">
-        <v>7044028</v>
+        <v>7043732</v>
       </c>
       <c r="S139" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16363,12 +16363,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på gränsen till färska.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16420,7 +16420,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129303092</v>
+        <v>129294143</v>
       </c>
       <c r="B140" t="n">
         <v>57736</v>
@@ -16449,19 +16449,24 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>524227</v>
+        <v>523985</v>
       </c>
       <c r="R140" t="n">
-        <v>7043799</v>
+        <v>7044028</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16488,14 +16493,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16506,23 +16521,48 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129303148</v>
+        <v>129303092</v>
       </c>
       <c r="B141" t="n">
         <v>57736</v>
@@ -16557,10 +16597,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>523952</v>
+        <v>524227</v>
       </c>
       <c r="R141" t="n">
-        <v>7044072</v>
+        <v>7043799</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16597,7 +16637,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16624,7 +16664,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129303098</v>
+        <v>129303148</v>
       </c>
       <c r="B142" t="n">
         <v>57736</v>
@@ -16659,10 +16699,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>524297</v>
+        <v>523952</v>
       </c>
       <c r="R142" t="n">
-        <v>7043866</v>
+        <v>7044072</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16699,7 +16739,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16726,7 +16766,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129303093</v>
+        <v>129303098</v>
       </c>
       <c r="B143" t="n">
         <v>57736</v>
@@ -16761,10 +16801,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>524246</v>
+        <v>524297</v>
       </c>
       <c r="R143" t="n">
-        <v>7043787</v>
+        <v>7043866</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16801,7 +16841,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16828,7 +16868,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129295984</v>
+        <v>129303093</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -16857,21 +16897,16 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>524244</v>
+        <v>524246</v>
       </c>
       <c r="R144" t="n">
-        <v>7043732</v>
+        <v>7043787</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16901,24 +16936,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16929,41 +16954,16 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -17418,7 +17418,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129303090</v>
+        <v>129290810</v>
       </c>
       <c r="B149" t="n">
         <v>57736</v>
@@ -17447,19 +17447,29 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>524194</v>
+        <v>524168</v>
       </c>
       <c r="R149" t="n">
-        <v>7043755</v>
+        <v>7044054</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17486,14 +17496,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17504,23 +17524,48 @@
       </c>
       <c r="AG149" t="b">
         <v>0</v>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129303123</v>
+        <v>129294258</v>
       </c>
       <c r="B150" t="n">
         <v>57736</v>
@@ -17549,19 +17594,24 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>523980</v>
+        <v>524049</v>
       </c>
       <c r="R150" t="n">
-        <v>7044026</v>
+        <v>7043961</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17588,14 +17638,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17606,23 +17666,48 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129303091</v>
+        <v>129303090</v>
       </c>
       <c r="B151" t="n">
         <v>57736</v>
@@ -17657,10 +17742,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>524225</v>
+        <v>524194</v>
       </c>
       <c r="R151" t="n">
-        <v>7043779</v>
+        <v>7043755</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17697,7 +17782,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17724,7 +17809,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129303139</v>
+        <v>129303123</v>
       </c>
       <c r="B152" t="n">
         <v>57736</v>
@@ -17759,10 +17844,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>523860</v>
+        <v>523980</v>
       </c>
       <c r="R152" t="n">
-        <v>7044250</v>
+        <v>7044026</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17799,7 +17884,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17826,7 +17911,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129303096</v>
+        <v>129303091</v>
       </c>
       <c r="B153" t="n">
         <v>57736</v>
@@ -17861,10 +17946,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>524226</v>
+        <v>524225</v>
       </c>
       <c r="R153" t="n">
-        <v>7043829</v>
+        <v>7043779</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17928,7 +18013,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129303144</v>
+        <v>129303139</v>
       </c>
       <c r="B154" t="n">
         <v>57736</v>
@@ -17963,10 +18048,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>523900</v>
+        <v>523860</v>
       </c>
       <c r="R154" t="n">
-        <v>7044174</v>
+        <v>7044250</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18003,7 +18088,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18030,7 +18115,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129290810</v>
+        <v>129303096</v>
       </c>
       <c r="B155" t="n">
         <v>57736</v>
@@ -18059,29 +18144,19 @@
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>524168</v>
+        <v>524226</v>
       </c>
       <c r="R155" t="n">
-        <v>7044054</v>
+        <v>7043829</v>
       </c>
       <c r="S155" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18108,24 +18183,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18136,48 +18201,23 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129294258</v>
+        <v>129303144</v>
       </c>
       <c r="B156" t="n">
         <v>57736</v>
@@ -18206,24 +18246,19 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>524049</v>
+        <v>523900</v>
       </c>
       <c r="R156" t="n">
-        <v>7043961</v>
+        <v>7044174</v>
       </c>
       <c r="S156" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18250,24 +18285,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18278,41 +18303,16 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -20529,7 +20529,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129303100</v>
+        <v>129294096</v>
       </c>
       <c r="B177" t="n">
         <v>57736</v>
@@ -20558,19 +20558,24 @@
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>524235</v>
+        <v>523971</v>
       </c>
       <c r="R177" t="n">
-        <v>7043960</v>
+        <v>7044037</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20597,14 +20602,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20615,23 +20630,48 @@
       </c>
       <c r="AG177" t="b">
         <v>0</v>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129303143</v>
+        <v>129303100</v>
       </c>
       <c r="B178" t="n">
         <v>57736</v>
@@ -20666,10 +20706,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>523911</v>
+        <v>524235</v>
       </c>
       <c r="R178" t="n">
-        <v>7044178</v>
+        <v>7043960</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20706,7 +20746,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20733,7 +20773,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129303112</v>
+        <v>129303143</v>
       </c>
       <c r="B179" t="n">
         <v>57736</v>
@@ -20768,10 +20808,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>524044</v>
+        <v>523911</v>
       </c>
       <c r="R179" t="n">
-        <v>7043935</v>
+        <v>7044178</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20808,7 +20848,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20835,7 +20875,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129303116</v>
+        <v>129303112</v>
       </c>
       <c r="B180" t="n">
         <v>57736</v>
@@ -20870,10 +20910,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>524033</v>
+        <v>524044</v>
       </c>
       <c r="R180" t="n">
-        <v>7043952</v>
+        <v>7043935</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20937,7 +20977,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129303138</v>
+        <v>129303116</v>
       </c>
       <c r="B181" t="n">
         <v>57736</v>
@@ -20972,10 +21012,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>523879</v>
+        <v>524033</v>
       </c>
       <c r="R181" t="n">
-        <v>7044256</v>
+        <v>7043952</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21012,7 +21052,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21039,7 +21079,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129303131</v>
+        <v>129303138</v>
       </c>
       <c r="B182" t="n">
         <v>57736</v>
@@ -21074,10 +21114,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>524059</v>
+        <v>523879</v>
       </c>
       <c r="R182" t="n">
-        <v>7044016</v>
+        <v>7044256</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21141,7 +21181,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129303128</v>
+        <v>129303131</v>
       </c>
       <c r="B183" t="n">
         <v>57736</v>
@@ -21176,10 +21216,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>524186</v>
+        <v>524059</v>
       </c>
       <c r="R183" t="n">
-        <v>7043943</v>
+        <v>7044016</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21216,7 +21256,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21243,7 +21283,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129294096</v>
+        <v>129303128</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -21272,24 +21312,19 @@
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>523971</v>
+        <v>524186</v>
       </c>
       <c r="R184" t="n">
-        <v>7044037</v>
+        <v>7043943</v>
       </c>
       <c r="S184" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21316,24 +21351,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21344,41 +21369,16 @@
       </c>
       <c r="AG184" t="b">
         <v>0</v>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -18767,7 +18767,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129291995</v>
+        <v>129303119</v>
       </c>
       <c r="B161" t="n">
         <v>57736</v>
@@ -18796,21 +18796,16 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>524225</v>
+        <v>524000</v>
       </c>
       <c r="R161" t="n">
-        <v>7043980</v>
+        <v>7044000</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18840,24 +18835,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18868,48 +18853,23 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129303119</v>
+        <v>129303095</v>
       </c>
       <c r="B162" t="n">
         <v>57736</v>
@@ -18944,10 +18904,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>524000</v>
+        <v>524229</v>
       </c>
       <c r="R162" t="n">
-        <v>7044000</v>
+        <v>7043821</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19011,7 +18971,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129303095</v>
+        <v>129303082</v>
       </c>
       <c r="B163" t="n">
         <v>57736</v>
@@ -19046,10 +19006,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>524229</v>
+        <v>524269</v>
       </c>
       <c r="R163" t="n">
-        <v>7043821</v>
+        <v>7043735</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19086,7 +19046,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19113,7 +19073,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129303082</v>
+        <v>129291995</v>
       </c>
       <c r="B164" t="n">
         <v>57736</v>
@@ -19142,16 +19102,21 @@
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>524269</v>
+        <v>524225</v>
       </c>
       <c r="R164" t="n">
-        <v>7043735</v>
+        <v>7043980</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19181,14 +19146,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19199,16 +19174,41 @@
       </c>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -22179,7 +22179,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129284163</v>
+        <v>129303141</v>
       </c>
       <c r="B192" t="n">
         <v>57736</v>
@@ -22208,24 +22208,19 @@
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>523881</v>
+        <v>523902</v>
       </c>
       <c r="R192" t="n">
-        <v>7044157</v>
+        <v>7044224</v>
       </c>
       <c r="S192" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22252,24 +22247,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22280,48 +22265,23 @@
       </c>
       <c r="AG192" t="b">
         <v>0</v>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129296040</v>
+        <v>129303140</v>
       </c>
       <c r="B193" t="n">
         <v>57736</v>
@@ -22350,21 +22310,16 @@
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>524232</v>
+        <v>523866</v>
       </c>
       <c r="R193" t="n">
-        <v>7043714</v>
+        <v>7044256</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22394,24 +22349,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22422,48 +22367,23 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO193" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129303141</v>
+        <v>129284163</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -22492,19 +22412,24 @@
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>523902</v>
+        <v>523881</v>
       </c>
       <c r="R194" t="n">
-        <v>7044224</v>
+        <v>7044157</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22531,14 +22456,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22549,23 +22484,48 @@
       </c>
       <c r="AG194" t="b">
         <v>0</v>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129303140</v>
+        <v>129296040</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -22594,16 +22554,21 @@
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>523866</v>
+        <v>524232</v>
       </c>
       <c r="R195" t="n">
-        <v>7044256</v>
+        <v>7043714</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22633,14 +22598,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22651,16 +22626,41 @@
       </c>
       <c r="AG195" t="b">
         <v>0</v>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -13368,7 +13368,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129284656</v>
+        <v>129303107</v>
       </c>
       <c r="B114" t="n">
         <v>57736</v>
@@ -13397,24 +13397,19 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>523856</v>
+        <v>524056</v>
       </c>
       <c r="R114" t="n">
-        <v>7044190</v>
+        <v>7043920</v>
       </c>
       <c r="S114" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13441,24 +13436,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, högt upp på en tall.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13469,48 +13454,23 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129303107</v>
+        <v>129303108</v>
       </c>
       <c r="B115" t="n">
         <v>57736</v>
@@ -13545,10 +13505,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524056</v>
+        <v>524052</v>
       </c>
       <c r="R115" t="n">
-        <v>7043920</v>
+        <v>7043922</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13585,7 +13545,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13612,7 +13572,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129303108</v>
+        <v>129303097</v>
       </c>
       <c r="B116" t="n">
         <v>57736</v>
@@ -13647,10 +13607,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524052</v>
+        <v>524306</v>
       </c>
       <c r="R116" t="n">
-        <v>7043922</v>
+        <v>7043867</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13687,7 +13647,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13714,7 +13674,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129303097</v>
+        <v>129284656</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -13743,19 +13703,24 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524306</v>
+        <v>523856</v>
       </c>
       <c r="R117" t="n">
-        <v>7043867</v>
+        <v>7044190</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13782,14 +13747,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, högt upp på en tall.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13800,16 +13775,41 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -18319,7 +18319,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129283727</v>
+        <v>129303122</v>
       </c>
       <c r="B157" t="n">
         <v>57736</v>
@@ -18348,21 +18348,16 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>523881</v>
+        <v>523976</v>
       </c>
       <c r="R157" t="n">
-        <v>7044149</v>
+        <v>7044021</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18392,24 +18387,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka högt upp på en gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18420,48 +18405,23 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129303122</v>
+        <v>129303145</v>
       </c>
       <c r="B158" t="n">
         <v>57736</v>
@@ -18496,10 +18456,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>523976</v>
+        <v>523898</v>
       </c>
       <c r="R158" t="n">
-        <v>7044021</v>
+        <v>7044169</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18536,7 +18496,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18563,7 +18523,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129303145</v>
+        <v>129303110</v>
       </c>
       <c r="B159" t="n">
         <v>57736</v>
@@ -18598,10 +18558,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>523898</v>
+        <v>524053</v>
       </c>
       <c r="R159" t="n">
-        <v>7044169</v>
+        <v>7043929</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18638,7 +18598,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18665,7 +18625,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129303110</v>
+        <v>129283727</v>
       </c>
       <c r="B160" t="n">
         <v>57736</v>
@@ -18694,16 +18654,21 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>524053</v>
+        <v>523881</v>
       </c>
       <c r="R160" t="n">
-        <v>7043929</v>
+        <v>7044149</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18733,14 +18698,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, färska, enstaka högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18751,16 +18726,41 @@
       </c>
       <c r="AG160" t="b">
         <v>0</v>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -20529,7 +20529,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129294096</v>
+        <v>129303100</v>
       </c>
       <c r="B177" t="n">
         <v>57736</v>
@@ -20558,24 +20558,19 @@
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>523971</v>
+        <v>524235</v>
       </c>
       <c r="R177" t="n">
-        <v>7044037</v>
+        <v>7043960</v>
       </c>
       <c r="S177" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20602,24 +20597,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20630,48 +20615,23 @@
       </c>
       <c r="AG177" t="b">
         <v>0</v>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129303100</v>
+        <v>129303143</v>
       </c>
       <c r="B178" t="n">
         <v>57736</v>
@@ -20706,10 +20666,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>524235</v>
+        <v>523911</v>
       </c>
       <c r="R178" t="n">
-        <v>7043960</v>
+        <v>7044178</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20746,7 +20706,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20773,7 +20733,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129303143</v>
+        <v>129303112</v>
       </c>
       <c r="B179" t="n">
         <v>57736</v>
@@ -20808,10 +20768,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>523911</v>
+        <v>524044</v>
       </c>
       <c r="R179" t="n">
-        <v>7044178</v>
+        <v>7043935</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20848,7 +20808,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20875,7 +20835,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129303112</v>
+        <v>129303116</v>
       </c>
       <c r="B180" t="n">
         <v>57736</v>
@@ -20910,10 +20870,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>524044</v>
+        <v>524033</v>
       </c>
       <c r="R180" t="n">
-        <v>7043935</v>
+        <v>7043952</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20977,7 +20937,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129303116</v>
+        <v>129303138</v>
       </c>
       <c r="B181" t="n">
         <v>57736</v>
@@ -21012,10 +20972,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>524033</v>
+        <v>523879</v>
       </c>
       <c r="R181" t="n">
-        <v>7043952</v>
+        <v>7044256</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21052,7 +21012,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21079,7 +21039,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129303138</v>
+        <v>129303131</v>
       </c>
       <c r="B182" t="n">
         <v>57736</v>
@@ -21114,10 +21074,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>523879</v>
+        <v>524059</v>
       </c>
       <c r="R182" t="n">
-        <v>7044256</v>
+        <v>7044016</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21181,7 +21141,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129303131</v>
+        <v>129303128</v>
       </c>
       <c r="B183" t="n">
         <v>57736</v>
@@ -21216,10 +21176,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>524059</v>
+        <v>524186</v>
       </c>
       <c r="R183" t="n">
-        <v>7044016</v>
+        <v>7043943</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21256,7 +21216,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21283,7 +21243,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129303128</v>
+        <v>129294096</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -21312,19 +21272,24 @@
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>524186</v>
+        <v>523971</v>
       </c>
       <c r="R184" t="n">
-        <v>7043943</v>
+        <v>7044037</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21351,14 +21316,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21369,16 +21344,41 @@
       </c>
       <c r="AG184" t="b">
         <v>0</v>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
@@ -22179,7 +22179,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129303141</v>
+        <v>129284163</v>
       </c>
       <c r="B192" t="n">
         <v>57736</v>
@@ -22208,19 +22208,24 @@
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>523902</v>
+        <v>523881</v>
       </c>
       <c r="R192" t="n">
-        <v>7044224</v>
+        <v>7044157</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22247,14 +22252,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22265,23 +22280,48 @@
       </c>
       <c r="AG192" t="b">
         <v>0</v>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129303140</v>
+        <v>129296040</v>
       </c>
       <c r="B193" t="n">
         <v>57736</v>
@@ -22310,16 +22350,21 @@
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>523866</v>
+        <v>524232</v>
       </c>
       <c r="R193" t="n">
-        <v>7044256</v>
+        <v>7043714</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22349,14 +22394,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22367,23 +22422,48 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129284163</v>
+        <v>129303141</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -22412,24 +22492,19 @@
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>523881</v>
+        <v>523902</v>
       </c>
       <c r="R194" t="n">
-        <v>7044157</v>
+        <v>7044224</v>
       </c>
       <c r="S194" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22456,24 +22531,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22484,48 +22549,23 @@
       </c>
       <c r="AG194" t="b">
         <v>0</v>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO194" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129296040</v>
+        <v>129303140</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -22554,21 +22594,16 @@
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>524232</v>
+        <v>523866</v>
       </c>
       <c r="R195" t="n">
-        <v>7043714</v>
+        <v>7044256</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22598,24 +22633,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22626,41 +22651,16 @@
       </c>
       <c r="AG195" t="b">
         <v>0</v>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO195" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -12920,10 +12920,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129303134</v>
+        <v>129294077</v>
       </c>
       <c r="B110" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12949,19 +12949,24 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>523912</v>
+        <v>523957</v>
       </c>
       <c r="R110" t="n">
-        <v>7044281</v>
+        <v>7044053</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12988,14 +12993,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13006,16 +13021,41 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -13025,7 +13065,7 @@
         <v>129303106</v>
       </c>
       <c r="B111" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13124,10 +13164,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129294077</v>
+        <v>129303134</v>
       </c>
       <c r="B112" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13153,24 +13193,19 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>523957</v>
+        <v>523912</v>
       </c>
       <c r="R112" t="n">
-        <v>7044053</v>
+        <v>7044281</v>
       </c>
       <c r="S112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13197,24 +13232,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13225,41 +13250,16 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -13269,7 +13269,7 @@
         <v>129303099</v>
       </c>
       <c r="B113" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13368,10 +13368,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129303107</v>
+        <v>129284656</v>
       </c>
       <c r="B114" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13397,19 +13397,24 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>524056</v>
+        <v>523856</v>
       </c>
       <c r="R114" t="n">
-        <v>7043920</v>
+        <v>7044190</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13436,14 +13441,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre, högt upp på en tall.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13454,26 +13469,51 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129303108</v>
+        <v>129303107</v>
       </c>
       <c r="B115" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13505,10 +13545,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524052</v>
+        <v>524056</v>
       </c>
       <c r="R115" t="n">
-        <v>7043922</v>
+        <v>7043920</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13545,7 +13585,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13572,10 +13612,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129303097</v>
+        <v>129303108</v>
       </c>
       <c r="B116" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13607,10 +13647,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524306</v>
+        <v>524052</v>
       </c>
       <c r="R116" t="n">
-        <v>7043867</v>
+        <v>7043922</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13647,7 +13687,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13674,10 +13714,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129284656</v>
+        <v>129303097</v>
       </c>
       <c r="B117" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13703,24 +13743,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>523856</v>
+        <v>524306</v>
       </c>
       <c r="R117" t="n">
-        <v>7044190</v>
+        <v>7043867</v>
       </c>
       <c r="S117" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13747,24 +13782,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, högt upp på en tall.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13775,41 +13800,16 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13819,7 +13819,7 @@
         <v>129303132</v>
       </c>
       <c r="B118" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13918,10 +13918,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129303120</v>
+        <v>129303118</v>
       </c>
       <c r="B119" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13953,10 +13953,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>523983</v>
+        <v>524000</v>
       </c>
       <c r="R119" t="n">
-        <v>7044011</v>
+        <v>7043995</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13993,7 +13993,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14020,10 +14020,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129303118</v>
+        <v>129303120</v>
       </c>
       <c r="B120" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524000</v>
+        <v>523983</v>
       </c>
       <c r="R120" t="n">
-        <v>7043995</v>
+        <v>7044011</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14122,10 +14122,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129303124</v>
+        <v>129286184</v>
       </c>
       <c r="B121" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14151,19 +14151,24 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523976</v>
+        <v>523842</v>
       </c>
       <c r="R121" t="n">
-        <v>7044029</v>
+        <v>7044233</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14190,14 +14195,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14208,26 +14223,51 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129303129</v>
+        <v>129292836</v>
       </c>
       <c r="B122" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14253,19 +14293,24 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524088</v>
+        <v>524162</v>
       </c>
       <c r="R122" t="n">
-        <v>7044015</v>
+        <v>7043929</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14292,14 +14337,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14310,26 +14365,51 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129286184</v>
+        <v>129303124</v>
       </c>
       <c r="B123" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14355,24 +14435,19 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>523842</v>
+        <v>523976</v>
       </c>
       <c r="R123" t="n">
-        <v>7044233</v>
+        <v>7044029</v>
       </c>
       <c r="S123" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14399,24 +14474,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14427,51 +14492,26 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129292836</v>
+        <v>129303129</v>
       </c>
       <c r="B124" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14497,24 +14537,19 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524162</v>
+        <v>524088</v>
       </c>
       <c r="R124" t="n">
-        <v>7043929</v>
+        <v>7044015</v>
       </c>
       <c r="S124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14541,24 +14576,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14569,41 +14594,16 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -14613,7 +14613,7 @@
         <v>129290167</v>
       </c>
       <c r="B125" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14752,10 +14752,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129303136</v>
+        <v>129303135</v>
       </c>
       <c r="B126" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14787,10 +14787,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523897</v>
+        <v>523902</v>
       </c>
       <c r="R126" t="n">
-        <v>7044281</v>
+        <v>7044288</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14827,7 +14827,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14854,10 +14854,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129303135</v>
+        <v>129303136</v>
       </c>
       <c r="B127" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14889,10 +14889,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523902</v>
+        <v>523897</v>
       </c>
       <c r="R127" t="n">
-        <v>7044288</v>
+        <v>7044281</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14959,7 +14959,7 @@
         <v>129303111</v>
       </c>
       <c r="B128" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15058,10 +15058,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129295685</v>
+        <v>129303087</v>
       </c>
       <c r="B129" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15087,21 +15087,16 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524198</v>
+        <v>524219</v>
       </c>
       <c r="R129" t="n">
-        <v>7043758</v>
+        <v>7043705</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15131,24 +15126,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15159,51 +15144,26 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129283648</v>
+        <v>129303133</v>
       </c>
       <c r="B130" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15229,21 +15189,16 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>523885</v>
+        <v>523992</v>
       </c>
       <c r="R130" t="n">
-        <v>7044152</v>
+        <v>7044262</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15273,24 +15228,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15301,51 +15246,26 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129285070</v>
+        <v>129303121</v>
       </c>
       <c r="B131" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15371,24 +15291,19 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>523844</v>
+        <v>523979</v>
       </c>
       <c r="R131" t="n">
-        <v>7044210</v>
+        <v>7044017</v>
       </c>
       <c r="S131" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15415,24 +15330,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15443,51 +15348,26 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129285747</v>
+        <v>129303081</v>
       </c>
       <c r="B132" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15513,24 +15393,19 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>523850</v>
+        <v>524190</v>
       </c>
       <c r="R132" t="n">
-        <v>7044210</v>
+        <v>7043804</v>
       </c>
       <c r="S132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15557,24 +15432,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15585,51 +15450,26 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129294128</v>
+        <v>129295685</v>
       </c>
       <c r="B133" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15657,19 +15497,19 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>523987</v>
+        <v>524198</v>
       </c>
       <c r="R133" t="n">
-        <v>7044025</v>
+        <v>7043758</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15701,7 +15541,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15711,12 +15551,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15768,10 +15608,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129303133</v>
+        <v>129283648</v>
       </c>
       <c r="B134" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15797,16 +15637,21 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>523992</v>
+        <v>523885</v>
       </c>
       <c r="R134" t="n">
-        <v>7044262</v>
+        <v>7044152</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15836,14 +15681,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15854,26 +15709,51 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129303081</v>
+        <v>129285070</v>
       </c>
       <c r="B135" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15899,19 +15779,24 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524190</v>
+        <v>523844</v>
       </c>
       <c r="R135" t="n">
-        <v>7043804</v>
+        <v>7044210</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15938,14 +15823,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15956,26 +15851,51 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129303121</v>
+        <v>129285747</v>
       </c>
       <c r="B136" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16001,19 +15921,24 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>523979</v>
+        <v>523850</v>
       </c>
       <c r="R136" t="n">
-        <v>7044017</v>
+        <v>7044210</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16040,14 +15965,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16058,26 +15993,51 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129303087</v>
+        <v>129294128</v>
       </c>
       <c r="B137" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16103,16 +16063,21 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>524219</v>
+        <v>523987</v>
       </c>
       <c r="R137" t="n">
-        <v>7043705</v>
+        <v>7044025</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16142,14 +16107,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16160,16 +16135,41 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16179,7 +16179,7 @@
         <v>129303137</v>
       </c>
       <c r="B138" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16278,10 +16278,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129295984</v>
+        <v>129303098</v>
       </c>
       <c r="B139" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16307,21 +16307,16 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>524244</v>
+        <v>524297</v>
       </c>
       <c r="R139" t="n">
-        <v>7043732</v>
+        <v>7043866</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16351,24 +16346,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16379,51 +16364,26 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129294143</v>
+        <v>129303093</v>
       </c>
       <c r="B140" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16449,24 +16409,19 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>523985</v>
+        <v>524246</v>
       </c>
       <c r="R140" t="n">
-        <v>7044028</v>
+        <v>7043787</v>
       </c>
       <c r="S140" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16493,24 +16448,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16521,41 +16466,16 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -16565,7 +16485,7 @@
         <v>129303092</v>
       </c>
       <c r="B141" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16667,7 +16587,7 @@
         <v>129303148</v>
       </c>
       <c r="B142" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16766,10 +16686,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129303098</v>
+        <v>129295984</v>
       </c>
       <c r="B143" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16795,16 +16715,21 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>524297</v>
+        <v>524244</v>
       </c>
       <c r="R143" t="n">
-        <v>7043866</v>
+        <v>7043732</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16834,14 +16759,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på gränsen till färska.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16852,26 +16787,51 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129303093</v>
+        <v>129294143</v>
       </c>
       <c r="B144" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16897,19 +16857,24 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>524246</v>
+        <v>523985</v>
       </c>
       <c r="R144" t="n">
-        <v>7043787</v>
+        <v>7044028</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16936,14 +16901,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16954,26 +16929,51 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129294174</v>
+        <v>129303127</v>
       </c>
       <c r="B145" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16999,24 +16999,19 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>523983</v>
+        <v>523955</v>
       </c>
       <c r="R145" t="n">
-        <v>7044020</v>
+        <v>7044054</v>
       </c>
       <c r="S145" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17043,24 +17038,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17071,51 +17056,26 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129303127</v>
+        <v>129303088</v>
       </c>
       <c r="B146" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17147,10 +17107,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>523955</v>
+        <v>524211</v>
       </c>
       <c r="R146" t="n">
-        <v>7044054</v>
+        <v>7043713</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17187,7 +17147,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17214,10 +17174,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129303088</v>
+        <v>129303115</v>
       </c>
       <c r="B147" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17249,10 +17209,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>524211</v>
+        <v>524039</v>
       </c>
       <c r="R147" t="n">
-        <v>7043713</v>
+        <v>7043944</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17289,7 +17249,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17316,10 +17276,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129303115</v>
+        <v>129294174</v>
       </c>
       <c r="B148" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17345,19 +17305,24 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>524039</v>
+        <v>523983</v>
       </c>
       <c r="R148" t="n">
-        <v>7043944</v>
+        <v>7044020</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17384,14 +17349,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17402,16 +17377,41 @@
       </c>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -17421,7 +17421,7 @@
         <v>129290810</v>
       </c>
       <c r="B149" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>129294258</v>
       </c>
       <c r="B150" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17707,10 +17707,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129303090</v>
+        <v>129303091</v>
       </c>
       <c r="B151" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17742,10 +17742,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>524194</v>
+        <v>524225</v>
       </c>
       <c r="R151" t="n">
-        <v>7043755</v>
+        <v>7043779</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17782,7 +17782,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17809,10 +17809,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129303123</v>
+        <v>129303139</v>
       </c>
       <c r="B152" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17844,10 +17844,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>523980</v>
+        <v>523860</v>
       </c>
       <c r="R152" t="n">
-        <v>7044026</v>
+        <v>7044250</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17884,7 +17884,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17911,10 +17911,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129303091</v>
+        <v>129303123</v>
       </c>
       <c r="B153" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17946,10 +17946,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>524225</v>
+        <v>523980</v>
       </c>
       <c r="R153" t="n">
-        <v>7043779</v>
+        <v>7044026</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18013,10 +18013,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129303139</v>
+        <v>129303090</v>
       </c>
       <c r="B154" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18048,10 +18048,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>523860</v>
+        <v>524194</v>
       </c>
       <c r="R154" t="n">
-        <v>7044250</v>
+        <v>7043755</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18088,7 +18088,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18118,7 +18118,7 @@
         <v>129303096</v>
       </c>
       <c r="B155" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>129303144</v>
       </c>
       <c r="B156" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18319,10 +18319,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129303122</v>
+        <v>129303145</v>
       </c>
       <c r="B157" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18354,10 +18354,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>523976</v>
+        <v>523898</v>
       </c>
       <c r="R157" t="n">
-        <v>7044021</v>
+        <v>7044169</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18421,10 +18421,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129303145</v>
+        <v>129303122</v>
       </c>
       <c r="B158" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18456,10 +18456,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>523898</v>
+        <v>523976</v>
       </c>
       <c r="R158" t="n">
-        <v>7044169</v>
+        <v>7044021</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18496,7 +18496,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18526,7 +18526,7 @@
         <v>129303110</v>
       </c>
       <c r="B159" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>129283727</v>
       </c>
       <c r="B160" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18767,10 +18767,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129303119</v>
+        <v>129291995</v>
       </c>
       <c r="B161" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18796,16 +18796,21 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>524000</v>
+        <v>524225</v>
       </c>
       <c r="R161" t="n">
-        <v>7044000</v>
+        <v>7043980</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18835,14 +18840,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18853,26 +18868,51 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129303095</v>
+        <v>129303082</v>
       </c>
       <c r="B162" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18904,10 +18944,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>524229</v>
+        <v>524269</v>
       </c>
       <c r="R162" t="n">
-        <v>7043821</v>
+        <v>7043735</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18944,7 +18984,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18971,10 +19011,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129303082</v>
+        <v>129303119</v>
       </c>
       <c r="B163" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19006,10 +19046,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>524269</v>
+        <v>524000</v>
       </c>
       <c r="R163" t="n">
-        <v>7043735</v>
+        <v>7044000</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19046,7 +19086,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19073,10 +19113,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129291995</v>
+        <v>129303095</v>
       </c>
       <c r="B164" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19102,21 +19142,16 @@
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>524225</v>
+        <v>524229</v>
       </c>
       <c r="R164" t="n">
-        <v>7043980</v>
+        <v>7043821</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19146,24 +19181,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19174,41 +19199,16 @@
       </c>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -19218,7 +19218,7 @@
         <v>129290684</v>
       </c>
       <c r="B165" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>129295476</v>
       </c>
       <c r="B166" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19509,10 +19509,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303094</v>
+        <v>129303117</v>
       </c>
       <c r="B167" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19544,10 +19544,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>524244</v>
+        <v>524002</v>
       </c>
       <c r="R167" t="n">
-        <v>7043795</v>
+        <v>7043990</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19611,10 +19611,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129303117</v>
+        <v>129303094</v>
       </c>
       <c r="B168" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19646,10 +19646,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>524002</v>
+        <v>524244</v>
       </c>
       <c r="R168" t="n">
-        <v>7043990</v>
+        <v>7043795</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19716,7 +19716,7 @@
         <v>129303101</v>
       </c>
       <c r="B169" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>129303125</v>
       </c>
       <c r="B170" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19917,10 +19917,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129303130</v>
+        <v>129303113</v>
       </c>
       <c r="B171" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19952,10 +19952,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>524087</v>
+        <v>524042</v>
       </c>
       <c r="R171" t="n">
-        <v>7044036</v>
+        <v>7043944</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20022,7 +20022,7 @@
         <v>129303104</v>
       </c>
       <c r="B172" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20121,10 +20121,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129303113</v>
+        <v>129303142</v>
       </c>
       <c r="B173" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20156,10 +20156,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>524042</v>
+        <v>523900</v>
       </c>
       <c r="R173" t="n">
-        <v>7043944</v>
+        <v>7044204</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20223,10 +20223,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129303142</v>
+        <v>129303109</v>
       </c>
       <c r="B174" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20258,10 +20258,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>523900</v>
+        <v>524053</v>
       </c>
       <c r="R174" t="n">
-        <v>7044204</v>
+        <v>7043923</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20325,10 +20325,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129303109</v>
+        <v>129303130</v>
       </c>
       <c r="B175" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20360,10 +20360,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>524053</v>
+        <v>524087</v>
       </c>
       <c r="R175" t="n">
-        <v>7043923</v>
+        <v>7044036</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20400,7 +20400,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20430,7 +20430,7 @@
         <v>129303105</v>
       </c>
       <c r="B176" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20529,10 +20529,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129303100</v>
+        <v>129294096</v>
       </c>
       <c r="B177" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20558,19 +20558,24 @@
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>524235</v>
+        <v>523971</v>
       </c>
       <c r="R177" t="n">
-        <v>7043960</v>
+        <v>7044037</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20597,14 +20602,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20615,26 +20630,51 @@
       </c>
       <c r="AG177" t="b">
         <v>0</v>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129303143</v>
+        <v>129303131</v>
       </c>
       <c r="B178" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20666,10 +20706,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>523911</v>
+        <v>524059</v>
       </c>
       <c r="R178" t="n">
-        <v>7044178</v>
+        <v>7044016</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20706,7 +20746,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20733,10 +20773,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129303112</v>
+        <v>129303100</v>
       </c>
       <c r="B179" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20768,10 +20808,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>524044</v>
+        <v>524235</v>
       </c>
       <c r="R179" t="n">
-        <v>7043935</v>
+        <v>7043960</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20808,7 +20848,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20835,10 +20875,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129303116</v>
+        <v>129303143</v>
       </c>
       <c r="B180" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20870,10 +20910,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>524033</v>
+        <v>523911</v>
       </c>
       <c r="R180" t="n">
-        <v>7043952</v>
+        <v>7044178</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20910,7 +20950,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20937,10 +20977,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129303138</v>
+        <v>129303128</v>
       </c>
       <c r="B181" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20972,10 +21012,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>523879</v>
+        <v>524186</v>
       </c>
       <c r="R181" t="n">
-        <v>7044256</v>
+        <v>7043943</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21012,7 +21052,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21039,10 +21079,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129303131</v>
+        <v>129303116</v>
       </c>
       <c r="B182" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21074,10 +21114,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>524059</v>
+        <v>524033</v>
       </c>
       <c r="R182" t="n">
-        <v>7044016</v>
+        <v>7043952</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21114,7 +21154,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21141,10 +21181,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129303128</v>
+        <v>129303112</v>
       </c>
       <c r="B183" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21176,10 +21216,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>524186</v>
+        <v>524044</v>
       </c>
       <c r="R183" t="n">
-        <v>7043943</v>
+        <v>7043935</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21243,10 +21283,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129294096</v>
+        <v>129303138</v>
       </c>
       <c r="B184" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21272,24 +21312,19 @@
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>523971</v>
+        <v>523879</v>
       </c>
       <c r="R184" t="n">
-        <v>7044037</v>
+        <v>7044256</v>
       </c>
       <c r="S184" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21316,24 +21351,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21344,41 +21369,16 @@
       </c>
       <c r="AG184" t="b">
         <v>0</v>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
@@ -21388,7 +21388,7 @@
         <v>129284399</v>
       </c>
       <c r="B185" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21527,10 +21527,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129303147</v>
+        <v>129303146</v>
       </c>
       <c r="B186" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21562,10 +21562,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>523930</v>
+        <v>523926</v>
       </c>
       <c r="R186" t="n">
-        <v>7044107</v>
+        <v>7044118</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21602,7 +21602,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21629,10 +21629,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129303146</v>
+        <v>129303114</v>
       </c>
       <c r="B187" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21664,10 +21664,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>523926</v>
+        <v>524041</v>
       </c>
       <c r="R187" t="n">
-        <v>7044118</v>
+        <v>7043942</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21704,7 +21704,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21731,10 +21731,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129303126</v>
+        <v>129303147</v>
       </c>
       <c r="B188" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21766,10 +21766,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>523960</v>
+        <v>523930</v>
       </c>
       <c r="R188" t="n">
-        <v>7044047</v>
+        <v>7044107</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21806,7 +21806,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21833,10 +21833,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129303114</v>
+        <v>129303126</v>
       </c>
       <c r="B189" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21868,10 +21868,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>524041</v>
+        <v>523960</v>
       </c>
       <c r="R189" t="n">
-        <v>7043942</v>
+        <v>7044047</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21908,7 +21908,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21935,10 +21935,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129290433</v>
+        <v>129303103</v>
       </c>
       <c r="B190" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21964,24 +21964,19 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>524140</v>
+        <v>524143</v>
       </c>
       <c r="R190" t="n">
-        <v>7044077</v>
+        <v>7043912</v>
       </c>
       <c r="S190" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -22008,24 +22003,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, tydliga på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22036,51 +22021,26 @@
       </c>
       <c r="AG190" t="b">
         <v>0</v>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO190" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129303103</v>
+        <v>129290433</v>
       </c>
       <c r="B191" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22106,19 +22066,24 @@
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>524143</v>
+        <v>524140</v>
       </c>
       <c r="R191" t="n">
-        <v>7043912</v>
+        <v>7044077</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -22145,14 +22110,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, tydliga på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22163,16 +22138,41 @@
       </c>
       <c r="AG191" t="b">
         <v>0</v>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -22182,7 +22182,7 @@
         <v>129284163</v>
       </c>
       <c r="B192" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>129296040</v>
       </c>
       <c r="B193" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>129303141</v>
       </c>
       <c r="B194" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>129303140</v>
       </c>
       <c r="B195" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -16278,7 +16278,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129303098</v>
+        <v>129303148</v>
       </c>
       <c r="B139" t="n">
         <v>57737</v>
@@ -16313,10 +16313,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>524297</v>
+        <v>523952</v>
       </c>
       <c r="R139" t="n">
-        <v>7043866</v>
+        <v>7044072</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16380,7 +16380,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129303093</v>
+        <v>129295984</v>
       </c>
       <c r="B140" t="n">
         <v>57737</v>
@@ -16409,16 +16409,21 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>524246</v>
+        <v>524244</v>
       </c>
       <c r="R140" t="n">
-        <v>7043787</v>
+        <v>7043732</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16448,14 +16453,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på gränsen till färska.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16466,23 +16481,48 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129303092</v>
+        <v>129294143</v>
       </c>
       <c r="B141" t="n">
         <v>57737</v>
@@ -16511,19 +16551,24 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>524227</v>
+        <v>523985</v>
       </c>
       <c r="R141" t="n">
-        <v>7043799</v>
+        <v>7044028</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16550,14 +16595,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16568,23 +16623,48 @@
       </c>
       <c r="AG141" t="b">
         <v>0</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129303148</v>
+        <v>129303098</v>
       </c>
       <c r="B142" t="n">
         <v>57737</v>
@@ -16619,10 +16699,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>523952</v>
+        <v>524297</v>
       </c>
       <c r="R142" t="n">
-        <v>7044072</v>
+        <v>7043866</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16659,7 +16739,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16686,7 +16766,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129295984</v>
+        <v>129303093</v>
       </c>
       <c r="B143" t="n">
         <v>57737</v>
@@ -16715,21 +16795,16 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>524244</v>
+        <v>524246</v>
       </c>
       <c r="R143" t="n">
-        <v>7043732</v>
+        <v>7043787</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16759,24 +16834,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16787,48 +16852,23 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129294143</v>
+        <v>129303092</v>
       </c>
       <c r="B144" t="n">
         <v>57737</v>
@@ -16857,24 +16897,19 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>523985</v>
+        <v>524227</v>
       </c>
       <c r="R144" t="n">
-        <v>7044028</v>
+        <v>7043799</v>
       </c>
       <c r="S144" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16901,24 +16936,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16929,41 +16954,16 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -17707,7 +17707,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129303091</v>
+        <v>129303096</v>
       </c>
       <c r="B151" t="n">
         <v>57737</v>
@@ -17742,10 +17742,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>524225</v>
+        <v>524226</v>
       </c>
       <c r="R151" t="n">
-        <v>7043779</v>
+        <v>7043829</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17809,7 +17809,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129303139</v>
+        <v>129303123</v>
       </c>
       <c r="B152" t="n">
         <v>57737</v>
@@ -17844,10 +17844,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>523860</v>
+        <v>523980</v>
       </c>
       <c r="R152" t="n">
-        <v>7044250</v>
+        <v>7044026</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17884,7 +17884,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17911,7 +17911,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129303123</v>
+        <v>129303090</v>
       </c>
       <c r="B153" t="n">
         <v>57737</v>
@@ -17946,10 +17946,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>523980</v>
+        <v>524194</v>
       </c>
       <c r="R153" t="n">
-        <v>7044026</v>
+        <v>7043755</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18013,7 +18013,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129303090</v>
+        <v>129303144</v>
       </c>
       <c r="B154" t="n">
         <v>57737</v>
@@ -18048,10 +18048,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>524194</v>
+        <v>523900</v>
       </c>
       <c r="R154" t="n">
-        <v>7043755</v>
+        <v>7044174</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18088,7 +18088,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18115,7 +18115,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129303096</v>
+        <v>129303091</v>
       </c>
       <c r="B155" t="n">
         <v>57737</v>
@@ -18150,10 +18150,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>524226</v>
+        <v>524225</v>
       </c>
       <c r="R155" t="n">
-        <v>7043829</v>
+        <v>7043779</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18217,7 +18217,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129303144</v>
+        <v>129303139</v>
       </c>
       <c r="B156" t="n">
         <v>57737</v>
@@ -18252,10 +18252,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>523900</v>
+        <v>523860</v>
       </c>
       <c r="R156" t="n">
-        <v>7044174</v>
+        <v>7044250</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18292,7 +18292,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18909,7 +18909,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129303082</v>
+        <v>129303095</v>
       </c>
       <c r="B162" t="n">
         <v>57737</v>
@@ -18944,10 +18944,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>524269</v>
+        <v>524229</v>
       </c>
       <c r="R162" t="n">
-        <v>7043735</v>
+        <v>7043821</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18984,7 +18984,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19011,7 +19011,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129303119</v>
+        <v>129303082</v>
       </c>
       <c r="B163" t="n">
         <v>57737</v>
@@ -19046,10 +19046,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>524000</v>
+        <v>524269</v>
       </c>
       <c r="R163" t="n">
-        <v>7044000</v>
+        <v>7043735</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19086,7 +19086,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19113,7 +19113,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129303095</v>
+        <v>129303119</v>
       </c>
       <c r="B164" t="n">
         <v>57737</v>
@@ -19148,10 +19148,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>524229</v>
+        <v>524000</v>
       </c>
       <c r="R164" t="n">
-        <v>7043821</v>
+        <v>7044000</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -12923,7 +12923,7 @@
         <v>129294077</v>
       </c>
       <c r="B110" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13062,10 +13062,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129303106</v>
+        <v>129303134</v>
       </c>
       <c r="B111" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>524060</v>
+        <v>523912</v>
       </c>
       <c r="R111" t="n">
-        <v>7043917</v>
+        <v>7044281</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13164,10 +13164,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129303134</v>
+        <v>129303106</v>
       </c>
       <c r="B112" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13199,10 +13199,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>523912</v>
+        <v>524060</v>
       </c>
       <c r="R112" t="n">
-        <v>7044281</v>
+        <v>7043917</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13239,7 +13239,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13269,7 +13269,7 @@
         <v>129303099</v>
       </c>
       <c r="B113" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>129284656</v>
       </c>
       <c r="B114" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>129303107</v>
       </c>
       <c r="B115" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>129303108</v>
       </c>
       <c r="B116" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>129303097</v>
       </c>
       <c r="B117" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>129303132</v>
       </c>
       <c r="B118" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13918,10 +13918,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129303118</v>
+        <v>129303120</v>
       </c>
       <c r="B119" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13953,10 +13953,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524000</v>
+        <v>523983</v>
       </c>
       <c r="R119" t="n">
-        <v>7043995</v>
+        <v>7044011</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13993,7 +13993,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14020,10 +14020,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129303120</v>
+        <v>129303118</v>
       </c>
       <c r="B120" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>523983</v>
+        <v>524000</v>
       </c>
       <c r="R120" t="n">
-        <v>7044011</v>
+        <v>7043995</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14125,7 +14125,7 @@
         <v>129286184</v>
       </c>
       <c r="B121" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>129292836</v>
       </c>
       <c r="B122" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>129303124</v>
       </c>
       <c r="B123" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>129303129</v>
       </c>
       <c r="B124" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>129290167</v>
       </c>
       <c r="B125" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14752,10 +14752,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129303135</v>
+        <v>129303111</v>
       </c>
       <c r="B126" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14787,10 +14787,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523902</v>
+        <v>524047</v>
       </c>
       <c r="R126" t="n">
-        <v>7044288</v>
+        <v>7043931</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14827,7 +14827,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14857,7 +14857,7 @@
         <v>129303136</v>
       </c>
       <c r="B127" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14956,10 +14956,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129303111</v>
+        <v>129303135</v>
       </c>
       <c r="B128" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14991,10 +14991,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>524047</v>
+        <v>523902</v>
       </c>
       <c r="R128" t="n">
-        <v>7043931</v>
+        <v>7044288</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15058,10 +15058,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129303087</v>
+        <v>129295685</v>
       </c>
       <c r="B129" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15087,16 +15087,21 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524219</v>
+        <v>524198</v>
       </c>
       <c r="R129" t="n">
-        <v>7043705</v>
+        <v>7043758</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15126,14 +15131,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15144,26 +15159,51 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129303133</v>
+        <v>129283648</v>
       </c>
       <c r="B130" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15189,16 +15229,21 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>523992</v>
+        <v>523885</v>
       </c>
       <c r="R130" t="n">
-        <v>7044262</v>
+        <v>7044152</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15228,14 +15273,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15246,26 +15301,51 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129303121</v>
+        <v>129285070</v>
       </c>
       <c r="B131" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15291,19 +15371,24 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>523979</v>
+        <v>523844</v>
       </c>
       <c r="R131" t="n">
-        <v>7044017</v>
+        <v>7044210</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15330,14 +15415,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15348,26 +15443,51 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129303081</v>
+        <v>129285747</v>
       </c>
       <c r="B132" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15393,19 +15513,24 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524190</v>
+        <v>523850</v>
       </c>
       <c r="R132" t="n">
-        <v>7043804</v>
+        <v>7044210</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15432,14 +15557,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15450,26 +15585,51 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129295685</v>
+        <v>129294128</v>
       </c>
       <c r="B133" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15497,19 +15657,19 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524198</v>
+        <v>523987</v>
       </c>
       <c r="R133" t="n">
-        <v>7043758</v>
+        <v>7044025</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15541,7 +15701,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15551,12 +15711,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15608,10 +15768,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129283648</v>
+        <v>129303133</v>
       </c>
       <c r="B134" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15637,21 +15797,16 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>523885</v>
+        <v>523992</v>
       </c>
       <c r="R134" t="n">
-        <v>7044152</v>
+        <v>7044262</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15681,24 +15836,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15709,51 +15854,26 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129285070</v>
+        <v>129303081</v>
       </c>
       <c r="B135" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15779,24 +15899,19 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>523844</v>
+        <v>524190</v>
       </c>
       <c r="R135" t="n">
-        <v>7044210</v>
+        <v>7043804</v>
       </c>
       <c r="S135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15823,24 +15938,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15851,51 +15956,26 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129285747</v>
+        <v>129303121</v>
       </c>
       <c r="B136" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15921,24 +16001,19 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>523850</v>
+        <v>523979</v>
       </c>
       <c r="R136" t="n">
-        <v>7044210</v>
+        <v>7044017</v>
       </c>
       <c r="S136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15965,24 +16040,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15993,51 +16058,26 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129294128</v>
+        <v>129303087</v>
       </c>
       <c r="B137" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16063,21 +16103,16 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>523987</v>
+        <v>524219</v>
       </c>
       <c r="R137" t="n">
-        <v>7044025</v>
+        <v>7043705</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16107,24 +16142,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16135,41 +16160,16 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16179,7 +16179,7 @@
         <v>129303137</v>
       </c>
       <c r="B138" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16278,10 +16278,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129303148</v>
+        <v>129303092</v>
       </c>
       <c r="B139" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16313,10 +16313,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>523952</v>
+        <v>524227</v>
       </c>
       <c r="R139" t="n">
-        <v>7044072</v>
+        <v>7043799</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16380,10 +16380,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129295984</v>
+        <v>129303148</v>
       </c>
       <c r="B140" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16409,21 +16409,16 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>524244</v>
+        <v>523952</v>
       </c>
       <c r="R140" t="n">
-        <v>7043732</v>
+        <v>7044072</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16453,24 +16448,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16481,51 +16466,26 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129294143</v>
+        <v>129303098</v>
       </c>
       <c r="B141" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16551,24 +16511,19 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>523985</v>
+        <v>524297</v>
       </c>
       <c r="R141" t="n">
-        <v>7044028</v>
+        <v>7043866</v>
       </c>
       <c r="S141" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16595,24 +16550,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16623,51 +16568,26 @@
       </c>
       <c r="AG141" t="b">
         <v>0</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129303098</v>
+        <v>129303093</v>
       </c>
       <c r="B142" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16699,10 +16619,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>524297</v>
+        <v>524246</v>
       </c>
       <c r="R142" t="n">
-        <v>7043866</v>
+        <v>7043787</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16739,7 +16659,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16766,10 +16686,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129303093</v>
+        <v>129295984</v>
       </c>
       <c r="B143" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16795,16 +16715,21 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>524246</v>
+        <v>524244</v>
       </c>
       <c r="R143" t="n">
-        <v>7043787</v>
+        <v>7043732</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16834,14 +16759,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på gränsen till färska.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16852,26 +16787,51 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129303092</v>
+        <v>129294143</v>
       </c>
       <c r="B144" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16897,19 +16857,24 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>524227</v>
+        <v>523985</v>
       </c>
       <c r="R144" t="n">
-        <v>7043799</v>
+        <v>7044028</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16936,14 +16901,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16954,26 +16929,51 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129303127</v>
+        <v>129294174</v>
       </c>
       <c r="B145" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16999,19 +16999,24 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>523955</v>
+        <v>523983</v>
       </c>
       <c r="R145" t="n">
-        <v>7044054</v>
+        <v>7044020</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17038,14 +17043,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17056,26 +17071,51 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129303088</v>
+        <v>129303127</v>
       </c>
       <c r="B146" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17107,10 +17147,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>524211</v>
+        <v>523955</v>
       </c>
       <c r="R146" t="n">
-        <v>7043713</v>
+        <v>7044054</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17147,7 +17187,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17174,10 +17214,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129303115</v>
+        <v>129303088</v>
       </c>
       <c r="B147" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17209,10 +17249,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>524039</v>
+        <v>524211</v>
       </c>
       <c r="R147" t="n">
-        <v>7043944</v>
+        <v>7043713</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17249,7 +17289,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17276,10 +17316,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129294174</v>
+        <v>129303115</v>
       </c>
       <c r="B148" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17305,24 +17345,19 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>523983</v>
+        <v>524039</v>
       </c>
       <c r="R148" t="n">
-        <v>7044020</v>
+        <v>7043944</v>
       </c>
       <c r="S148" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17349,24 +17384,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17377,41 +17402,16 @@
       </c>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -17421,7 +17421,7 @@
         <v>129290810</v>
       </c>
       <c r="B149" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>129294258</v>
       </c>
       <c r="B150" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17707,10 +17707,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129303096</v>
+        <v>129303090</v>
       </c>
       <c r="B151" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17742,10 +17742,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>524226</v>
+        <v>524194</v>
       </c>
       <c r="R151" t="n">
-        <v>7043829</v>
+        <v>7043755</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17782,7 +17782,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17812,7 +17812,7 @@
         <v>129303123</v>
       </c>
       <c r="B152" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17911,10 +17911,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129303090</v>
+        <v>129303091</v>
       </c>
       <c r="B153" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17946,10 +17946,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>524194</v>
+        <v>524225</v>
       </c>
       <c r="R153" t="n">
-        <v>7043755</v>
+        <v>7043779</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18013,10 +18013,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129303144</v>
+        <v>129303139</v>
       </c>
       <c r="B154" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18048,10 +18048,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>523900</v>
+        <v>523860</v>
       </c>
       <c r="R154" t="n">
-        <v>7044174</v>
+        <v>7044250</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18088,7 +18088,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18115,10 +18115,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129303091</v>
+        <v>129303096</v>
       </c>
       <c r="B155" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18150,10 +18150,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>524225</v>
+        <v>524226</v>
       </c>
       <c r="R155" t="n">
-        <v>7043779</v>
+        <v>7043829</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18217,10 +18217,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129303139</v>
+        <v>129303144</v>
       </c>
       <c r="B156" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18252,10 +18252,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>523860</v>
+        <v>523900</v>
       </c>
       <c r="R156" t="n">
-        <v>7044250</v>
+        <v>7044174</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18292,7 +18292,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18319,10 +18319,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129303145</v>
+        <v>129283727</v>
       </c>
       <c r="B157" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18348,16 +18348,21 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>523898</v>
+        <v>523881</v>
       </c>
       <c r="R157" t="n">
-        <v>7044169</v>
+        <v>7044149</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18387,14 +18392,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska, enstaka högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18405,16 +18420,41 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -18424,7 +18464,7 @@
         <v>129303122</v>
       </c>
       <c r="B158" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18523,10 +18563,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129303110</v>
+        <v>129303145</v>
       </c>
       <c r="B159" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18558,10 +18598,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>524053</v>
+        <v>523898</v>
       </c>
       <c r="R159" t="n">
-        <v>7043929</v>
+        <v>7044169</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18598,7 +18638,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18625,10 +18665,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129283727</v>
+        <v>129303110</v>
       </c>
       <c r="B160" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18654,21 +18694,16 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>523881</v>
+        <v>524053</v>
       </c>
       <c r="R160" t="n">
-        <v>7044149</v>
+        <v>7043929</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18698,24 +18733,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka högt upp på en gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18726,41 +18751,16 @@
       </c>
       <c r="AG160" t="b">
         <v>0</v>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -18770,7 +18770,7 @@
         <v>129291995</v>
       </c>
       <c r="B161" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18909,10 +18909,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129303095</v>
+        <v>129303119</v>
       </c>
       <c r="B162" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18944,10 +18944,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>524229</v>
+        <v>524000</v>
       </c>
       <c r="R162" t="n">
-        <v>7043821</v>
+        <v>7044000</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19011,10 +19011,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129303082</v>
+        <v>129303095</v>
       </c>
       <c r="B163" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19046,10 +19046,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>524269</v>
+        <v>524229</v>
       </c>
       <c r="R163" t="n">
-        <v>7043735</v>
+        <v>7043821</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19086,7 +19086,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19113,10 +19113,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129303119</v>
+        <v>129303082</v>
       </c>
       <c r="B164" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19148,10 +19148,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>524000</v>
+        <v>524269</v>
       </c>
       <c r="R164" t="n">
-        <v>7044000</v>
+        <v>7043735</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19188,7 +19188,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19215,10 +19215,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129290684</v>
+        <v>129303094</v>
       </c>
       <c r="B165" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19244,29 +19244,19 @@
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>524150</v>
+        <v>524244</v>
       </c>
       <c r="R165" t="n">
-        <v>7044038</v>
+        <v>7043795</v>
       </c>
       <c r="S165" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19293,24 +19283,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19321,51 +19301,26 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129295476</v>
+        <v>129303117</v>
       </c>
       <c r="B166" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19391,29 +19346,19 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>524222</v>
+        <v>524002</v>
       </c>
       <c r="R166" t="n">
-        <v>7043799</v>
+        <v>7043990</v>
       </c>
       <c r="S166" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19440,24 +19385,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19468,51 +19403,26 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303117</v>
+        <v>129303101</v>
       </c>
       <c r="B167" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19544,10 +19454,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>524002</v>
+        <v>524169</v>
       </c>
       <c r="R167" t="n">
-        <v>7043990</v>
+        <v>7043927</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19584,7 +19494,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19611,10 +19521,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129303094</v>
+        <v>129303125</v>
       </c>
       <c r="B168" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19646,10 +19556,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>524244</v>
+        <v>523973</v>
       </c>
       <c r="R168" t="n">
-        <v>7043795</v>
+        <v>7044031</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19686,7 +19596,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19713,10 +19623,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129303101</v>
+        <v>129290684</v>
       </c>
       <c r="B169" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19742,19 +19652,29 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>524169</v>
+        <v>524150</v>
       </c>
       <c r="R169" t="n">
-        <v>7043927</v>
+        <v>7044038</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19781,14 +19701,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19799,26 +19729,51 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129303125</v>
+        <v>129295476</v>
       </c>
       <c r="B170" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19844,19 +19799,29 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>523973</v>
+        <v>524222</v>
       </c>
       <c r="R170" t="n">
-        <v>7044031</v>
+        <v>7043799</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19883,14 +19848,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19901,26 +19876,51 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129303113</v>
+        <v>129303130</v>
       </c>
       <c r="B171" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19952,10 +19952,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>524042</v>
+        <v>524087</v>
       </c>
       <c r="R171" t="n">
-        <v>7043944</v>
+        <v>7044036</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20022,7 +20022,7 @@
         <v>129303104</v>
       </c>
       <c r="B172" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20121,10 +20121,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129303142</v>
+        <v>129303113</v>
       </c>
       <c r="B173" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20156,10 +20156,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>523900</v>
+        <v>524042</v>
       </c>
       <c r="R173" t="n">
-        <v>7044204</v>
+        <v>7043944</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20223,10 +20223,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129303109</v>
+        <v>129303142</v>
       </c>
       <c r="B174" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20258,10 +20258,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>524053</v>
+        <v>523900</v>
       </c>
       <c r="R174" t="n">
-        <v>7043923</v>
+        <v>7044204</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20325,10 +20325,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129303130</v>
+        <v>129303109</v>
       </c>
       <c r="B175" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20360,10 +20360,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>524087</v>
+        <v>524053</v>
       </c>
       <c r="R175" t="n">
-        <v>7044036</v>
+        <v>7043923</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20400,7 +20400,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20430,7 +20430,7 @@
         <v>129303105</v>
       </c>
       <c r="B176" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>129294096</v>
       </c>
       <c r="B177" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20671,10 +20671,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129303131</v>
+        <v>129303100</v>
       </c>
       <c r="B178" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20706,10 +20706,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>524059</v>
+        <v>524235</v>
       </c>
       <c r="R178" t="n">
-        <v>7044016</v>
+        <v>7043960</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20773,10 +20773,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129303100</v>
+        <v>129303143</v>
       </c>
       <c r="B179" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20808,10 +20808,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>524235</v>
+        <v>523911</v>
       </c>
       <c r="R179" t="n">
-        <v>7043960</v>
+        <v>7044178</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20848,7 +20848,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20875,10 +20875,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129303143</v>
+        <v>129303112</v>
       </c>
       <c r="B180" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20910,10 +20910,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>523911</v>
+        <v>524044</v>
       </c>
       <c r="R180" t="n">
-        <v>7044178</v>
+        <v>7043935</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20950,7 +20950,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20977,10 +20977,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129303128</v>
+        <v>129303116</v>
       </c>
       <c r="B181" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21012,10 +21012,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>524186</v>
+        <v>524033</v>
       </c>
       <c r="R181" t="n">
-        <v>7043943</v>
+        <v>7043952</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21079,10 +21079,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129303116</v>
+        <v>129303138</v>
       </c>
       <c r="B182" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21114,10 +21114,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>524033</v>
+        <v>523879</v>
       </c>
       <c r="R182" t="n">
-        <v>7043952</v>
+        <v>7044256</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21181,10 +21181,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129303112</v>
+        <v>129303131</v>
       </c>
       <c r="B183" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21216,10 +21216,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>524044</v>
+        <v>524059</v>
       </c>
       <c r="R183" t="n">
-        <v>7043935</v>
+        <v>7044016</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21256,7 +21256,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21283,10 +21283,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129303138</v>
+        <v>129303128</v>
       </c>
       <c r="B184" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21318,10 +21318,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>523879</v>
+        <v>524186</v>
       </c>
       <c r="R184" t="n">
-        <v>7044256</v>
+        <v>7043943</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21358,7 +21358,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21388,7 +21388,7 @@
         <v>129284399</v>
       </c>
       <c r="B185" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21527,10 +21527,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129303146</v>
+        <v>129303147</v>
       </c>
       <c r="B186" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21562,10 +21562,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>523926</v>
+        <v>523930</v>
       </c>
       <c r="R186" t="n">
-        <v>7044118</v>
+        <v>7044107</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21602,7 +21602,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21629,10 +21629,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129303114</v>
+        <v>129303146</v>
       </c>
       <c r="B187" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21664,10 +21664,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>524041</v>
+        <v>523926</v>
       </c>
       <c r="R187" t="n">
-        <v>7043942</v>
+        <v>7044118</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21704,7 +21704,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21731,10 +21731,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129303147</v>
+        <v>129303126</v>
       </c>
       <c r="B188" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21766,10 +21766,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>523930</v>
+        <v>523960</v>
       </c>
       <c r="R188" t="n">
-        <v>7044107</v>
+        <v>7044047</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21806,7 +21806,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21833,10 +21833,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129303126</v>
+        <v>129303114</v>
       </c>
       <c r="B189" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21868,10 +21868,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>523960</v>
+        <v>524041</v>
       </c>
       <c r="R189" t="n">
-        <v>7044047</v>
+        <v>7043942</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21908,7 +21908,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21935,10 +21935,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129303103</v>
+        <v>129290433</v>
       </c>
       <c r="B190" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21964,19 +21964,24 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>524143</v>
+        <v>524140</v>
       </c>
       <c r="R190" t="n">
-        <v>7043912</v>
+        <v>7044077</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -22003,14 +22008,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, tydliga på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22021,26 +22036,51 @@
       </c>
       <c r="AG190" t="b">
         <v>0</v>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129290433</v>
+        <v>129303103</v>
       </c>
       <c r="B191" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22066,24 +22106,19 @@
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>524140</v>
+        <v>524143</v>
       </c>
       <c r="R191" t="n">
-        <v>7044077</v>
+        <v>7043912</v>
       </c>
       <c r="S191" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -22110,24 +22145,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, tydliga på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22138,51 +22163,26 @@
       </c>
       <c r="AG191" t="b">
         <v>0</v>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO191" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129284163</v>
+        <v>129296040</v>
       </c>
       <c r="B192" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22215,17 +22215,17 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>523881</v>
+        <v>524232</v>
       </c>
       <c r="R192" t="n">
-        <v>7044157</v>
+        <v>7043714</v>
       </c>
       <c r="S192" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -22264,12 +22264,12 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22321,10 +22321,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129296040</v>
+        <v>129284163</v>
       </c>
       <c r="B193" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22357,17 +22357,17 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>524232</v>
+        <v>523881</v>
       </c>
       <c r="R193" t="n">
-        <v>7043714</v>
+        <v>7044157</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -22406,12 +22406,12 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22466,7 +22466,7 @@
         <v>129303141</v>
       </c>
       <c r="B194" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>129303140</v>
       </c>
       <c r="B195" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -16278,7 +16278,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129303092</v>
+        <v>129295984</v>
       </c>
       <c r="B139" t="n">
         <v>57740</v>
@@ -16307,16 +16307,21 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>524227</v>
+        <v>524244</v>
       </c>
       <c r="R139" t="n">
-        <v>7043799</v>
+        <v>7043732</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16346,14 +16351,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på gränsen till färska.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16364,23 +16379,48 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129303148</v>
+        <v>129294143</v>
       </c>
       <c r="B140" t="n">
         <v>57740</v>
@@ -16409,19 +16449,24 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>523952</v>
+        <v>523985</v>
       </c>
       <c r="R140" t="n">
-        <v>7044072</v>
+        <v>7044028</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16448,14 +16493,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16466,23 +16521,48 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129303098</v>
+        <v>129303092</v>
       </c>
       <c r="B141" t="n">
         <v>57740</v>
@@ -16517,10 +16597,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>524297</v>
+        <v>524227</v>
       </c>
       <c r="R141" t="n">
-        <v>7043866</v>
+        <v>7043799</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16557,7 +16637,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16584,7 +16664,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129303093</v>
+        <v>129303148</v>
       </c>
       <c r="B142" t="n">
         <v>57740</v>
@@ -16619,10 +16699,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>524246</v>
+        <v>523952</v>
       </c>
       <c r="R142" t="n">
-        <v>7043787</v>
+        <v>7044072</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16659,7 +16739,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16686,7 +16766,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129295984</v>
+        <v>129303098</v>
       </c>
       <c r="B143" t="n">
         <v>57740</v>
@@ -16715,21 +16795,16 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>524244</v>
+        <v>524297</v>
       </c>
       <c r="R143" t="n">
-        <v>7043732</v>
+        <v>7043866</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16759,24 +16834,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16787,48 +16852,23 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129294143</v>
+        <v>129303093</v>
       </c>
       <c r="B144" t="n">
         <v>57740</v>
@@ -16857,24 +16897,19 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>523985</v>
+        <v>524246</v>
       </c>
       <c r="R144" t="n">
-        <v>7044028</v>
+        <v>7043787</v>
       </c>
       <c r="S144" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16901,24 +16936,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16929,41 +16954,16 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -19215,7 +19215,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129303094</v>
+        <v>129290684</v>
       </c>
       <c r="B165" t="n">
         <v>57740</v>
@@ -19244,19 +19244,29 @@
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>524244</v>
+        <v>524150</v>
       </c>
       <c r="R165" t="n">
-        <v>7043795</v>
+        <v>7044038</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19283,14 +19293,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19301,23 +19321,48 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129303117</v>
+        <v>129303094</v>
       </c>
       <c r="B166" t="n">
         <v>57740</v>
@@ -19352,10 +19397,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>524002</v>
+        <v>524244</v>
       </c>
       <c r="R166" t="n">
-        <v>7043990</v>
+        <v>7043795</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19392,7 +19437,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19419,7 +19464,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303101</v>
+        <v>129303117</v>
       </c>
       <c r="B167" t="n">
         <v>57740</v>
@@ -19454,10 +19499,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>524169</v>
+        <v>524002</v>
       </c>
       <c r="R167" t="n">
-        <v>7043927</v>
+        <v>7043990</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19494,7 +19539,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19521,7 +19566,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129303125</v>
+        <v>129303101</v>
       </c>
       <c r="B168" t="n">
         <v>57740</v>
@@ -19556,10 +19601,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>523973</v>
+        <v>524169</v>
       </c>
       <c r="R168" t="n">
-        <v>7044031</v>
+        <v>7043927</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19623,7 +19668,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129290684</v>
+        <v>129303125</v>
       </c>
       <c r="B169" t="n">
         <v>57740</v>
@@ -19652,29 +19697,19 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>524150</v>
+        <v>523973</v>
       </c>
       <c r="R169" t="n">
-        <v>7044038</v>
+        <v>7044031</v>
       </c>
       <c r="S169" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19701,24 +19736,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19729,41 +19754,16 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
@@ -21385,7 +21385,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129284399</v>
+        <v>129303126</v>
       </c>
       <c r="B185" t="n">
         <v>57740</v>
@@ -21414,24 +21414,19 @@
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>523878</v>
+        <v>523960</v>
       </c>
       <c r="R185" t="n">
-        <v>7044161</v>
+        <v>7044047</v>
       </c>
       <c r="S185" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21458,24 +21453,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Ringhack, färska och tydliga, på en gran.</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21486,48 +21471,23 @@
       </c>
       <c r="AG185" t="b">
         <v>0</v>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129303147</v>
+        <v>129284399</v>
       </c>
       <c r="B186" t="n">
         <v>57740</v>
@@ -21556,19 +21516,24 @@
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>523930</v>
+        <v>523878</v>
       </c>
       <c r="R186" t="n">
-        <v>7044107</v>
+        <v>7044161</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21595,14 +21560,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska och tydliga, på en gran.</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21613,23 +21588,48 @@
       </c>
       <c r="AG186" t="b">
         <v>0</v>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129303146</v>
+        <v>129303147</v>
       </c>
       <c r="B187" t="n">
         <v>57740</v>
@@ -21664,10 +21664,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>523926</v>
+        <v>523930</v>
       </c>
       <c r="R187" t="n">
-        <v>7044118</v>
+        <v>7044107</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21704,7 +21704,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21731,7 +21731,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129303126</v>
+        <v>129303146</v>
       </c>
       <c r="B188" t="n">
         <v>57740</v>
@@ -21766,10 +21766,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>523960</v>
+        <v>523926</v>
       </c>
       <c r="R188" t="n">
-        <v>7044047</v>
+        <v>7044118</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21806,7 +21806,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21935,7 +21935,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129290433</v>
+        <v>129303103</v>
       </c>
       <c r="B190" t="n">
         <v>57740</v>
@@ -21964,24 +21964,19 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>524140</v>
+        <v>524143</v>
       </c>
       <c r="R190" t="n">
-        <v>7044077</v>
+        <v>7043912</v>
       </c>
       <c r="S190" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -22008,24 +22003,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, tydliga på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22036,48 +22021,23 @@
       </c>
       <c r="AG190" t="b">
         <v>0</v>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO190" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129303103</v>
+        <v>129290433</v>
       </c>
       <c r="B191" t="n">
         <v>57740</v>
@@ -22106,19 +22066,24 @@
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>524143</v>
+        <v>524140</v>
       </c>
       <c r="R191" t="n">
-        <v>7043912</v>
+        <v>7044077</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -22145,14 +22110,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, tydliga på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22163,16 +22138,41 @@
       </c>
       <c r="AG191" t="b">
         <v>0</v>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -22321,7 +22321,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129284163</v>
+        <v>129303141</v>
       </c>
       <c r="B193" t="n">
         <v>57740</v>
@@ -22350,24 +22350,19 @@
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>523881</v>
+        <v>523902</v>
       </c>
       <c r="R193" t="n">
-        <v>7044157</v>
+        <v>7044224</v>
       </c>
       <c r="S193" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -22394,24 +22389,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22422,48 +22407,23 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO193" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129303141</v>
+        <v>129303140</v>
       </c>
       <c r="B194" t="n">
         <v>57740</v>
@@ -22498,10 +22458,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>523902</v>
+        <v>523866</v>
       </c>
       <c r="R194" t="n">
-        <v>7044224</v>
+        <v>7044256</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22538,7 +22498,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22565,7 +22525,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129303140</v>
+        <v>129284163</v>
       </c>
       <c r="B195" t="n">
         <v>57740</v>
@@ -22594,19 +22554,24 @@
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>523866</v>
+        <v>523881</v>
       </c>
       <c r="R195" t="n">
-        <v>7044256</v>
+        <v>7044157</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22633,14 +22598,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22651,16 +22626,41 @@
       </c>
       <c r="AG195" t="b">
         <v>0</v>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -16278,7 +16278,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129295984</v>
+        <v>129303092</v>
       </c>
       <c r="B139" t="n">
         <v>57740</v>
@@ -16307,21 +16307,16 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>524244</v>
+        <v>524227</v>
       </c>
       <c r="R139" t="n">
-        <v>7043732</v>
+        <v>7043799</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16351,24 +16346,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16379,48 +16364,23 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129294143</v>
+        <v>129303148</v>
       </c>
       <c r="B140" t="n">
         <v>57740</v>
@@ -16449,24 +16409,19 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>523985</v>
+        <v>523952</v>
       </c>
       <c r="R140" t="n">
-        <v>7044028</v>
+        <v>7044072</v>
       </c>
       <c r="S140" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16493,24 +16448,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16521,48 +16466,23 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129303092</v>
+        <v>129303098</v>
       </c>
       <c r="B141" t="n">
         <v>57740</v>
@@ -16597,10 +16517,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>524227</v>
+        <v>524297</v>
       </c>
       <c r="R141" t="n">
-        <v>7043799</v>
+        <v>7043866</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16637,7 +16557,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16664,7 +16584,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129303148</v>
+        <v>129303093</v>
       </c>
       <c r="B142" t="n">
         <v>57740</v>
@@ -16699,10 +16619,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>523952</v>
+        <v>524246</v>
       </c>
       <c r="R142" t="n">
-        <v>7044072</v>
+        <v>7043787</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16739,7 +16659,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16766,7 +16686,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129303098</v>
+        <v>129295984</v>
       </c>
       <c r="B143" t="n">
         <v>57740</v>
@@ -16795,16 +16715,21 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>524297</v>
+        <v>524244</v>
       </c>
       <c r="R143" t="n">
-        <v>7043866</v>
+        <v>7043732</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16834,14 +16759,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på gränsen till färska.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16852,23 +16787,48 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129303093</v>
+        <v>129294143</v>
       </c>
       <c r="B144" t="n">
         <v>57740</v>
@@ -16897,19 +16857,24 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>524246</v>
+        <v>523985</v>
       </c>
       <c r="R144" t="n">
-        <v>7043787</v>
+        <v>7044028</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16936,14 +16901,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16954,16 +16929,41 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -13062,7 +13062,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129303134</v>
+        <v>129303106</v>
       </c>
       <c r="B111" t="n">
         <v>57740</v>
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>523912</v>
+        <v>524060</v>
       </c>
       <c r="R111" t="n">
-        <v>7044281</v>
+        <v>7043917</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13164,7 +13164,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129303106</v>
+        <v>129303134</v>
       </c>
       <c r="B112" t="n">
         <v>57740</v>
@@ -13199,10 +13199,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524060</v>
+        <v>523912</v>
       </c>
       <c r="R112" t="n">
-        <v>7043917</v>
+        <v>7044281</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13239,7 +13239,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14610,7 +14610,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129290167</v>
+        <v>129303136</v>
       </c>
       <c r="B125" t="n">
         <v>57740</v>
@@ -14639,21 +14639,16 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>524109</v>
+        <v>523897</v>
       </c>
       <c r="R125" t="n">
-        <v>7044093</v>
+        <v>7044281</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14683,24 +14678,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14711,48 +14696,23 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129303111</v>
+        <v>129303135</v>
       </c>
       <c r="B126" t="n">
         <v>57740</v>
@@ -14787,10 +14747,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>524047</v>
+        <v>523902</v>
       </c>
       <c r="R126" t="n">
-        <v>7043931</v>
+        <v>7044288</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14827,7 +14787,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14854,7 +14814,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129303136</v>
+        <v>129290167</v>
       </c>
       <c r="B127" t="n">
         <v>57740</v>
@@ -14883,16 +14843,21 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523897</v>
+        <v>524109</v>
       </c>
       <c r="R127" t="n">
-        <v>7044281</v>
+        <v>7044093</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14922,14 +14887,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gammal gran.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14940,23 +14915,48 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129303135</v>
+        <v>129303111</v>
       </c>
       <c r="B128" t="n">
         <v>57740</v>
@@ -14991,10 +14991,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>523902</v>
+        <v>524047</v>
       </c>
       <c r="R128" t="n">
-        <v>7044288</v>
+        <v>7043931</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15058,7 +15058,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129295685</v>
+        <v>129303133</v>
       </c>
       <c r="B129" t="n">
         <v>57740</v>
@@ -15087,21 +15087,16 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524198</v>
+        <v>523992</v>
       </c>
       <c r="R129" t="n">
-        <v>7043758</v>
+        <v>7044262</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15131,24 +15126,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15159,48 +15144,23 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129283648</v>
+        <v>129303081</v>
       </c>
       <c r="B130" t="n">
         <v>57740</v>
@@ -15229,21 +15189,16 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>523885</v>
+        <v>524190</v>
       </c>
       <c r="R130" t="n">
-        <v>7044152</v>
+        <v>7043804</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15273,24 +15228,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15301,48 +15246,23 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129285070</v>
+        <v>129303121</v>
       </c>
       <c r="B131" t="n">
         <v>57740</v>
@@ -15371,24 +15291,19 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>523844</v>
+        <v>523979</v>
       </c>
       <c r="R131" t="n">
-        <v>7044210</v>
+        <v>7044017</v>
       </c>
       <c r="S131" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15415,24 +15330,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15443,48 +15348,23 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129285747</v>
+        <v>129303087</v>
       </c>
       <c r="B132" t="n">
         <v>57740</v>
@@ -15513,24 +15393,19 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>523850</v>
+        <v>524219</v>
       </c>
       <c r="R132" t="n">
-        <v>7044210</v>
+        <v>7043705</v>
       </c>
       <c r="S132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15557,24 +15432,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15585,48 +15450,23 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129294128</v>
+        <v>129295685</v>
       </c>
       <c r="B133" t="n">
         <v>57740</v>
@@ -15657,19 +15497,19 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>523987</v>
+        <v>524198</v>
       </c>
       <c r="R133" t="n">
-        <v>7044025</v>
+        <v>7043758</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15701,7 +15541,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15711,12 +15551,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15768,7 +15608,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129303133</v>
+        <v>129283648</v>
       </c>
       <c r="B134" t="n">
         <v>57740</v>
@@ -15797,16 +15637,21 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>523992</v>
+        <v>523885</v>
       </c>
       <c r="R134" t="n">
-        <v>7044262</v>
+        <v>7044152</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15836,14 +15681,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15854,23 +15709,48 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129303081</v>
+        <v>129285070</v>
       </c>
       <c r="B135" t="n">
         <v>57740</v>
@@ -15899,19 +15779,24 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524190</v>
+        <v>523844</v>
       </c>
       <c r="R135" t="n">
-        <v>7043804</v>
+        <v>7044210</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15938,14 +15823,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15956,23 +15851,48 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129303121</v>
+        <v>129285747</v>
       </c>
       <c r="B136" t="n">
         <v>57740</v>
@@ -16001,19 +15921,24 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>523979</v>
+        <v>523850</v>
       </c>
       <c r="R136" t="n">
-        <v>7044017</v>
+        <v>7044210</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16040,14 +15965,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16058,23 +15993,48 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129303087</v>
+        <v>129294128</v>
       </c>
       <c r="B137" t="n">
         <v>57740</v>
@@ -16103,16 +16063,21 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>524219</v>
+        <v>523987</v>
       </c>
       <c r="R137" t="n">
-        <v>7043705</v>
+        <v>7044025</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16142,14 +16107,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16160,16 +16135,41 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16278,7 +16278,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129303092</v>
+        <v>129295984</v>
       </c>
       <c r="B139" t="n">
         <v>57740</v>
@@ -16307,16 +16307,21 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>524227</v>
+        <v>524244</v>
       </c>
       <c r="R139" t="n">
-        <v>7043799</v>
+        <v>7043732</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16346,14 +16351,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på gränsen till färska.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16364,23 +16379,48 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129303148</v>
+        <v>129294143</v>
       </c>
       <c r="B140" t="n">
         <v>57740</v>
@@ -16409,19 +16449,24 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>523952</v>
+        <v>523985</v>
       </c>
       <c r="R140" t="n">
-        <v>7044072</v>
+        <v>7044028</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16448,14 +16493,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16466,23 +16521,48 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129303098</v>
+        <v>129303092</v>
       </c>
       <c r="B141" t="n">
         <v>57740</v>
@@ -16517,10 +16597,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>524297</v>
+        <v>524227</v>
       </c>
       <c r="R141" t="n">
-        <v>7043866</v>
+        <v>7043799</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16557,7 +16637,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16584,7 +16664,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129303093</v>
+        <v>129303148</v>
       </c>
       <c r="B142" t="n">
         <v>57740</v>
@@ -16619,10 +16699,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>524246</v>
+        <v>523952</v>
       </c>
       <c r="R142" t="n">
-        <v>7043787</v>
+        <v>7044072</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16659,7 +16739,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16686,7 +16766,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129295984</v>
+        <v>129303098</v>
       </c>
       <c r="B143" t="n">
         <v>57740</v>
@@ -16715,21 +16795,16 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>524244</v>
+        <v>524297</v>
       </c>
       <c r="R143" t="n">
-        <v>7043732</v>
+        <v>7043866</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16759,24 +16834,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16787,48 +16852,23 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129294143</v>
+        <v>129303093</v>
       </c>
       <c r="B144" t="n">
         <v>57740</v>
@@ -16857,24 +16897,19 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>523985</v>
+        <v>524246</v>
       </c>
       <c r="R144" t="n">
-        <v>7044028</v>
+        <v>7043787</v>
       </c>
       <c r="S144" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16901,24 +16936,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16929,41 +16954,16 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -17418,7 +17418,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129290810</v>
+        <v>129303090</v>
       </c>
       <c r="B149" t="n">
         <v>57740</v>
@@ -17447,29 +17447,19 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>524168</v>
+        <v>524194</v>
       </c>
       <c r="R149" t="n">
-        <v>7044054</v>
+        <v>7043755</v>
       </c>
       <c r="S149" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17496,24 +17486,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17524,48 +17504,23 @@
       </c>
       <c r="AG149" t="b">
         <v>0</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129294258</v>
+        <v>129303123</v>
       </c>
       <c r="B150" t="n">
         <v>57740</v>
@@ -17594,24 +17549,19 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>524049</v>
+        <v>523980</v>
       </c>
       <c r="R150" t="n">
-        <v>7043961</v>
+        <v>7044026</v>
       </c>
       <c r="S150" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17638,24 +17588,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17666,48 +17606,23 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129303090</v>
+        <v>129303091</v>
       </c>
       <c r="B151" t="n">
         <v>57740</v>
@@ -17742,10 +17657,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>524194</v>
+        <v>524225</v>
       </c>
       <c r="R151" t="n">
-        <v>7043755</v>
+        <v>7043779</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17782,7 +17697,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17809,7 +17724,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129303123</v>
+        <v>129303139</v>
       </c>
       <c r="B152" t="n">
         <v>57740</v>
@@ -17844,10 +17759,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>523980</v>
+        <v>523860</v>
       </c>
       <c r="R152" t="n">
-        <v>7044026</v>
+        <v>7044250</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17884,7 +17799,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17911,7 +17826,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129303091</v>
+        <v>129303096</v>
       </c>
       <c r="B153" t="n">
         <v>57740</v>
@@ -17946,10 +17861,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>524225</v>
+        <v>524226</v>
       </c>
       <c r="R153" t="n">
-        <v>7043779</v>
+        <v>7043829</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18013,7 +17928,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129303139</v>
+        <v>129303144</v>
       </c>
       <c r="B154" t="n">
         <v>57740</v>
@@ -18048,10 +17963,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>523860</v>
+        <v>523900</v>
       </c>
       <c r="R154" t="n">
-        <v>7044250</v>
+        <v>7044174</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18088,7 +18003,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18115,7 +18030,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129303096</v>
+        <v>129290810</v>
       </c>
       <c r="B155" t="n">
         <v>57740</v>
@@ -18144,19 +18059,29 @@
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>524226</v>
+        <v>524168</v>
       </c>
       <c r="R155" t="n">
-        <v>7043829</v>
+        <v>7044054</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18183,14 +18108,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18201,23 +18136,48 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129303144</v>
+        <v>129294258</v>
       </c>
       <c r="B156" t="n">
         <v>57740</v>
@@ -18246,19 +18206,24 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>523900</v>
+        <v>524049</v>
       </c>
       <c r="R156" t="n">
-        <v>7044174</v>
+        <v>7043961</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18285,14 +18250,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18303,16 +18278,41 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -18767,7 +18767,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129291995</v>
+        <v>129303119</v>
       </c>
       <c r="B161" t="n">
         <v>57740</v>
@@ -18796,21 +18796,16 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>524225</v>
+        <v>524000</v>
       </c>
       <c r="R161" t="n">
-        <v>7043980</v>
+        <v>7044000</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18840,24 +18835,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18868,48 +18853,23 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129303119</v>
+        <v>129303095</v>
       </c>
       <c r="B162" t="n">
         <v>57740</v>
@@ -18944,10 +18904,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>524000</v>
+        <v>524229</v>
       </c>
       <c r="R162" t="n">
-        <v>7044000</v>
+        <v>7043821</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19011,7 +18971,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129303095</v>
+        <v>129303082</v>
       </c>
       <c r="B163" t="n">
         <v>57740</v>
@@ -19046,10 +19006,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>524229</v>
+        <v>524269</v>
       </c>
       <c r="R163" t="n">
-        <v>7043821</v>
+        <v>7043735</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19086,7 +19046,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19113,7 +19073,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129303082</v>
+        <v>129291995</v>
       </c>
       <c r="B164" t="n">
         <v>57740</v>
@@ -19142,16 +19102,21 @@
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>524269</v>
+        <v>524225</v>
       </c>
       <c r="R164" t="n">
-        <v>7043735</v>
+        <v>7043980</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19181,14 +19146,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19199,23 +19174,48 @@
       </c>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129290684</v>
+        <v>129303094</v>
       </c>
       <c r="B165" t="n">
         <v>57740</v>
@@ -19244,29 +19244,19 @@
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>524150</v>
+        <v>524244</v>
       </c>
       <c r="R165" t="n">
-        <v>7044038</v>
+        <v>7043795</v>
       </c>
       <c r="S165" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19293,24 +19283,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19321,48 +19301,23 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129303094</v>
+        <v>129303117</v>
       </c>
       <c r="B166" t="n">
         <v>57740</v>
@@ -19397,10 +19352,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>524244</v>
+        <v>524002</v>
       </c>
       <c r="R166" t="n">
-        <v>7043795</v>
+        <v>7043990</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19437,7 +19392,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19464,7 +19419,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303117</v>
+        <v>129303101</v>
       </c>
       <c r="B167" t="n">
         <v>57740</v>
@@ -19499,10 +19454,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>524002</v>
+        <v>524169</v>
       </c>
       <c r="R167" t="n">
-        <v>7043990</v>
+        <v>7043927</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19539,7 +19494,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19566,7 +19521,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129303101</v>
+        <v>129303125</v>
       </c>
       <c r="B168" t="n">
         <v>57740</v>
@@ -19601,10 +19556,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>524169</v>
+        <v>523973</v>
       </c>
       <c r="R168" t="n">
-        <v>7043927</v>
+        <v>7044031</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19668,7 +19623,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129303125</v>
+        <v>129290684</v>
       </c>
       <c r="B169" t="n">
         <v>57740</v>
@@ -19697,19 +19652,29 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>523973</v>
+        <v>524150</v>
       </c>
       <c r="R169" t="n">
-        <v>7044031</v>
+        <v>7044038</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19736,14 +19701,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19754,16 +19729,41 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
@@ -20529,7 +20529,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129294096</v>
+        <v>129303100</v>
       </c>
       <c r="B177" t="n">
         <v>57740</v>
@@ -20558,24 +20558,19 @@
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>523971</v>
+        <v>524235</v>
       </c>
       <c r="R177" t="n">
-        <v>7044037</v>
+        <v>7043960</v>
       </c>
       <c r="S177" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20602,24 +20597,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20630,48 +20615,23 @@
       </c>
       <c r="AG177" t="b">
         <v>0</v>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129303100</v>
+        <v>129303143</v>
       </c>
       <c r="B178" t="n">
         <v>57740</v>
@@ -20706,10 +20666,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>524235</v>
+        <v>523911</v>
       </c>
       <c r="R178" t="n">
-        <v>7043960</v>
+        <v>7044178</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20746,7 +20706,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20773,7 +20733,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129303143</v>
+        <v>129303112</v>
       </c>
       <c r="B179" t="n">
         <v>57740</v>
@@ -20808,10 +20768,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>523911</v>
+        <v>524044</v>
       </c>
       <c r="R179" t="n">
-        <v>7044178</v>
+        <v>7043935</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20848,7 +20808,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20875,7 +20835,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129303112</v>
+        <v>129303116</v>
       </c>
       <c r="B180" t="n">
         <v>57740</v>
@@ -20910,10 +20870,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>524044</v>
+        <v>524033</v>
       </c>
       <c r="R180" t="n">
-        <v>7043935</v>
+        <v>7043952</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20977,7 +20937,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129303116</v>
+        <v>129303138</v>
       </c>
       <c r="B181" t="n">
         <v>57740</v>
@@ -21012,10 +20972,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>524033</v>
+        <v>523879</v>
       </c>
       <c r="R181" t="n">
-        <v>7043952</v>
+        <v>7044256</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21052,7 +21012,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21079,7 +21039,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129303138</v>
+        <v>129303131</v>
       </c>
       <c r="B182" t="n">
         <v>57740</v>
@@ -21114,10 +21074,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>523879</v>
+        <v>524059</v>
       </c>
       <c r="R182" t="n">
-        <v>7044256</v>
+        <v>7044016</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21181,7 +21141,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129303131</v>
+        <v>129303128</v>
       </c>
       <c r="B183" t="n">
         <v>57740</v>
@@ -21216,10 +21176,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>524059</v>
+        <v>524186</v>
       </c>
       <c r="R183" t="n">
-        <v>7044016</v>
+        <v>7043943</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21256,7 +21216,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21283,7 +21243,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129303128</v>
+        <v>129294096</v>
       </c>
       <c r="B184" t="n">
         <v>57740</v>
@@ -21312,19 +21272,24 @@
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>524186</v>
+        <v>523971</v>
       </c>
       <c r="R184" t="n">
-        <v>7043943</v>
+        <v>7044037</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21351,14 +21316,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21369,23 +21344,48 @@
       </c>
       <c r="AG184" t="b">
         <v>0</v>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129303126</v>
+        <v>129284399</v>
       </c>
       <c r="B185" t="n">
         <v>57740</v>
@@ -21414,19 +21414,24 @@
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>523960</v>
+        <v>523878</v>
       </c>
       <c r="R185" t="n">
-        <v>7044047</v>
+        <v>7044161</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21453,14 +21458,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack, färska och tydliga, på en gran.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21471,23 +21486,48 @@
       </c>
       <c r="AG185" t="b">
         <v>0</v>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129284399</v>
+        <v>129303147</v>
       </c>
       <c r="B186" t="n">
         <v>57740</v>
@@ -21516,24 +21556,19 @@
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>523878</v>
+        <v>523930</v>
       </c>
       <c r="R186" t="n">
-        <v>7044161</v>
+        <v>7044107</v>
       </c>
       <c r="S186" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21560,24 +21595,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Ringhack, färska och tydliga, på en gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21588,48 +21613,23 @@
       </c>
       <c r="AG186" t="b">
         <v>0</v>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO186" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129303147</v>
+        <v>129303146</v>
       </c>
       <c r="B187" t="n">
         <v>57740</v>
@@ -21664,10 +21664,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>523930</v>
+        <v>523926</v>
       </c>
       <c r="R187" t="n">
-        <v>7044107</v>
+        <v>7044118</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21704,7 +21704,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21731,7 +21731,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129303146</v>
+        <v>129303126</v>
       </c>
       <c r="B188" t="n">
         <v>57740</v>
@@ -21766,10 +21766,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>523926</v>
+        <v>523960</v>
       </c>
       <c r="R188" t="n">
-        <v>7044118</v>
+        <v>7044047</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21806,7 +21806,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21935,7 +21935,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129303103</v>
+        <v>129290433</v>
       </c>
       <c r="B190" t="n">
         <v>57740</v>
@@ -21964,19 +21964,24 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>524143</v>
+        <v>524140</v>
       </c>
       <c r="R190" t="n">
-        <v>7043912</v>
+        <v>7044077</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -22003,14 +22008,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, tydliga på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22021,23 +22036,48 @@
       </c>
       <c r="AG190" t="b">
         <v>0</v>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129290433</v>
+        <v>129303103</v>
       </c>
       <c r="B191" t="n">
         <v>57740</v>
@@ -22066,24 +22106,19 @@
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>524140</v>
+        <v>524143</v>
       </c>
       <c r="R191" t="n">
-        <v>7044077</v>
+        <v>7043912</v>
       </c>
       <c r="S191" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -22110,24 +22145,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, tydliga på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22138,48 +22163,23 @@
       </c>
       <c r="AG191" t="b">
         <v>0</v>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO191" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129296040</v>
+        <v>129284163</v>
       </c>
       <c r="B192" t="n">
         <v>57740</v>
@@ -22215,17 +22215,17 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>524232</v>
+        <v>523881</v>
       </c>
       <c r="R192" t="n">
-        <v>7043714</v>
+        <v>7044157</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -22264,12 +22264,12 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22321,7 +22321,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129303141</v>
+        <v>129296040</v>
       </c>
       <c r="B193" t="n">
         <v>57740</v>
@@ -22350,16 +22350,21 @@
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>523902</v>
+        <v>524232</v>
       </c>
       <c r="R193" t="n">
-        <v>7044224</v>
+        <v>7043714</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22389,14 +22394,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22407,23 +22422,48 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129303140</v>
+        <v>129303141</v>
       </c>
       <c r="B194" t="n">
         <v>57740</v>
@@ -22458,10 +22498,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>523866</v>
+        <v>523902</v>
       </c>
       <c r="R194" t="n">
-        <v>7044256</v>
+        <v>7044224</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22498,7 +22538,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22525,7 +22565,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129284163</v>
+        <v>129303140</v>
       </c>
       <c r="B195" t="n">
         <v>57740</v>
@@ -22554,24 +22594,19 @@
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>523881</v>
+        <v>523866</v>
       </c>
       <c r="R195" t="n">
-        <v>7044157</v>
+        <v>7044256</v>
       </c>
       <c r="S195" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22598,24 +22633,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22626,41 +22651,16 @@
       </c>
       <c r="AG195" t="b">
         <v>0</v>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO195" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -16970,7 +16970,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129294174</v>
+        <v>129303127</v>
       </c>
       <c r="B145" t="n">
         <v>57740</v>
@@ -16999,24 +16999,19 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>523983</v>
+        <v>523955</v>
       </c>
       <c r="R145" t="n">
-        <v>7044020</v>
+        <v>7044054</v>
       </c>
       <c r="S145" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17043,24 +17038,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17071,48 +17056,23 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129303127</v>
+        <v>129303088</v>
       </c>
       <c r="B146" t="n">
         <v>57740</v>
@@ -17147,10 +17107,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>523955</v>
+        <v>524211</v>
       </c>
       <c r="R146" t="n">
-        <v>7044054</v>
+        <v>7043713</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17187,7 +17147,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17214,7 +17174,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129303088</v>
+        <v>129303115</v>
       </c>
       <c r="B147" t="n">
         <v>57740</v>
@@ -17249,10 +17209,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>524211</v>
+        <v>524039</v>
       </c>
       <c r="R147" t="n">
-        <v>7043713</v>
+        <v>7043944</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17289,7 +17249,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17316,7 +17276,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129303115</v>
+        <v>129294174</v>
       </c>
       <c r="B148" t="n">
         <v>57740</v>
@@ -17345,19 +17305,24 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>524039</v>
+        <v>523983</v>
       </c>
       <c r="R148" t="n">
-        <v>7043944</v>
+        <v>7044020</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17384,14 +17349,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17402,16 +17377,41 @@
       </c>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -19215,7 +19215,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129303094</v>
+        <v>129290684</v>
       </c>
       <c r="B165" t="n">
         <v>57740</v>
@@ -19244,19 +19244,29 @@
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>524244</v>
+        <v>524150</v>
       </c>
       <c r="R165" t="n">
-        <v>7043795</v>
+        <v>7044038</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19283,14 +19293,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19301,23 +19321,48 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129303117</v>
+        <v>129295476</v>
       </c>
       <c r="B166" t="n">
         <v>57740</v>
@@ -19346,19 +19391,29 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>524002</v>
+        <v>524222</v>
       </c>
       <c r="R166" t="n">
-        <v>7043990</v>
+        <v>7043799</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19385,14 +19440,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19403,23 +19468,48 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303101</v>
+        <v>129303094</v>
       </c>
       <c r="B167" t="n">
         <v>57740</v>
@@ -19454,10 +19544,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>524169</v>
+        <v>524244</v>
       </c>
       <c r="R167" t="n">
-        <v>7043927</v>
+        <v>7043795</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19494,7 +19584,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19521,7 +19611,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129303125</v>
+        <v>129303117</v>
       </c>
       <c r="B168" t="n">
         <v>57740</v>
@@ -19556,10 +19646,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>523973</v>
+        <v>524002</v>
       </c>
       <c r="R168" t="n">
-        <v>7044031</v>
+        <v>7043990</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19596,7 +19686,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19623,7 +19713,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129290684</v>
+        <v>129303101</v>
       </c>
       <c r="B169" t="n">
         <v>57740</v>
@@ -19652,29 +19742,19 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>524150</v>
+        <v>524169</v>
       </c>
       <c r="R169" t="n">
-        <v>7044038</v>
+        <v>7043927</v>
       </c>
       <c r="S169" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19701,24 +19781,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19729,48 +19799,23 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129295476</v>
+        <v>129303125</v>
       </c>
       <c r="B170" t="n">
         <v>57740</v>
@@ -19799,29 +19844,19 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>524222</v>
+        <v>523973</v>
       </c>
       <c r="R170" t="n">
-        <v>7043799</v>
+        <v>7044031</v>
       </c>
       <c r="S170" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19848,24 +19883,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19876,41 +19901,16 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -15058,7 +15058,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129303133</v>
+        <v>129295685</v>
       </c>
       <c r="B129" t="n">
         <v>57740</v>
@@ -15087,16 +15087,21 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>523992</v>
+        <v>524198</v>
       </c>
       <c r="R129" t="n">
-        <v>7044262</v>
+        <v>7043758</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15126,14 +15131,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15144,23 +15159,48 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129303081</v>
+        <v>129283648</v>
       </c>
       <c r="B130" t="n">
         <v>57740</v>
@@ -15189,16 +15229,21 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524190</v>
+        <v>523885</v>
       </c>
       <c r="R130" t="n">
-        <v>7043804</v>
+        <v>7044152</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15228,14 +15273,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15246,23 +15301,48 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129303121</v>
+        <v>129285070</v>
       </c>
       <c r="B131" t="n">
         <v>57740</v>
@@ -15291,19 +15371,24 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>523979</v>
+        <v>523844</v>
       </c>
       <c r="R131" t="n">
-        <v>7044017</v>
+        <v>7044210</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15330,14 +15415,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15348,23 +15443,48 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129303087</v>
+        <v>129285747</v>
       </c>
       <c r="B132" t="n">
         <v>57740</v>
@@ -15393,19 +15513,24 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524219</v>
+        <v>523850</v>
       </c>
       <c r="R132" t="n">
-        <v>7043705</v>
+        <v>7044210</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15432,14 +15557,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15450,23 +15585,48 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129295685</v>
+        <v>129294128</v>
       </c>
       <c r="B133" t="n">
         <v>57740</v>
@@ -15497,19 +15657,19 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524198</v>
+        <v>523987</v>
       </c>
       <c r="R133" t="n">
-        <v>7043758</v>
+        <v>7044025</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15541,7 +15701,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15551,12 +15711,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15608,7 +15768,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129283648</v>
+        <v>129303133</v>
       </c>
       <c r="B134" t="n">
         <v>57740</v>
@@ -15637,21 +15797,16 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>523885</v>
+        <v>523992</v>
       </c>
       <c r="R134" t="n">
-        <v>7044152</v>
+        <v>7044262</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15681,24 +15836,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15709,48 +15854,23 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129285070</v>
+        <v>129303081</v>
       </c>
       <c r="B135" t="n">
         <v>57740</v>
@@ -15779,24 +15899,19 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>523844</v>
+        <v>524190</v>
       </c>
       <c r="R135" t="n">
-        <v>7044210</v>
+        <v>7043804</v>
       </c>
       <c r="S135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15823,24 +15938,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15851,48 +15956,23 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129285747</v>
+        <v>129303121</v>
       </c>
       <c r="B136" t="n">
         <v>57740</v>
@@ -15921,24 +16001,19 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>523850</v>
+        <v>523979</v>
       </c>
       <c r="R136" t="n">
-        <v>7044210</v>
+        <v>7044017</v>
       </c>
       <c r="S136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15965,24 +16040,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15993,48 +16058,23 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129294128</v>
+        <v>129303087</v>
       </c>
       <c r="B137" t="n">
         <v>57740</v>
@@ -16063,21 +16103,16 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>523987</v>
+        <v>524219</v>
       </c>
       <c r="R137" t="n">
-        <v>7044025</v>
+        <v>7043705</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16107,24 +16142,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Savhack(ringhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16135,41 +16160,16 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16970,7 +16970,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129303127</v>
+        <v>129294174</v>
       </c>
       <c r="B145" t="n">
         <v>57740</v>
@@ -16999,19 +16999,24 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>523955</v>
+        <v>523983</v>
       </c>
       <c r="R145" t="n">
-        <v>7044054</v>
+        <v>7044020</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17038,14 +17043,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17056,23 +17071,48 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129303088</v>
+        <v>129303127</v>
       </c>
       <c r="B146" t="n">
         <v>57740</v>
@@ -17107,10 +17147,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>524211</v>
+        <v>523955</v>
       </c>
       <c r="R146" t="n">
-        <v>7043713</v>
+        <v>7044054</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17147,7 +17187,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17174,7 +17214,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129303115</v>
+        <v>129303088</v>
       </c>
       <c r="B147" t="n">
         <v>57740</v>
@@ -17209,10 +17249,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>524039</v>
+        <v>524211</v>
       </c>
       <c r="R147" t="n">
-        <v>7043944</v>
+        <v>7043713</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17249,7 +17289,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17276,7 +17316,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129294174</v>
+        <v>129303115</v>
       </c>
       <c r="B148" t="n">
         <v>57740</v>
@@ -17305,24 +17345,19 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>523983</v>
+        <v>524039</v>
       </c>
       <c r="R148" t="n">
-        <v>7044020</v>
+        <v>7043944</v>
       </c>
       <c r="S148" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17349,24 +17384,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17377,41 +17402,16 @@
       </c>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -19215,7 +19215,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129290684</v>
+        <v>129303094</v>
       </c>
       <c r="B165" t="n">
         <v>57740</v>
@@ -19244,29 +19244,19 @@
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>524150</v>
+        <v>524244</v>
       </c>
       <c r="R165" t="n">
-        <v>7044038</v>
+        <v>7043795</v>
       </c>
       <c r="S165" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19293,24 +19283,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19321,48 +19301,23 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129295476</v>
+        <v>129303117</v>
       </c>
       <c r="B166" t="n">
         <v>57740</v>
@@ -19391,29 +19346,19 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>524222</v>
+        <v>524002</v>
       </c>
       <c r="R166" t="n">
-        <v>7043799</v>
+        <v>7043990</v>
       </c>
       <c r="S166" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19440,24 +19385,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19468,48 +19403,23 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303094</v>
+        <v>129303101</v>
       </c>
       <c r="B167" t="n">
         <v>57740</v>
@@ -19544,10 +19454,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>524244</v>
+        <v>524169</v>
       </c>
       <c r="R167" t="n">
-        <v>7043795</v>
+        <v>7043927</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19584,7 +19494,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19611,7 +19521,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129303117</v>
+        <v>129303125</v>
       </c>
       <c r="B168" t="n">
         <v>57740</v>
@@ -19646,10 +19556,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>524002</v>
+        <v>523973</v>
       </c>
       <c r="R168" t="n">
-        <v>7043990</v>
+        <v>7044031</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19686,7 +19596,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19713,7 +19623,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129303101</v>
+        <v>129290684</v>
       </c>
       <c r="B169" t="n">
         <v>57740</v>
@@ -19742,19 +19652,29 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>524169</v>
+        <v>524150</v>
       </c>
       <c r="R169" t="n">
-        <v>7043927</v>
+        <v>7044038</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19781,14 +19701,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19799,23 +19729,48 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129303125</v>
+        <v>129295476</v>
       </c>
       <c r="B170" t="n">
         <v>57740</v>
@@ -19844,19 +19799,29 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>523973</v>
+        <v>524222</v>
       </c>
       <c r="R170" t="n">
-        <v>7044031</v>
+        <v>7043799</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19883,14 +19848,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19901,16 +19876,41 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -21385,7 +21385,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129284399</v>
+        <v>129303147</v>
       </c>
       <c r="B185" t="n">
         <v>57740</v>
@@ -21414,24 +21414,19 @@
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>523878</v>
+        <v>523930</v>
       </c>
       <c r="R185" t="n">
-        <v>7044161</v>
+        <v>7044107</v>
       </c>
       <c r="S185" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21458,24 +21453,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Ringhack, färska och tydliga, på en gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21486,48 +21471,23 @@
       </c>
       <c r="AG185" t="b">
         <v>0</v>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129303147</v>
+        <v>129303146</v>
       </c>
       <c r="B186" t="n">
         <v>57740</v>
@@ -21562,10 +21522,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>523930</v>
+        <v>523926</v>
       </c>
       <c r="R186" t="n">
-        <v>7044107</v>
+        <v>7044118</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21602,7 +21562,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21629,7 +21589,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129303146</v>
+        <v>129303126</v>
       </c>
       <c r="B187" t="n">
         <v>57740</v>
@@ -21664,10 +21624,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>523926</v>
+        <v>523960</v>
       </c>
       <c r="R187" t="n">
-        <v>7044118</v>
+        <v>7044047</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21704,7 +21664,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21731,7 +21691,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129303126</v>
+        <v>129303114</v>
       </c>
       <c r="B188" t="n">
         <v>57740</v>
@@ -21766,10 +21726,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>523960</v>
+        <v>524041</v>
       </c>
       <c r="R188" t="n">
-        <v>7044047</v>
+        <v>7043942</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21806,7 +21766,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21833,7 +21793,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129303114</v>
+        <v>129284399</v>
       </c>
       <c r="B189" t="n">
         <v>57740</v>
@@ -21862,19 +21822,24 @@
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>524041</v>
+        <v>523878</v>
       </c>
       <c r="R189" t="n">
-        <v>7043942</v>
+        <v>7044161</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21901,14 +21866,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och tydliga, på en gran.</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21919,16 +21894,41 @@
       </c>
       <c r="AG189" t="b">
         <v>0</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -13368,7 +13368,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129284656</v>
+        <v>129303097</v>
       </c>
       <c r="B114" t="n">
         <v>57740</v>
@@ -13397,24 +13397,19 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>523856</v>
+        <v>524306</v>
       </c>
       <c r="R114" t="n">
-        <v>7044190</v>
+        <v>7043867</v>
       </c>
       <c r="S114" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13441,24 +13436,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>09:27</t>
-        </is>
-      </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, högt upp på en tall.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13469,48 +13454,23 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129303107</v>
+        <v>129284656</v>
       </c>
       <c r="B115" t="n">
         <v>57740</v>
@@ -13539,19 +13499,24 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524056</v>
+        <v>523856</v>
       </c>
       <c r="R115" t="n">
-        <v>7043920</v>
+        <v>7044190</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13578,14 +13543,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre, högt upp på en tall.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13596,23 +13571,48 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129303108</v>
+        <v>129303107</v>
       </c>
       <c r="B116" t="n">
         <v>57740</v>
@@ -13647,10 +13647,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524052</v>
+        <v>524056</v>
       </c>
       <c r="R116" t="n">
-        <v>7043922</v>
+        <v>7043920</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13687,7 +13687,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13714,7 +13714,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129303097</v>
+        <v>129303108</v>
       </c>
       <c r="B117" t="n">
         <v>57740</v>
@@ -13749,10 +13749,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524306</v>
+        <v>524052</v>
       </c>
       <c r="R117" t="n">
-        <v>7043867</v>
+        <v>7043922</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13789,7 +13789,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14610,7 +14610,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129303136</v>
+        <v>129290167</v>
       </c>
       <c r="B125" t="n">
         <v>57740</v>
@@ -14639,16 +14639,21 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523897</v>
+        <v>524109</v>
       </c>
       <c r="R125" t="n">
-        <v>7044281</v>
+        <v>7044093</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14678,14 +14683,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gammal gran.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14696,23 +14711,48 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129303135</v>
+        <v>129303136</v>
       </c>
       <c r="B126" t="n">
         <v>57740</v>
@@ -14747,10 +14787,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523902</v>
+        <v>523897</v>
       </c>
       <c r="R126" t="n">
-        <v>7044288</v>
+        <v>7044281</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14787,7 +14827,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14814,7 +14854,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129290167</v>
+        <v>129303135</v>
       </c>
       <c r="B127" t="n">
         <v>57740</v>
@@ -14843,21 +14883,16 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>524109</v>
+        <v>523902</v>
       </c>
       <c r="R127" t="n">
-        <v>7044093</v>
+        <v>7044288</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14887,24 +14922,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14915,41 +14940,16 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -15768,7 +15768,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129303133</v>
+        <v>129303087</v>
       </c>
       <c r="B134" t="n">
         <v>57740</v>
@@ -15803,10 +15803,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>523992</v>
+        <v>524219</v>
       </c>
       <c r="R134" t="n">
-        <v>7044262</v>
+        <v>7043705</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15843,7 +15843,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15870,7 +15870,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129303081</v>
+        <v>129303133</v>
       </c>
       <c r="B135" t="n">
         <v>57740</v>
@@ -15905,10 +15905,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524190</v>
+        <v>523992</v>
       </c>
       <c r="R135" t="n">
-        <v>7043804</v>
+        <v>7044262</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15972,7 +15972,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129303121</v>
+        <v>129303081</v>
       </c>
       <c r="B136" t="n">
         <v>57740</v>
@@ -16007,10 +16007,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>523979</v>
+        <v>524190</v>
       </c>
       <c r="R136" t="n">
-        <v>7044017</v>
+        <v>7043804</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16047,7 +16047,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16074,7 +16074,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129303087</v>
+        <v>129303121</v>
       </c>
       <c r="B137" t="n">
         <v>57740</v>
@@ -16109,10 +16109,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>524219</v>
+        <v>523979</v>
       </c>
       <c r="R137" t="n">
-        <v>7043705</v>
+        <v>7044017</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16562,7 +16562,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129303092</v>
+        <v>129303098</v>
       </c>
       <c r="B141" t="n">
         <v>57740</v>
@@ -16597,10 +16597,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>524227</v>
+        <v>524297</v>
       </c>
       <c r="R141" t="n">
-        <v>7043799</v>
+        <v>7043866</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16637,7 +16637,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16664,7 +16664,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129303148</v>
+        <v>129303093</v>
       </c>
       <c r="B142" t="n">
         <v>57740</v>
@@ -16699,10 +16699,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>523952</v>
+        <v>524246</v>
       </c>
       <c r="R142" t="n">
-        <v>7044072</v>
+        <v>7043787</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16739,7 +16739,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16766,7 +16766,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129303098</v>
+        <v>129303092</v>
       </c>
       <c r="B143" t="n">
         <v>57740</v>
@@ -16801,10 +16801,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>524297</v>
+        <v>524227</v>
       </c>
       <c r="R143" t="n">
-        <v>7043866</v>
+        <v>7043799</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16868,7 +16868,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129303093</v>
+        <v>129303148</v>
       </c>
       <c r="B144" t="n">
         <v>57740</v>
@@ -16903,10 +16903,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>524246</v>
+        <v>523952</v>
       </c>
       <c r="R144" t="n">
-        <v>7043787</v>
+        <v>7044072</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17418,7 +17418,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129303090</v>
+        <v>129290810</v>
       </c>
       <c r="B149" t="n">
         <v>57740</v>
@@ -17447,19 +17447,29 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>524194</v>
+        <v>524168</v>
       </c>
       <c r="R149" t="n">
-        <v>7043755</v>
+        <v>7044054</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17486,14 +17496,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17504,23 +17524,48 @@
       </c>
       <c r="AG149" t="b">
         <v>0</v>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129303123</v>
+        <v>129294258</v>
       </c>
       <c r="B150" t="n">
         <v>57740</v>
@@ -17549,19 +17594,24 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>523980</v>
+        <v>524049</v>
       </c>
       <c r="R150" t="n">
-        <v>7044026</v>
+        <v>7043961</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17588,14 +17638,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17606,23 +17666,48 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129303091</v>
+        <v>129303144</v>
       </c>
       <c r="B151" t="n">
         <v>57740</v>
@@ -17657,10 +17742,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>524225</v>
+        <v>523900</v>
       </c>
       <c r="R151" t="n">
-        <v>7043779</v>
+        <v>7044174</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17697,7 +17782,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17724,7 +17809,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129303139</v>
+        <v>129303090</v>
       </c>
       <c r="B152" t="n">
         <v>57740</v>
@@ -17759,10 +17844,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>523860</v>
+        <v>524194</v>
       </c>
       <c r="R152" t="n">
-        <v>7044250</v>
+        <v>7043755</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17799,7 +17884,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17826,7 +17911,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129303096</v>
+        <v>129303139</v>
       </c>
       <c r="B153" t="n">
         <v>57740</v>
@@ -17861,10 +17946,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>524226</v>
+        <v>523860</v>
       </c>
       <c r="R153" t="n">
-        <v>7043829</v>
+        <v>7044250</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17901,7 +17986,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17928,7 +18013,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129303144</v>
+        <v>129303123</v>
       </c>
       <c r="B154" t="n">
         <v>57740</v>
@@ -17963,10 +18048,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>523900</v>
+        <v>523980</v>
       </c>
       <c r="R154" t="n">
-        <v>7044174</v>
+        <v>7044026</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18003,7 +18088,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18030,7 +18115,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129290810</v>
+        <v>129303091</v>
       </c>
       <c r="B155" t="n">
         <v>57740</v>
@@ -18059,29 +18144,19 @@
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>524168</v>
+        <v>524225</v>
       </c>
       <c r="R155" t="n">
-        <v>7044054</v>
+        <v>7043779</v>
       </c>
       <c r="S155" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18108,24 +18183,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18136,48 +18201,23 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129294258</v>
+        <v>129303096</v>
       </c>
       <c r="B156" t="n">
         <v>57740</v>
@@ -18206,24 +18246,19 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>524049</v>
+        <v>524226</v>
       </c>
       <c r="R156" t="n">
-        <v>7043961</v>
+        <v>7043829</v>
       </c>
       <c r="S156" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18250,24 +18285,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18278,48 +18303,23 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129283727</v>
+        <v>129303110</v>
       </c>
       <c r="B157" t="n">
         <v>57740</v>
@@ -18348,21 +18348,16 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>523881</v>
+        <v>524053</v>
       </c>
       <c r="R157" t="n">
-        <v>7044149</v>
+        <v>7043929</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18392,24 +18387,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka högt upp på en gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18420,41 +18405,16 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -18665,7 +18625,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129303110</v>
+        <v>129283727</v>
       </c>
       <c r="B160" t="n">
         <v>57740</v>
@@ -18694,16 +18654,21 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>524053</v>
+        <v>523881</v>
       </c>
       <c r="R160" t="n">
-        <v>7043929</v>
+        <v>7044149</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18733,14 +18698,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, färska, enstaka högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18751,23 +18726,48 @@
       </c>
       <c r="AG160" t="b">
         <v>0</v>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129303119</v>
+        <v>129291995</v>
       </c>
       <c r="B161" t="n">
         <v>57740</v>
@@ -18796,16 +18796,21 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>524000</v>
+        <v>524225</v>
       </c>
       <c r="R161" t="n">
-        <v>7044000</v>
+        <v>7043980</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18835,14 +18840,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18853,23 +18868,48 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129303095</v>
+        <v>129303119</v>
       </c>
       <c r="B162" t="n">
         <v>57740</v>
@@ -18904,10 +18944,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>524229</v>
+        <v>524000</v>
       </c>
       <c r="R162" t="n">
-        <v>7043821</v>
+        <v>7044000</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18971,7 +19011,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129303082</v>
+        <v>129303095</v>
       </c>
       <c r="B163" t="n">
         <v>57740</v>
@@ -19006,10 +19046,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>524269</v>
+        <v>524229</v>
       </c>
       <c r="R163" t="n">
-        <v>7043735</v>
+        <v>7043821</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19046,7 +19086,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19073,7 +19113,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129291995</v>
+        <v>129303082</v>
       </c>
       <c r="B164" t="n">
         <v>57740</v>
@@ -19102,21 +19142,16 @@
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>524225</v>
+        <v>524269</v>
       </c>
       <c r="R164" t="n">
-        <v>7043980</v>
+        <v>7043735</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19146,24 +19181,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19174,48 +19199,23 @@
       </c>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129303094</v>
+        <v>129290684</v>
       </c>
       <c r="B165" t="n">
         <v>57740</v>
@@ -19244,19 +19244,29 @@
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>524244</v>
+        <v>524150</v>
       </c>
       <c r="R165" t="n">
-        <v>7043795</v>
+        <v>7044038</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19283,14 +19293,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19301,23 +19321,48 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129303117</v>
+        <v>129295476</v>
       </c>
       <c r="B166" t="n">
         <v>57740</v>
@@ -19346,19 +19391,29 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Bammen, Bammen, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>524002</v>
+        <v>524222</v>
       </c>
       <c r="R166" t="n">
-        <v>7043990</v>
+        <v>7043799</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19385,14 +19440,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19403,23 +19468,48 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129303101</v>
+        <v>129303117</v>
       </c>
       <c r="B167" t="n">
         <v>57740</v>
@@ -19454,10 +19544,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>524169</v>
+        <v>524002</v>
       </c>
       <c r="R167" t="n">
-        <v>7043927</v>
+        <v>7043990</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19494,7 +19584,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19623,7 +19713,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129290684</v>
+        <v>129303094</v>
       </c>
       <c r="B169" t="n">
         <v>57740</v>
@@ -19652,29 +19742,19 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>524150</v>
+        <v>524244</v>
       </c>
       <c r="R169" t="n">
-        <v>7044038</v>
+        <v>7043795</v>
       </c>
       <c r="S169" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19701,24 +19781,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, påtagligt och tydligt på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19729,48 +19799,23 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129295476</v>
+        <v>129303101</v>
       </c>
       <c r="B170" t="n">
         <v>57740</v>
@@ -19799,29 +19844,19 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Bammen, Bammen, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>524222</v>
+        <v>524169</v>
       </c>
       <c r="R170" t="n">
-        <v>7043799</v>
+        <v>7043927</v>
       </c>
       <c r="S170" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19848,24 +19883,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19876,48 +19901,23 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129303130</v>
+        <v>129303113</v>
       </c>
       <c r="B171" t="n">
         <v>57740</v>
@@ -19952,10 +19952,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>524087</v>
+        <v>524042</v>
       </c>
       <c r="R171" t="n">
-        <v>7044036</v>
+        <v>7043944</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20019,7 +20019,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129303104</v>
+        <v>129303109</v>
       </c>
       <c r="B172" t="n">
         <v>57740</v>
@@ -20054,10 +20054,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>524081</v>
+        <v>524053</v>
       </c>
       <c r="R172" t="n">
-        <v>7043892</v>
+        <v>7043923</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20121,7 +20121,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129303113</v>
+        <v>129303130</v>
       </c>
       <c r="B173" t="n">
         <v>57740</v>
@@ -20156,10 +20156,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>524042</v>
+        <v>524087</v>
       </c>
       <c r="R173" t="n">
-        <v>7043944</v>
+        <v>7044036</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20196,7 +20196,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20223,7 +20223,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129303142</v>
+        <v>129303104</v>
       </c>
       <c r="B174" t="n">
         <v>57740</v>
@@ -20258,10 +20258,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>523900</v>
+        <v>524081</v>
       </c>
       <c r="R174" t="n">
-        <v>7044204</v>
+        <v>7043892</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20325,7 +20325,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129303109</v>
+        <v>129303142</v>
       </c>
       <c r="B175" t="n">
         <v>57740</v>
@@ -20360,10 +20360,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>524053</v>
+        <v>523900</v>
       </c>
       <c r="R175" t="n">
-        <v>7043923</v>
+        <v>7044204</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20733,7 +20733,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129303112</v>
+        <v>129294096</v>
       </c>
       <c r="B179" t="n">
         <v>57740</v>
@@ -20762,19 +20762,24 @@
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>524044</v>
+        <v>523971</v>
       </c>
       <c r="R179" t="n">
-        <v>7043935</v>
+        <v>7044037</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20801,14 +20806,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20819,23 +20834,48 @@
       </c>
       <c r="AG179" t="b">
         <v>0</v>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129303116</v>
+        <v>129303112</v>
       </c>
       <c r="B180" t="n">
         <v>57740</v>
@@ -20870,10 +20910,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>524033</v>
+        <v>524044</v>
       </c>
       <c r="R180" t="n">
-        <v>7043952</v>
+        <v>7043935</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20937,7 +20977,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129303138</v>
+        <v>129303116</v>
       </c>
       <c r="B181" t="n">
         <v>57740</v>
@@ -20972,10 +21012,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>523879</v>
+        <v>524033</v>
       </c>
       <c r="R181" t="n">
-        <v>7044256</v>
+        <v>7043952</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21012,7 +21052,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21039,7 +21079,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129303131</v>
+        <v>129303138</v>
       </c>
       <c r="B182" t="n">
         <v>57740</v>
@@ -21074,10 +21114,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>524059</v>
+        <v>523879</v>
       </c>
       <c r="R182" t="n">
-        <v>7044016</v>
+        <v>7044256</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21141,7 +21181,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129303128</v>
+        <v>129303131</v>
       </c>
       <c r="B183" t="n">
         <v>57740</v>
@@ -21176,10 +21216,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>524186</v>
+        <v>524059</v>
       </c>
       <c r="R183" t="n">
-        <v>7043943</v>
+        <v>7044016</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21216,7 +21256,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21243,7 +21283,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129294096</v>
+        <v>129303128</v>
       </c>
       <c r="B184" t="n">
         <v>57740</v>
@@ -21272,24 +21312,19 @@
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>523971</v>
+        <v>524186</v>
       </c>
       <c r="R184" t="n">
-        <v>7044037</v>
+        <v>7043943</v>
       </c>
       <c r="S184" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21316,24 +21351,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid gammal hyggeskant.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21344,48 +21369,23 @@
       </c>
       <c r="AG184" t="b">
         <v>0</v>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129303147</v>
+        <v>129284399</v>
       </c>
       <c r="B185" t="n">
         <v>57740</v>
@@ -21414,19 +21414,24 @@
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>sävsselet sö, Jmt</t>
+          <t>Oxmyren, Oxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>523930</v>
+        <v>523878</v>
       </c>
       <c r="R185" t="n">
-        <v>7044107</v>
+        <v>7044161</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21453,14 +21458,24 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska och tydliga, på en gran.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21471,23 +21486,48 @@
       </c>
       <c r="AG185" t="b">
         <v>0</v>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129303146</v>
+        <v>129303114</v>
       </c>
       <c r="B186" t="n">
         <v>57740</v>
@@ -21522,10 +21562,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>523926</v>
+        <v>524041</v>
       </c>
       <c r="R186" t="n">
-        <v>7044118</v>
+        <v>7043942</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21562,7 +21602,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21589,7 +21629,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129303126</v>
+        <v>129303147</v>
       </c>
       <c r="B187" t="n">
         <v>57740</v>
@@ -21624,10 +21664,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>523960</v>
+        <v>523930</v>
       </c>
       <c r="R187" t="n">
-        <v>7044047</v>
+        <v>7044107</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21664,7 +21704,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21691,7 +21731,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129303114</v>
+        <v>129303146</v>
       </c>
       <c r="B188" t="n">
         <v>57740</v>
@@ -21726,10 +21766,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>524041</v>
+        <v>523926</v>
       </c>
       <c r="R188" t="n">
-        <v>7043942</v>
+        <v>7044118</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21766,7 +21806,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21793,7 +21833,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129284399</v>
+        <v>129303126</v>
       </c>
       <c r="B189" t="n">
         <v>57740</v>
@@ -21822,24 +21862,19 @@
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Oxmyren, Oxmyren, Jmt</t>
+          <t>sävsselet sö, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>523878</v>
+        <v>523960</v>
       </c>
       <c r="R189" t="n">
-        <v>7044161</v>
+        <v>7044047</v>
       </c>
       <c r="S189" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21866,24 +21901,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Ringhack, färska och tydliga, på en gran.</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21894,41 +21919,16 @@
       </c>
       <c r="AG189" t="b">
         <v>0</v>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO189" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>

--- a/artfynd/A 47364-2025 artfynd.xlsx
+++ b/artfynd/A 47364-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY202"/>
+  <dimension ref="A1:AZ202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303209</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303208</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303080</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129376007</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303151</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129286799</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129287611</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129287621</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129287712</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1761,6 +1811,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290450</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1873,6 +1928,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129292744</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1970,6 +2030,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303149</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2107,6 +2172,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129287170</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2214,6 +2284,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129287650</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2346,6 +2421,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129289352</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2453,6 +2533,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129289415</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2590,6 +2675,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129289809</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2722,6 +2812,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290115</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2859,6 +2954,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129292345</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2971,6 +3071,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294284</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3078,6 +3183,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294482</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3210,6 +3320,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295010</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3317,6 +3432,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295161</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3424,6 +3544,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295347</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3556,6 +3681,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295640</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3698,6 +3828,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295781</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3800,6 +3935,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303195</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3902,6 +4042,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303196</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3999,6 +4144,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303197</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4096,6 +4246,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303198</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4193,6 +4348,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303199</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4290,6 +4450,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303200</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4387,6 +4552,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303201</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4489,6 +4659,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303202</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4586,6 +4761,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303203</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4688,6 +4868,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303204</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4790,6 +4975,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303205</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4892,6 +5082,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303206</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4989,6 +5184,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303207</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5121,6 +5321,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294585</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5258,6 +5463,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129286739</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5390,6 +5600,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129289835</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5532,6 +5747,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129289927</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5674,6 +5894,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290529</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5811,6 +6036,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294247</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5943,6 +6173,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294611</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6040,6 +6275,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303152</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6137,6 +6377,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303153</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6234,6 +6479,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303154</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6331,6 +6581,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303155</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6452,6 +6707,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303156</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6549,6 +6809,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303157</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6646,6 +6911,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303158</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6743,6 +7013,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303159</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6840,6 +7115,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303160</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6937,6 +7217,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303161</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7034,6 +7319,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303162</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7131,6 +7421,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303163</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7228,6 +7523,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303164</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7325,6 +7625,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303165</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7422,6 +7727,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303166</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7519,6 +7829,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303167</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7616,6 +7931,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303168</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7713,6 +8033,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303169</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7810,6 +8135,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303170</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7907,6 +8237,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303171</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8004,6 +8339,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303172</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8101,6 +8441,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303173</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8198,6 +8543,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303174</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8295,6 +8645,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303175</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8392,6 +8747,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303176</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8489,6 +8849,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303177</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8631,6 +8996,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129283648</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8773,6 +9143,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129283727</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8915,6 +9290,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129284163</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9057,6 +9437,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129284399</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9199,6 +9584,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129284656</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9341,6 +9731,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129285070</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9483,6 +9878,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129285747</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9625,6 +10025,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129286184</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9767,6 +10172,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290167</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9909,6 +10319,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290433</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10056,6 +10471,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290684</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10203,6 +10623,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290810</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10345,6 +10770,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129291995</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10487,6 +10917,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129292836</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10629,6 +11064,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294077</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10771,6 +11211,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294096</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10913,6 +11358,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294128</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11055,6 +11505,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294143</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11197,6 +11652,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294174</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11339,6 +11799,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294258</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11486,6 +11951,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295476</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11628,6 +12098,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295685</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11770,6 +12245,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295984</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11912,6 +12392,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296040</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12014,6 +12499,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303081</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12116,6 +12606,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303082</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12218,6 +12713,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303083</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12320,6 +12820,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303084</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12422,6 +12927,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303085</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12524,6 +13034,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303086</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12626,6 +13141,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303087</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12728,6 +13248,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303088</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12830,6 +13355,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303089</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12932,6 +13462,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303090</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13034,6 +13569,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303091</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13136,6 +13676,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303092</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13238,6 +13783,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303093</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13340,6 +13890,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303094</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13442,6 +13997,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303095</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13544,6 +14104,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303096</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13646,6 +14211,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303097</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13748,6 +14318,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303098</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13850,6 +14425,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303099</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13952,6 +14532,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303100</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14054,6 +14639,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303101</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14156,6 +14746,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303102</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14258,6 +14853,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303103</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14360,6 +14960,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303104</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14462,6 +15067,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303105</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14564,6 +15174,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303106</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14666,6 +15281,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303107</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14768,6 +15388,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303108</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14870,6 +15495,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303109</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14972,6 +15602,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303110</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15074,6 +15709,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303111</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15176,6 +15816,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303112</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15278,6 +15923,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303113</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15380,6 +16030,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303114</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15482,6 +16137,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303115</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15584,6 +16244,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303116</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15686,6 +16351,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303117</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15788,6 +16458,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303118</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15890,6 +16565,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303119</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15992,6 +16672,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303120</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16094,6 +16779,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303121</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16196,6 +16886,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303122</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16298,6 +16993,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303123</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16400,6 +17100,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303124</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16502,6 +17207,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303125</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16604,6 +17314,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303126</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16706,6 +17421,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303127</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16808,6 +17528,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303128</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16910,6 +17635,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303129</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17012,6 +17742,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303130</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17114,6 +17849,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303131</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17216,6 +17956,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303132</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17318,6 +18063,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303133</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17420,6 +18170,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303134</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17522,6 +18277,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303135</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17624,6 +18384,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303136</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17726,6 +18491,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303137</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17828,6 +18598,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303138</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17930,6 +18705,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303139</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18032,6 +18812,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303140</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18134,6 +18919,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303141</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18236,6 +19026,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303142</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18338,6 +19133,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303143</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18440,6 +19240,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303144</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18542,6 +19347,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303145</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18644,6 +19454,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303146</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18746,6 +19561,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303147</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18848,6 +19668,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303148</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18984,6 +19809,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129286516</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19115,6 +19945,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129291288</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19246,6 +20081,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293975</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19363,6 +20203,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294979</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19489,6 +20334,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293037</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19620,6 +20470,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293149</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19756,6 +20611,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129289693</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19887,6 +20747,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290074</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20023,6 +20888,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290296</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20159,6 +21029,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129291435</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20295,6 +21170,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129291542</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20431,6 +21311,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294021</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20562,6 +21447,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294365</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20693,6 +21583,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294458</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20824,6 +21719,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294820</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20960,6 +21860,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295240</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21091,6 +21996,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295438</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21227,6 +22137,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296356</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21363,6 +22278,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296451</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21460,6 +22380,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303178</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21579,6 +22504,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303179</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21698,6 +22628,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303180</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21817,6 +22752,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303181</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21914,6 +22854,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303182</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -22033,6 +22978,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303183</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22152,6 +23102,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303184</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22271,6 +23226,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303185</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22390,6 +23350,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303186</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22509,6 +23474,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303187</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22606,6 +23576,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303188</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22703,6 +23678,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303189</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22822,6 +23802,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303190</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22941,6 +23926,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303191</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -23038,6 +24028,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303192</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23157,6 +24152,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303193</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -23276,6 +24276,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303194</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23373,8 +24378,216 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303210</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>